--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 05-19 (회사 개발 착수 이후)</t>
+          <t>2026-04-21 ~ 05-22 (회사 개발 착수 이후)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>536건 (회사 기간 448건)</t>
+          <t>570건 (회사 기간 490건)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>55 / 64개 (86%)</t>
+          <t>63 / 73개 (86%)</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■</t>
+            <t>■■■■■■■■■■■■</t>
           </r>
           <r>
             <rPr>
@@ -1557,14 +1557,69 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (8)</t>
+            <t xml:space="preserve">  (30)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-21  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-22  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (1)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="40">
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
@@ -1601,6 +1656,7 @@
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1613,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1887,7 +1943,37 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-16 ~ 05-22</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>인프라·모바일·불량 처리</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>WS1~WS10 배포 안정화·보안 강화
+모바일 UI/UX 전면 개편(디자이너 PASS)
+불량 처리 흐름 재설계 Phase 1 (라인 결재·격리·처리)
+BOM 워크벤치 3-column·완료 워크플로
+입출고 내역 2·3차 main 머지
+권동환 5월 재고 100% 검증·CSV 외부 감시·ItemCode rename</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2947,12 +3033,12 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>직원 명단 관리</t>
+          <t>운영 인프라 안정화 (WS1~WS10)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
@@ -2960,7 +3046,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Docker·보안·로깅·예외·헬스/관측</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
@@ -2968,12 +3058,12 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>부서별 담당 색상 배지 표시</t>
+          <t>입출고 내역 2·3차 정비 (main 머지)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -2981,7 +3071,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr"/>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>model·process_step·department 파라미터</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
@@ -2989,12 +3083,12 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>작업자 PIN 로그인 + 감사 이력</t>
+          <t>모바일 UI/UX 전면 개편</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
@@ -3004,7 +3098,7 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>수정 이력 자동 기록</t>
+          <t>5개 화면 반응형 + 디자이너 PASS</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3108,12 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>로그인 및 권한 관리</t>
+          <t>불량 처리 흐름 재설계 Phase 1</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -3029,7 +3123,7 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>PIN 기반 — 역할별 접근 제어 예정</t>
+          <t>라인 결재·격리·처리·테스트 113건</t>
         </is>
       </c>
     </row>
@@ -3039,12 +3133,12 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>PC 화면 (데스크톱)</t>
+          <t>BOM 워크벤치 3-column + 완료 워크플로</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
@@ -3052,7 +3146,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>BOM 완료 상태 토글 + export</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n">
@@ -3060,12 +3158,12 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>모바일 화면</t>
+          <t>입출고 CSV 외부 감시 시스템</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
@@ -3073,7 +3171,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>월별 누적 미러</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
@@ -3081,12 +3183,12 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>다크 / 라이트 모드</t>
+          <t>ItemCode 도메인 정리</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -3094,7 +3196,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>erp_code 잔재 정리</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
@@ -3102,12 +3208,12 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>관리자 화면</t>
+          <t>외부 PC 첫 실행 안정화</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -3115,7 +3221,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>gitattributes + start.bat 사전 검사</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n">
@@ -3123,12 +3233,12 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>부서 관리 (DnD · 컬러 피커 · 검색)</t>
+          <t>권동환 5월 재고 100% 검증</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
@@ -3136,7 +3246,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>엑셀↔DB 동기화·자식 행 반영</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
@@ -3144,12 +3258,12 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>데이터 CSV 내보내기</t>
+          <t>직원 명단 관리</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -3165,12 +3279,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>원클릭 실행 (start.bat)</t>
+          <t>부서별 담당 색상 배지 표시</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -3186,12 +3300,12 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>테스트 자동화 (CI)</t>
+          <t>작업자 PIN 로그인 + 감사 이력</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -3201,7 +3315,7 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>pytest 42건 + vitest 12건</t>
+          <t>수정 이력 자동 기록</t>
         </is>
       </c>
     </row>
@@ -3211,237 +3325,434 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
+          <t>로그인 및 권한 관리</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>PIN 기반 — 역할별 접근 제어 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>PC 화면 (데스크톱)</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>모바일 화면</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>다크 / 라이트 모드</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>관리자 화면</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>부서 관리 (DnD · 컬러 피커 · 검색)</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>데이터 CSV 내보내기</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>원클릭 실행 (start.bat)</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>테스트 자동화 (CI)</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>pytest 42건 + vitest 12건</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
           <t>WAL-safe 백업 / 복구</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>ops 스크립트 자동화</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>입출고 화면·내역 흐름 재설계</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>입출고</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>담당자 동선 분석 후 (다음 주~다다음주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>BOM·입출고 정리 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>불량 처리 흐름 Phase 2</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>역할별 접근 권한 연동</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>재고</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>외부 접근 환경 구성</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>PC 또는 NAS 서버 + API 인증</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="15" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>발주 관리</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>구매</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="E71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>생산 실적 / 원가 관리</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>부서별 생산진행도 대시보드</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E73" s="16" t="inlineStr">
         <is>
           <t>사장님 요청 — 검토 중</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -3458,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4183,7 +4494,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -4195,6 +4506,50 @@
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="50" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-21 docs: 자체 MES 구축 PR — 1:1 보고용 슬라이드 데크(pr.html)
+2026-05-21 data: 권동환 5월 재고 매칭 - 폴더 정리·사용자 수작업 파일·후보 보조표 스크립트
+2026-05-21 data: 5월 입출고 audit 로그 갱신 — SR-20260520-052533 불량처
+2026-05-21 docs: PR 슬라이드 톤 다듬기 + 환율 정정 ($1=1,500원)
+chore: ERP/erp → MES 표기 일괄 정리 — 도메인 erp_code 식별자는 보존</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="50" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22 chore: vault-sync 코드 작업 일괄 반영 (vault/ 제외, 85파일)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -4211,7 +4566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F537"/>
+  <dimension ref="A1:F571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21406,6 +21761,1094 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B538" s="18" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C538" s="18" t="inlineStr">
+        <is>
+          <t>a5b858aa</t>
+        </is>
+      </c>
+      <c r="D538" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 admin: 외부 심사용 입출고 CSV 미러 시스템 (자동 누적 + 월별 다운로드)</t>
+        </is>
+      </c>
+      <c r="E538" s="18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F538" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C539" s="9" t="inlineStr">
+        <is>
+          <t>91231f96</t>
+        </is>
+      </c>
+      <c r="D539" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 docs: 개발현황 엑셀에 근무 외 작업 시각화 추가</t>
+        </is>
+      </c>
+      <c r="E539" s="9" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F539" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B540" s="18" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C540" s="18" t="inlineStr">
+        <is>
+          <t>ddae2e2c</t>
+        </is>
+      </c>
+      <c r="D540" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 admin: OpenAPI baseline 재생성 (audit-csv 라우터 4종 반영)</t>
+        </is>
+      </c>
+      <c r="E540" s="18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F540" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B541" s="9" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C541" s="9" t="inlineStr">
+        <is>
+          <t>14943b3f</t>
+        </is>
+      </c>
+      <c r="D541" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 입출고 내역 알약 정합 (BOM ± 부호, 구분·단건 통일 폭, 일시/구분 중앙정렬)</t>
+        </is>
+      </c>
+      <c r="E541" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F541" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B542" s="18" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C542" s="18" t="inlineStr">
+        <is>
+          <t>e91f1fe1</t>
+        </is>
+      </c>
+      <c r="D542" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 backend: 주간보고 모델 매트릭스 ProductSymbol DB 기반 동적 매핑</t>
+        </is>
+      </c>
+      <c r="E542" s="18" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F542" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B543" s="9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C543" s="9" t="inlineStr">
+        <is>
+          <t>4db421a2</t>
+        </is>
+      </c>
+      <c r="D543" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 backend: F4b 완료 — UtcDatetime을 전체 응답 스키마로 확산 (9h 오차 근본 수정)</t>
+        </is>
+      </c>
+      <c r="E543" s="9" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F543" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B544" s="18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C544" s="18" t="inlineStr">
+        <is>
+          <t>ab38bcf0</t>
+        </is>
+      </c>
+      <c r="D544" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 docs: F4b 완료에 따라 작업 계획 문서 제거</t>
+        </is>
+      </c>
+      <c r="E544" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F544" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B545" s="9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C545" s="9" t="inlineStr">
+        <is>
+          <t>5ce4e17a</t>
+        </is>
+      </c>
+      <c r="D545" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 대시보드 필터 버튼을 생산가능 행 우측으로 이동</t>
+        </is>
+      </c>
+      <c r="E545" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F545" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B546" s="18" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C546" s="18" t="inlineStr">
+        <is>
+          <t>e8ddce86</t>
+        </is>
+      </c>
+      <c r="D546" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 backend: OpenAPI baseline 갱신 — EmployeeResponse format:date-time 복원</t>
+        </is>
+      </c>
+      <c r="E546" s="18" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F546" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C547" s="9" t="inlineStr">
+        <is>
+          <t>bff4a081</t>
+        </is>
+      </c>
+      <c r="D547" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 입출고 내역 좌측 잔손 — ADJUST 묶음 수량·메모 셀·자동 접힘·담당자 정리</t>
+        </is>
+      </c>
+      <c r="E547" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F547" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B548" s="18" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="C548" s="18" t="inlineStr">
+        <is>
+          <t>6730961c</t>
+        </is>
+      </c>
+      <c r="D548" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 주간보고 공정별 변화 카드 픽셀 조정 + 5월 입출고 감사 CSV</t>
+        </is>
+      </c>
+      <c r="E548" s="18" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F548" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B549" s="9" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C549" s="9" t="inlineStr">
+        <is>
+          <t>7f735504</t>
+        </is>
+      </c>
+      <c r="D549" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 refactor: queue/alerts/counts dead 기능 흔적 제거 + CLAUDE.md 갱신</t>
+        </is>
+      </c>
+      <c r="E549" s="9" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F549" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B550" s="18" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C550" s="18" t="inlineStr">
+        <is>
+          <t>cab3e4f1</t>
+        </is>
+      </c>
+      <c r="D550" s="19" t="inlineStr">
+        <is>
+          <t>Merge feat/cleanup-dead-pages: queue/alerts/counts dead 기능 흔적 제거</t>
+        </is>
+      </c>
+      <c r="E550" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F550" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B551" s="9" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C551" s="9" t="inlineStr">
+        <is>
+          <t>7c7edeb7</t>
+        </is>
+      </c>
+      <c r="D551" s="10" t="inlineStr">
+        <is>
+          <t>chore: separate dev baselines from attic</t>
+        </is>
+      </c>
+      <c r="E551" s="9" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F551" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B552" s="18" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C552" s="18" t="inlineStr">
+        <is>
+          <t>f1695796</t>
+        </is>
+      </c>
+      <c r="D552" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 입출고 내역 우측 카드 재정비 — Hero 통합·좌측 톤 일관</t>
+        </is>
+      </c>
+      <c r="E552" s="18" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F552" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B553" s="9" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C553" s="9" t="inlineStr">
+        <is>
+          <t>50979139</t>
+        </is>
+      </c>
+      <c r="D553" s="10" t="inlineStr">
+        <is>
+          <t>Merge feat/history-phase4: 입출고 내역 우측 카드 재정비</t>
+        </is>
+      </c>
+      <c r="E553" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F553" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B554" s="18" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C554" s="18" t="inlineStr">
+        <is>
+          <t>f22065dc</t>
+        </is>
+      </c>
+      <c r="D554" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: BOM/단품 chip 도 구분 열 FlowBadge 규칙으로 통일 (min-w-6.5rem · px-3 py-1 · text-xs · tracking-wide)</t>
+        </is>
+      </c>
+      <c r="E554" s="18" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F554" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B555" s="9" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C555" s="9" t="inlineStr">
+        <is>
+          <t>e3a7c033</t>
+        </is>
+      </c>
+      <c r="D555" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: BOM 워크벤치 잘린 품목명·코드 호버 시 풀네임 툴팁</t>
+        </is>
+      </c>
+      <c r="E555" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F555" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B556" s="18" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C556" s="18" t="inlineStr">
+        <is>
+          <t>77c5df46</t>
+        </is>
+      </c>
+      <c r="D556" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 docs: 발표 대본 초안 SCRIPT.md 추가</t>
+        </is>
+      </c>
+      <c r="E556" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F556" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C557" s="9" t="inlineStr">
+        <is>
+          <t>db7ae55d</t>
+        </is>
+      </c>
+      <c r="D557" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 desktop: 부서 내 작업 흐름 표시 — batch.from==to 면 그 부서 단일 표기</t>
+        </is>
+      </c>
+      <c r="E557" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F557" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B558" s="18" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C558" s="18" t="inlineStr">
+        <is>
+          <t>188582d4</t>
+        </is>
+      </c>
+      <c r="D558" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-20 backend: 품목 추가 시 erp_code 시리얼 카테고리 전역 스코프 + sort_order 자동 부여</t>
+        </is>
+      </c>
+      <c r="E558" s="18" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F558" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C559" s="9" t="inlineStr">
+        <is>
+          <t>ebf71d31</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-20 data: 권동환 5월 재고 ↔ MES 마스터 매칭 산출물·스크립트</t>
+        </is>
+      </c>
+      <c r="E559" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F559" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B560" s="18" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C560" s="18" t="inlineStr">
+        <is>
+          <t>cb178b8d</t>
+        </is>
+      </c>
+      <c r="D560" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-21 docs: 자체 MES 구축 PR — 1:1 보고용 슬라이드 데크(pr.html)</t>
+        </is>
+      </c>
+      <c r="E560" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F560" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C561" s="9" t="inlineStr">
+        <is>
+          <t>a246db65</t>
+        </is>
+      </c>
+      <c r="D561" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21 data: 권동환 5월 재고 매칭 - 폴더 정리·사용자 수작업 파일·후보 보조표 스크립트</t>
+        </is>
+      </c>
+      <c r="E561" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F561" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B562" s="18" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C562" s="18" t="inlineStr">
+        <is>
+          <t>21e98cdf</t>
+        </is>
+      </c>
+      <c r="D562" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-21 data: 5월 입출고 audit 로그 갱신 — SR-20260520-052533 불량처리 승인 기록 1건</t>
+        </is>
+      </c>
+      <c r="E562" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F562" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="C563" s="9" t="inlineStr">
+        <is>
+          <t>00feb4c7</t>
+        </is>
+      </c>
+      <c r="D563" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21 docs: PR 슬라이드 톤 다듬기 + 환율 정정 ($1=1,500원)</t>
+        </is>
+      </c>
+      <c r="E563" s="9" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F563" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B564" s="18" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="C564" s="18" t="inlineStr">
+        <is>
+          <t>214020e1</t>
+        </is>
+      </c>
+      <c r="D564" s="19" t="inlineStr">
+        <is>
+          <t>chore: ERP/erp → MES 표기 일괄 정리 — 도메인 erp_code 식별자는 보존</t>
+        </is>
+      </c>
+      <c r="E564" s="18" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F564" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="C565" s="9" t="inlineStr">
+        <is>
+          <t>b792f7a0</t>
+        </is>
+      </c>
+      <c r="D565" s="10" t="inlineStr">
+        <is>
+          <t>refactor: 입출고 내역 구분 라벨 — 죽은 거래 타입 5종 완전 제거</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F565" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B566" s="18" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C566" s="18" t="inlineStr">
+        <is>
+          <t>33b9e321</t>
+        </is>
+      </c>
+      <c r="D566" s="19" t="inlineStr">
+        <is>
+          <t>docs: 발표 슬라이드 파일명 변경 — 교육.html / 비교.html</t>
+        </is>
+      </c>
+      <c r="E566" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F566" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B567" s="9" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C567" s="9" t="inlineStr">
+        <is>
+          <t>f1ff96ce</t>
+        </is>
+      </c>
+      <c r="D567" s="10" t="inlineStr">
+        <is>
+          <t>chore: items.item_code 통합 + ErpCode → ItemCode 도메인 rename</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F567" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B568" s="18" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C568" s="18" t="inlineStr">
+        <is>
+          <t>4d5861a6</t>
+        </is>
+      </c>
+      <c r="D568" s="19" t="inlineStr">
+        <is>
+          <t>docs: 불량 처리 흐름 재설계 문서 추가</t>
+        </is>
+      </c>
+      <c r="E568" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F568" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>c6aa0eb8</t>
+        </is>
+      </c>
+      <c r="D569" s="10" t="inlineStr">
+        <is>
+          <t>chore: ERP 잔재 후속 정리 — cosmetic + 누락된 진짜 잔재</t>
+        </is>
+      </c>
+      <c r="E569" s="9" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F569" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B570" s="18" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C570" s="18" t="inlineStr">
+        <is>
+          <t>fe1c1ba1</t>
+        </is>
+      </c>
+      <c r="D570" s="19" t="inlineStr">
+        <is>
+          <t>chore: 외부 PC 첫 실행 안정화 — .gitattributes + start.bat 사전 검사</t>
+        </is>
+      </c>
+      <c r="E570" s="18" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F570" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B571" s="9" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C571" s="9" t="inlineStr">
+        <is>
+          <t>174ba759</t>
+        </is>
+      </c>
+      <c r="D571" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22 chore: vault-sync 코드 작업 일괄 반영 (vault/ 제외, 85파일)</t>
+        </is>
+      </c>
+      <c r="E571" s="9" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F571" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 05-22 (회사 개발 착수 이후)</t>
+          <t>2026-04-21 ~ 05-28 (회사 개발 착수 이후)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>570건 (회사 기간 490건)</t>
+          <t>722건 (회사 기간 637건)</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>179건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>276건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>63 / 73개 (86%)</t>
+          <t>73 / 83개 (88%)</t>
         </is>
       </c>
     </row>
@@ -1608,16 +1608,219 @@
           </r>
           <r>
             <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (1)</t>
+            <t xml:space="preserve">  (4)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-23  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (67)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-24  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (23)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-25  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (3)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-26  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (10)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-27  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (38)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-28  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (3)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-29  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (5)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="47">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -1626,20 +1829,25 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
@@ -1651,11 +1859,13 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
@@ -1669,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1969,9 +2179,41 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-23 ~ 05-28</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>사내 시연 + 양식 정비 + 운영 정책 맞춤</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>관리자 화면 4종 한꺼번에 보강 (저장 경고·공통 버튼·BOM 전체 필터)
+직원별 입출고 권한 토글 신설 (개인 단위 차단)
+화면 데이터 갱신 방식 정비 (React Query)
+불량 처리·입출고 흐름 정합 + 5/28 자동결재·재작업 후속 보완
+품목 시리얼(공정 단위) + 김건호 과장님 검토 5월 재고 검증
+품목 관리 소프트 삭제 보강 / 생산 가능 화면 모델별 대표 제품 5종
+현장 사용성 피드백 11건 일괄 반영
+생산부 사내 시연 + 6월 전환 계획 공유 (5/27)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1988,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3258,12 +3500,12 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>직원 명단 관리</t>
+          <t>직원별 입출고 권한 토글 신설</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -3271,7 +3513,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>직원 개인 단위 토글, 꺼지면 진입 불가</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n">
@@ -3279,12 +3525,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>부서별 담당 색상 배지 표시</t>
+          <t>관리자 화면 4종 한꺼번에 보강</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -3292,7 +3538,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr"/>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>저장 경고·공통 버튼·BOM 전체 필터·대시보드 동선</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n">
@@ -3300,12 +3550,12 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>작업자 PIN 로그인 + 감사 이력</t>
+          <t>화면 데이터 갱신 방식 정비</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -3315,7 +3565,7 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>수정 이력 자동 기록</t>
+          <t>React Query 도입·도메인 10여 개 통일</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3575,12 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>로그인 및 권한 관리</t>
+          <t>모델 관리 인라인 편집 + 끌어서 정렬</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -3340,7 +3590,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>PIN 기반 — 역할별 접근 제어 예정</t>
+          <t>정렬 순서 DB 컬럼 추가</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3600,12 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>PC 화면 (데스크톱)</t>
+          <t>불량 처리 흐름 후속 보완</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -3363,7 +3613,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>5/28 자동결재·재작업 화면·요청자/승인자 표시</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n">
@@ -3371,12 +3625,12 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>모바일 화면</t>
+          <t>품목 시리얼 (공정 단위) + 5월 재고 검증</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -3384,7 +3638,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr"/>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>공정 단위, 김건호 과장님 검토 반영</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n">
@@ -3392,12 +3650,12 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>다크 / 라이트 모드</t>
+          <t>품목 관리 — 소프트 삭제 보강</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -3405,7 +3663,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>삭제 시 비활성 상태로 목록 아래, 재활성 가능</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n">
@@ -3413,12 +3675,12 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>관리자 화면</t>
+          <t>생산 가능 화면 — 모델별 대표 제품 5종</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -3426,7 +3688,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>기존 합계 표시 → 대표 완제품 5종으로</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n">
@@ -3434,12 +3700,12 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>부서 관리 (DnD · 컬러 피커 · 검색)</t>
+          <t>현장 사용성 피드백 11건 일괄 반영</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
@@ -3447,7 +3713,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>안내 메시지·모달·큰 이미지 보기·필터 통일 등</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n">
@@ -3455,12 +3725,12 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>데이터 CSV 내보내기</t>
+          <t>백엔드 큰 파일 정리 (종류별 분리)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -3468,7 +3738,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr"/>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>models.py·bootstrap_db.py + 로그인 인증 흐름 정리</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n">
@@ -3476,12 +3750,12 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>원클릭 실행 (start.bat)</t>
+          <t>직원 명단 관리</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
@@ -3497,12 +3771,12 @@
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>테스트 자동화 (CI)</t>
+          <t>부서별 담당 색상 배지 표시</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
@@ -3510,11 +3784,7 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>pytest 42건 + vitest 12건</t>
-        </is>
-      </c>
+      <c r="E64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="n">
@@ -3522,237 +3792,459 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
+          <t>작업자 PIN 로그인 + 감사 이력</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>수정 이력 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>로그인 및 권한 관리</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>PIN 기반 — 역할별 접근 제어 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>PC 화면 (데스크톱)</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>모바일 화면</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>다크 / 라이트 모드</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>관리자 화면</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>부서 관리 (DnD · 컬러 피커 · 검색)</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>데이터 CSV 내보내기</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>원클릭 실행 (start.bat)</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>테스트 자동화 (CI)</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>pytest 42건 + vitest 12건</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
           <t>WAL-safe 백업 / 복구</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>ops 스크립트 자동화</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="15" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>데이터</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
         <is>
           <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="15" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>부서 결재·집계·자동화</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>역할별 접근 권한 연동</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E78" s="16" t="inlineStr">
         <is>
           <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="15" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
-      <c r="C69" s="15" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>재고</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E79" s="16" t="inlineStr">
         <is>
           <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>외부 접근 환경 구성</t>
         </is>
       </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>PC 또는 NAS 서버 + API 인증</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>발주 관리</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>구매</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E71" s="16" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="E81" s="16" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>생산 실적 / 원가 관리</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C82" s="15" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>부서별 생산진행도 대시보드</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t>사장님 요청 — 검토 중</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="15" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -3769,7 +4261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4542,14 +5034,181 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>2026-05-22 chore: vault-sync 코드 작업 일괄 반영 (vault/ 제외, 85파일)</t>
+          <t>2026-05-22 chore: vault-sync 코드 작업 일괄 반영 (vault/ 제외, 85파일)
+2026-05-22 docs: 주간보고 5/16~5/22 작성 + 개발현황 엑셀 갱신
+feat: BOM 자동 연결 스크립트 + capacity API PF 필터 + 상세 모달 개편
+fix: capacity 모달 품목코드/light·dark 색상 + ThemeToggle data-theme</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="50" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>67</v>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>[PR-3.3-2a-badge-remove] 필터 버튼 숫자 배지 제거
+[PR-3.3-2b-clear-chip] 필터 적용 칩에 초기화 X 아이콘 추가
+[PR-3.3-1a-button] feat: 공통 Button 컴포넌트 신설 (variant/size/ico
+[PR-3.3-1b-filterchip] refactor: FilterChip → Button(ghost/s
+[PR-1.1-2] feat: 같은 품목 중복 선택 시 수량 합산 (addItem 재요청+교체)</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>[W7-2-employees] React Query: employees
+[W7-3-items] React Query: items
+[W9-C] employees.reset_employee_pin PIN seam 통합
+[W9-B] models.py 705줄 -&gt; 도메인별 models/ 패키지 분리
+[W9-A] /api/transactions/monthly-counts endpoint 신규</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="50" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>[weekly] 공정별 변화 하단 행 grid-cols-3 — 출고가 카드 간 같은 x 에 정렬
+[ux] 사이드바·테마토글 비활성 아이콘 배경 transparent
+[chore] audit CSV — 2026-05-24 입출고 거래 9건 추가</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>[defect][io] 불량 처리·입출고 흐름 종합 개편
+[chore] audit CSV — 2026-05 거래 누적 반영
+[defect][chore] B/C 체크리스트 마무리 — historyBatchInterpreter defe
+[capacity] 합계 → 모델별 대표 PF 5종 표시로 재설계
+[admin][item] 품목 소프트 삭제/복구 기능 + 관련 UI 개선</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="50" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-26 docs: CLAUDE.md에 커밋 메시지 형식 규칙 명시
+2026-05-27 ux: Step 1 — 피드백 11건 반영
+2026-05-27 ux: Step 2 — 단일 화면 로직 버그 3건
+2026-05-27 ux: Step 3 — 모달 드래그 닫힘 버그 fix (2번)
+2026-05-27 ux: Step 3 v2 — 모달 드래그 닫힘 양방향 차단 보강</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="50" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-28 docs: 발표 후속 자료 — 슬라이드 보완 + 피드백 양식 + 컨닝페이퍼
+2026-05-28 defect: 불량 자동결재·재작업 트리뷰·UI 문구 정리·요청자/승인자 버그
+2026-05-28 docs: CLAUDE.md — 커밋 메시지 날짜는 실제 시점(date 명령)으로 확인 </t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="50" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-29 weekly: 매트릭스 거래타입 분류 상수화·enum 누락 방어·백엔드 동결
+2026-05-29 frontend: 입출고 내역 재작업 우측 패널 title + 불량 BOM 펼침 버튼
+2026-05-29 docs: 피드백 모음 폴더 신설 (허동현·김건호·김민재)
+2026-05-29 docs: 주간보고 5/23~5/28 메일 + 변환 스크립트 + 양식 규칙
+2026-05-29 feedback: 허동현 4건 추가 (사진정책·담당자검증·소수점·PIN자리수)</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -4566,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F571"/>
+  <dimension ref="A1:F723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22849,6 +23508,4870 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B572" s="18" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C572" s="18" t="inlineStr">
+        <is>
+          <t>9d97ed24</t>
+        </is>
+      </c>
+      <c r="D572" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-22 docs: 주간보고 5/16~5/22 작성 + 개발현황 엑셀 갱신</t>
+        </is>
+      </c>
+      <c r="E572" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F572" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B573" s="22" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="C573" s="22" t="inlineStr">
+        <is>
+          <t>4924327d</t>
+        </is>
+      </c>
+      <c r="D573" s="23" t="inlineStr">
+        <is>
+          <t>feat: BOM 자동 연결 스크립트 + capacity API PF 필터 + 상세 모달 개편</t>
+        </is>
+      </c>
+      <c r="E573" s="22" t="inlineStr">
+        <is>
+          <t>feat</t>
+        </is>
+      </c>
+      <c r="F573" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B574" s="22" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="C574" s="22" t="inlineStr">
+        <is>
+          <t>b763aafd</t>
+        </is>
+      </c>
+      <c r="D574" s="23" t="inlineStr">
+        <is>
+          <t>fix: capacity 모달 품목코드/light·dark 색상 + ThemeToggle data-theme 셀렉터 일치</t>
+        </is>
+      </c>
+      <c r="E574" s="22" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F574" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B575" s="22" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C575" s="22" t="inlineStr">
+        <is>
+          <t>7c4fa400</t>
+        </is>
+      </c>
+      <c r="D575" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-2a-badge-remove] 필터 버튼 숫자 배지 제거</t>
+        </is>
+      </c>
+      <c r="E575" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F575" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B576" s="22" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C576" s="22" t="inlineStr">
+        <is>
+          <t>232536a1</t>
+        </is>
+      </c>
+      <c r="D576" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-2b-clear-chip] 필터 적용 칩에 초기화 X 아이콘 추가</t>
+        </is>
+      </c>
+      <c r="E576" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F576" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B577" s="22" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C577" s="22" t="inlineStr">
+        <is>
+          <t>5ecc5d06</t>
+        </is>
+      </c>
+      <c r="D577" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1a-button] feat: 공통 Button 컴포넌트 신설 (variant/size/icon/loading)</t>
+        </is>
+      </c>
+      <c r="E577" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F577" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B578" s="22" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C578" s="22" t="inlineStr">
+        <is>
+          <t>df152c27</t>
+        </is>
+      </c>
+      <c r="D578" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1b-filterchip] refactor: FilterChip → Button(ghost/secondary) 기반으로 교체</t>
+        </is>
+      </c>
+      <c r="E578" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F578" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B579" s="22" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C579" s="22" t="inlineStr">
+        <is>
+          <t>111f9787</t>
+        </is>
+      </c>
+      <c r="D579" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-2] feat: 같은 품목 중복 선택 시 수량 합산 (addItem 재요청+교체)</t>
+        </is>
+      </c>
+      <c r="E579" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F579" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B580" s="22" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C580" s="22" t="inlineStr">
+        <is>
+          <t>d81b4da5</t>
+        </is>
+      </c>
+      <c r="D580" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1c-admin-headers] refactor: AdminPageHeader 추가/저장/취소 버튼 → Button 컴포넌트 교체 (모델·품목·직원·부서)</t>
+        </is>
+      </c>
+      <c r="E580" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F580" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B581" s="22" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C581" s="22" t="inlineStr">
+        <is>
+          <t>b60e6afc</t>
+        </is>
+      </c>
+      <c r="D581" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-3a-viewmode] HistoryCalendarStrip viewMode + 부모 setter 노출</t>
+        </is>
+      </c>
+      <c r="E581" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F581" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B582" s="22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C582" s="22" t="inlineStr">
+        <is>
+          <t>832646fc</t>
+        </is>
+      </c>
+      <c r="D582" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1d-bom] refactor: BomWorkbench 내보내기·편집·사용처 버튼 → Button 컴포넌트 교체</t>
+        </is>
+      </c>
+      <c r="E582" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F582" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B583" s="22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C583" s="22" t="inlineStr">
+        <is>
+          <t>cb2ce830</t>
+        </is>
+      </c>
+      <c r="D583" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1e-pin] refactor: AdminDangerZone PIN 변경 버튼 → Button 컴포넌트 교체</t>
+        </is>
+      </c>
+      <c r="E583" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F583" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B584" s="22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C584" s="22" t="inlineStr">
+        <is>
+          <t>9b5d8978</t>
+        </is>
+      </c>
+      <c r="D584" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-1a] handleGoToWarehouse: router.push(?tab=warehouse) 추가</t>
+        </is>
+      </c>
+      <c r="E584" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F584" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B585" s="22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C585" s="22" t="inlineStr">
+        <is>
+          <t>110f9f86</t>
+        </is>
+      </c>
+      <c r="D585" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-3b-yearview] 연도 단위 fetch + monthlyCountMap 연 뷰 카드 채우기</t>
+        </is>
+      </c>
+      <c r="E585" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F585" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B586" s="22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C586" s="22" t="inlineStr">
+        <is>
+          <t>22cfe7d8</t>
+        </is>
+      </c>
+      <c r="D586" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3.3-1f-wizard] refactor: WizardStepCard '다음 단계로' 버튼 → Button 컴포넌트 교체</t>
+        </is>
+      </c>
+      <c r="E586" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F586" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B587" s="22" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="C587" s="22" t="inlineStr">
+        <is>
+          <t>121b4ecc</t>
+        </is>
+      </c>
+      <c r="D587" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-3] feat: AdminDepartmentsContext에 dirty/setDirty 상태 노출</t>
+        </is>
+      </c>
+      <c r="E587" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F587" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B588" s="22" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="C588" s="22" t="inlineStr">
+        <is>
+          <t>3aac2724</t>
+        </is>
+      </c>
+      <c r="D588" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-1b] IoTargetPicker: highlightItemId prop + row scrollIntoView/flash</t>
+        </is>
+      </c>
+      <c r="E588" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F588" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B589" s="22" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C589" s="22" t="inlineStr">
+        <is>
+          <t>3a050778</t>
+        </is>
+      </c>
+      <c r="D589" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-1c] IoComposeView: preselectedItem BOM 분기 + workType 가드</t>
+        </is>
+      </c>
+      <c r="E589" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F589" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B590" s="22" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="C590" s="22" t="inlineStr">
+        <is>
+          <t>c0897757</t>
+        </is>
+      </c>
+      <c r="D590" s="23" t="inlineStr">
+        <is>
+          <t>[PR-1.1-1d] MobileIoComposeWizard: 동일 preselectedItem BOM 분기 적용</t>
+        </is>
+      </c>
+      <c r="E590" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F590" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B591" s="22" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C591" s="22" t="inlineStr">
+        <is>
+          <t>ec34be89</t>
+        </is>
+      </c>
+      <c r="D591" s="23" t="inlineStr">
+        <is>
+          <t>merge: PR-1 1-2 중복 품목 합산 (A2 worktree)</t>
+        </is>
+      </c>
+      <c r="E591" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F591" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B592" s="22" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C592" s="22" t="inlineStr">
+        <is>
+          <t>e8b5959a</t>
+        </is>
+      </c>
+      <c r="D592" s="23" t="inlineStr">
+        <is>
+          <t>merge: PR-1 1-1 대시보드→입출고 URL 동선 + preselectedItem (A1 worktree)</t>
+        </is>
+      </c>
+      <c r="E592" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F592" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B593" s="22" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C593" s="22" t="inlineStr">
+        <is>
+          <t>deeeca03</t>
+        </is>
+      </c>
+      <c r="D593" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-4] Fix: 품목 관리 status pill 자리 고정 — 부족 텍스트 잘림 해결</t>
+        </is>
+      </c>
+      <c r="E593" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F593" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B594" s="22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C594" s="22" t="inlineStr">
+        <is>
+          <t>8e2fff6f</t>
+        </is>
+      </c>
+      <c r="D594" s="23" t="inlineStr">
+        <is>
+          <t>[PR-4.4-1a-text-input][PR-4.4-1b-preset] 부서 색상 — 숨겨진 color input 제거, hex 텍스트 입력 + 실시간 검증, Tailwind 36색 프리셋 팔레트 추가</t>
+        </is>
+      </c>
+      <c r="E594" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F594" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B595" s="22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C595" s="22" t="inlineStr">
+        <is>
+          <t>1ac1c472</t>
+        </is>
+      </c>
+      <c r="D595" s="23" t="inlineStr">
+        <is>
+          <t>[PR-4.4-2a-type] BomDeptFilter 타입 추가 (DeptLetter | "ALL")</t>
+        </is>
+      </c>
+      <c r="E595" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F595" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B596" s="22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C596" s="22" t="inlineStr">
+        <is>
+          <t>28ead1e3</t>
+        </is>
+      </c>
+      <c r="D596" s="23" t="inlineStr">
+        <is>
+          <t>[PR-4.4-2b-tabs] BomDeptTabs에 "전체" 칩 첫 항목 추가</t>
+        </is>
+      </c>
+      <c r="E596" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F596" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B597" s="22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C597" s="22" t="inlineStr">
+        <is>
+          <t>d78aed92</t>
+        </is>
+      </c>
+      <c r="D597" s="23" t="inlineStr">
+        <is>
+          <t>[PR-4.4-2c-filter] BOM 부서 필터 "ALL" 지원</t>
+        </is>
+      </c>
+      <c r="E597" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F597" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B598" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C598" s="22" t="inlineStr">
+        <is>
+          <t>75bf92a0</t>
+        </is>
+      </c>
+      <c r="D598" s="23" t="inlineStr">
+        <is>
+          <t>feat: 모델·품목 관리의 '+추가' 버튼을 페이지 헤더에서 목록 패널 헤더로 이동</t>
+        </is>
+      </c>
+      <c r="E598" s="22" t="inlineStr">
+        <is>
+          <t>feat</t>
+        </is>
+      </c>
+      <c r="F598" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B599" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C599" s="22" t="inlineStr">
+        <is>
+          <t>7126811f</t>
+        </is>
+      </c>
+      <c r="D599" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-2a-context] 품목 관리 editForm/saveItem/dirty를 context로 끌어올림</t>
+        </is>
+      </c>
+      <c r="E599" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F599" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B600" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C600" s="22" t="inlineStr">
+        <is>
+          <t>33da1eaa</t>
+        </is>
+      </c>
+      <c r="D600" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-2b-button] 품목 AdminDetailCard 헤더에 저장 버튼 추가</t>
+        </is>
+      </c>
+      <c r="E600" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F600" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B601" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C601" s="22" t="inlineStr">
+        <is>
+          <t>79c000a6</t>
+        </is>
+      </c>
+      <c r="D601" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3a-hook] Unsaved guard hook + 모달 + admin dirty registry 신설</t>
+        </is>
+      </c>
+      <c r="E601" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F601" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B602" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C602" s="22" t="inlineStr">
+        <is>
+          <t>b3f89e8a</t>
+        </is>
+      </c>
+      <c r="D602" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5a-api] 모델 관리 PUT /api/models/{slot} + catalogApi.updateModel 신설</t>
+        </is>
+      </c>
+      <c r="E602" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F602" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B603" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C603" s="22" t="inlineStr">
+        <is>
+          <t>456964f1</t>
+        </is>
+      </c>
+      <c r="D603" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-6a-sidebar] 관리자 사이드바 설정→보안 탭 변경</t>
+        </is>
+      </c>
+      <c r="E603" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F603" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B604" s="22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C604" s="22" t="inlineStr">
+        <is>
+          <t>e342d8b7</t>
+        </is>
+      </c>
+      <c r="D604" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5a-edit] 모델 관리 인라인 편집 — editForm/dirty/saveModel hook + Provider adminPin 연결</t>
+        </is>
+      </c>
+      <c r="E604" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F604" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B605" s="22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C605" s="22" t="inlineStr">
+        <is>
+          <t>e5b5c176</t>
+        </is>
+      </c>
+      <c r="D605" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-6b-zone-remove] 위험영역 섹션 통째로 제거 + 헤더 업데이트</t>
+        </is>
+      </c>
+      <c r="E605" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F605" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B606" s="22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C606" s="22" t="inlineStr">
+        <is>
+          <t>5bd6be08</t>
+        </is>
+      </c>
+      <c r="D606" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5a-ui] 모델 관리 UI — 인라인 편집 폼 + 저장 버튼 + 목록 row 다듬기</t>
+        </is>
+      </c>
+      <c r="E606" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F606" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B607" s="22" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C607" s="22" t="inlineStr">
+        <is>
+          <t>8f3e0e43</t>
+        </is>
+      </c>
+      <c r="D607" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-6c-hook-cleanup] useAdminSettings 훅에서 resetDatabase/resetPin 제거</t>
+        </is>
+      </c>
+      <c r="E607" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F607" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B608" s="22" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C608" s="22" t="inlineStr">
+        <is>
+          <t>89821d33</t>
+        </is>
+      </c>
+      <c r="D608" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3b-employees] 직원 dirty 감지 + 항목 변경/추가 가드 + registry 등록</t>
+        </is>
+      </c>
+      <c r="E608" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F608" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B609" s="22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C609" s="22" t="inlineStr">
+        <is>
+          <t>6463bcb8</t>
+        </is>
+      </c>
+      <c r="D609" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5b-migration] product_symbols.display_order 컬럼 + slot 백필 마이그레이션</t>
+        </is>
+      </c>
+      <c r="E609" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F609" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B610" s="22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C610" s="22" t="inlineStr">
+        <is>
+          <t>e1f2fff8</t>
+        </is>
+      </c>
+      <c r="D610" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5b-api] PATCH /api/models/reorder 라우터 신설</t>
+        </is>
+      </c>
+      <c r="E610" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F610" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B611" s="22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C611" s="22" t="inlineStr">
+        <is>
+          <t>bd60dcb3</t>
+        </is>
+      </c>
+      <c r="D611" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-5b-frontend] 모델 관리 HTML5 native 드래그 reorder UI</t>
+        </is>
+      </c>
+      <c r="E611" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F611" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B612" s="22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C612" s="22" t="inlineStr">
+        <is>
+          <t>eb4e30e6</t>
+        </is>
+      </c>
+      <c r="D612" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3c-items] 품목 dirty 감지 + 항목 변경/추가 가드 + registry 등록</t>
+        </is>
+      </c>
+      <c r="E612" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F612" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B613" s="22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C613" s="22" t="inlineStr">
+        <is>
+          <t>1835a86a</t>
+        </is>
+      </c>
+      <c r="D613" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3d-departments] 부서 가드 인프라 + 항목 변경 wrap (dirty placeholder)</t>
+        </is>
+      </c>
+      <c r="E613" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F613" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B614" s="22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C614" s="22" t="inlineStr">
+        <is>
+          <t>9dbb8514</t>
+        </is>
+      </c>
+      <c r="D614" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3e-sidebar] AdminSidebar 섹션 변경 가드 (트리거 b)</t>
+        </is>
+      </c>
+      <c r="E614" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F614" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B615" s="22" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C615" s="22" t="inlineStr">
+        <is>
+          <t>dfe2959e</t>
+        </is>
+      </c>
+      <c r="D615" s="23" t="inlineStr">
+        <is>
+          <t>[PR-2.2-3f-shell] 메인 탭 변경 가드 + AdminDirtyProvider 마운트 + typecheck fix</t>
+        </is>
+      </c>
+      <c r="E615" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F615" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B616" s="22" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="C616" s="22" t="inlineStr">
+        <is>
+          <t>e1928e87</t>
+        </is>
+      </c>
+      <c r="D616" s="23" t="inlineStr">
+        <is>
+          <t>merge: PR-2 2-2 품목 저장 버튼 헤더 통일 (B2 worktree)</t>
+        </is>
+      </c>
+      <c r="E616" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F616" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B617" s="22" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C617" s="22" t="inlineStr">
+        <is>
+          <t>0ce8af6d</t>
+        </is>
+      </c>
+      <c r="D617" s="23" t="inlineStr">
+        <is>
+          <t>merge: PR-2 2-5b 모델 드래그 reorder 충돌 해결 (B5a+B5b 통합)</t>
+        </is>
+      </c>
+      <c r="E617" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F617" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B618" s="22" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="C618" s="22" t="inlineStr">
+        <is>
+          <t>ea590514</t>
+        </is>
+      </c>
+      <c r="D618" s="23" t="inlineStr">
+        <is>
+          <t>[fix] EditItemForm useAdminMasterItems import 경로 수정 (../../../ → ../../)</t>
+        </is>
+      </c>
+      <c r="E618" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F618" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B619" s="22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="C619" s="22" t="inlineStr">
+        <is>
+          <t>dc7216ed</t>
+        </is>
+      </c>
+      <c r="D619" s="23" t="inlineStr">
+        <is>
+          <t>merge: PR-2 2-3 unsaved guard 충돌 해결 (B2 context lift 채택)</t>
+        </is>
+      </c>
+      <c r="E619" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F619" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B620" s="22" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="C620" s="22" t="inlineStr">
+        <is>
+          <t>0684577e</t>
+        </is>
+      </c>
+      <c r="D620" s="23" t="inlineStr">
+        <is>
+          <t>[chore] OpenAPI baseline 갱신 (모델 PUT·PATCH reorder 신설 반영)</t>
+        </is>
+      </c>
+      <c r="E620" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F620" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B621" s="22" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="C621" s="22" t="inlineStr">
+        <is>
+          <t>7344cdf3</t>
+        </is>
+      </c>
+      <c r="D621" s="23" t="inlineStr">
+        <is>
+          <t>[review-fix] 모델 DELETE PIN 인증 + AdminModelsSection dirty registry 등록</t>
+        </is>
+      </c>
+      <c r="E621" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F621" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B622" s="22" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="C622" s="22" t="inlineStr">
+        <is>
+          <t>31a61bbb</t>
+        </is>
+      </c>
+      <c r="D622" s="23" t="inlineStr">
+        <is>
+          <t>[W1-A] Pydantic schemas 이동 — routers/models.py → schemas.py</t>
+        </is>
+      </c>
+      <c r="E622" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F622" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B623" s="22" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C623" s="22" t="inlineStr">
+        <is>
+          <t>11c2f211</t>
+        </is>
+      </c>
+      <c r="D623" s="23" t="inlineStr">
+        <is>
+          <t>[W1-4] reorder 로직 일반화 — services/reorder.py 신설</t>
+        </is>
+      </c>
+      <c r="E623" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F623" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B624" s="22" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C624" s="22" t="inlineStr">
+        <is>
+          <t>7c2e9eae</t>
+        </is>
+      </c>
+      <c r="D624" s="23" t="inlineStr">
+        <is>
+          <t>[W2] DirtyGuard 통합 — lib/ui/dirty-guard.tsx 신설</t>
+        </is>
+      </c>
+      <c r="E624" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F624" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B625" s="22" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C625" s="22" t="inlineStr">
+        <is>
+          <t>fe811939</t>
+        </is>
+      </c>
+      <c r="D625" s="23" t="inlineStr">
+        <is>
+          <t>[W3-A] PIN 인증 Depends seam — backend</t>
+        </is>
+      </c>
+      <c r="E625" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F625" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B626" s="22" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C626" s="22" t="inlineStr">
+        <is>
+          <t>426c562b</t>
+        </is>
+      </c>
+      <c r="D626" s="23" t="inlineStr">
+        <is>
+          <t>[W3-B] PIN session — frontend</t>
+        </is>
+      </c>
+      <c r="E626" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F626" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B627" s="22" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="C627" s="22" t="inlineStr">
+        <is>
+          <t>38d3e688</t>
+        </is>
+      </c>
+      <c r="D627" s="23" t="inlineStr">
+        <is>
+          <t>[W4-A] React Query 인프라 + models 도메인 reference</t>
+        </is>
+      </c>
+      <c r="E627" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F627" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B628" s="22" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="C628" s="22" t="inlineStr">
+        <is>
+          <t>10d0576f</t>
+        </is>
+      </c>
+      <c r="D628" s="23" t="inlineStr">
+        <is>
+          <t>[W4-C] MSW 도입 + api-catalog.test.ts 재작성</t>
+        </is>
+      </c>
+      <c r="E628" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F628" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B629" s="22" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="C629" s="22" t="inlineStr">
+        <is>
+          <t>3b555ec1</t>
+        </is>
+      </c>
+      <c r="D629" s="23" t="inlineStr">
+        <is>
+          <t>[W6-hooks] IoComposeView 부분 분해 — useIoUrlSync + useIoPreselect</t>
+        </is>
+      </c>
+      <c r="E629" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F629" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B630" s="22" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C630" s="22" t="inlineStr">
+        <is>
+          <t>9676298f</t>
+        </is>
+      </c>
+      <c r="D630" s="23" t="inlineStr">
+        <is>
+          <t>[W5-emp] Employees hook 3분할 — List/Form/Commands</t>
+        </is>
+      </c>
+      <c r="E630" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F630" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B631" s="22" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C631" s="22" t="inlineStr">
+        <is>
+          <t>8e8d7f4a</t>
+        </is>
+      </c>
+      <c r="D631" s="23" t="inlineStr">
+        <is>
+          <t>[W5-items] MasterItems hook 3분할 — List/Form/Commands</t>
+        </is>
+      </c>
+      <c r="E631" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F631" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B632" s="22" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C632" s="22" t="inlineStr">
+        <is>
+          <t>c25b1bfb</t>
+        </is>
+      </c>
+      <c r="D632" s="23" t="inlineStr">
+        <is>
+          <t>[W5-dept] Departments hook 3분할 — List/Form/Commands</t>
+        </is>
+      </c>
+      <c r="E632" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F632" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B633" s="22" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C633" s="22" t="inlineStr">
+        <is>
+          <t>d637cda5</t>
+        </is>
+      </c>
+      <c r="D633" s="23" t="inlineStr">
+        <is>
+          <t>[W5-models] Models hook 3분할 — List/Form/Commands</t>
+        </is>
+      </c>
+      <c r="E633" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F633" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B634" s="22" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="C634" s="22" t="inlineStr">
+        <is>
+          <t>ca81d2ae</t>
+        </is>
+      </c>
+      <c r="D634" s="23" t="inlineStr">
+        <is>
+          <t>[W7-0] React Query Devtools 제거</t>
+        </is>
+      </c>
+      <c r="E634" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F634" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B635" s="22" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="C635" s="22" t="inlineStr">
+        <is>
+          <t>abd6b554</t>
+        </is>
+      </c>
+      <c r="D635" s="23" t="inlineStr">
+        <is>
+          <t>[W7-4-transactions] React Query: transactions 마이그레이션 + MSW 핸들러</t>
+        </is>
+      </c>
+      <c r="E635" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F635" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B636" s="22" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="C636" s="22" t="inlineStr">
+        <is>
+          <t>823b5e26</t>
+        </is>
+      </c>
+      <c r="D636" s="23" t="inlineStr">
+        <is>
+          <t>[W7-5-bom] React Query: bom 마이그레이션 + MSW 핸들러</t>
+        </is>
+      </c>
+      <c r="E636" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F636" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B637" s="22" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="C637" s="22" t="inlineStr">
+        <is>
+          <t>9b24704e</t>
+        </is>
+      </c>
+      <c r="D637" s="23" t="inlineStr">
+        <is>
+          <t>[W7-6-inventory] React Query: inventory 마이그레이션 + MSW 핸들러</t>
+        </is>
+      </c>
+      <c r="E637" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F637" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B638" s="22" t="inlineStr">
+        <is>
+          <t>23:58</t>
+        </is>
+      </c>
+      <c r="C638" s="22" t="inlineStr">
+        <is>
+          <t>65121ed8</t>
+        </is>
+      </c>
+      <c r="D638" s="23" t="inlineStr">
+        <is>
+          <t>[W7-7-settings] React Query: settings</t>
+        </is>
+      </c>
+      <c r="E638" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F638" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B639" s="22" t="inlineStr">
+        <is>
+          <t>23:58</t>
+        </is>
+      </c>
+      <c r="C639" s="22" t="inlineStr">
+        <is>
+          <t>20a6a19a</t>
+        </is>
+      </c>
+      <c r="D639" s="23" t="inlineStr">
+        <is>
+          <t>[W7-8-stock-requests] React Query: stock-requests</t>
+        </is>
+      </c>
+      <c r="E639" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F639" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B640" s="22" t="inlineStr">
+        <is>
+          <t>23:58</t>
+        </is>
+      </c>
+      <c r="C640" s="22" t="inlineStr">
+        <is>
+          <t>bb71b9a2</t>
+        </is>
+      </c>
+      <c r="D640" s="23" t="inlineStr">
+        <is>
+          <t>[W7-9-production] React Query: production</t>
+        </is>
+      </c>
+      <c r="E640" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F640" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B641" s="22" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="C641" s="22" t="inlineStr">
+        <is>
+          <t>c0169f18</t>
+        </is>
+      </c>
+      <c r="D641" s="23" t="inlineStr">
+        <is>
+          <t>[W7-10-admin] React Query: admin</t>
+        </is>
+      </c>
+      <c r="E641" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F641" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B642" s="22" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="C642" s="22" t="inlineStr">
+        <is>
+          <t>fd98fa4f</t>
+        </is>
+      </c>
+      <c r="D642" s="23" t="inlineStr">
+        <is>
+          <t>[W7-2-employees] React Query: employees</t>
+        </is>
+      </c>
+      <c r="E642" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F642" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B643" s="22" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="C643" s="22" t="inlineStr">
+        <is>
+          <t>37688c39</t>
+        </is>
+      </c>
+      <c r="D643" s="23" t="inlineStr">
+        <is>
+          <t>[W7-3-items] React Query: items</t>
+        </is>
+      </c>
+      <c r="E643" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F643" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B644" s="22" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C644" s="22" t="inlineStr">
+        <is>
+          <t>a207f78d</t>
+        </is>
+      </c>
+      <c r="D644" s="23" t="inlineStr">
+        <is>
+          <t>[W9-C] employees.reset_employee_pin PIN seam 통합</t>
+        </is>
+      </c>
+      <c r="E644" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F644" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B645" s="22" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C645" s="22" t="inlineStr">
+        <is>
+          <t>7901ec6a</t>
+        </is>
+      </c>
+      <c r="D645" s="23" t="inlineStr">
+        <is>
+          <t>[W9-B] models.py 705줄 -&gt; 도메인별 models/ 패키지 분리</t>
+        </is>
+      </c>
+      <c r="E645" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F645" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B646" s="22" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="C646" s="22" t="inlineStr">
+        <is>
+          <t>295db1f3</t>
+        </is>
+      </c>
+      <c r="D646" s="23" t="inlineStr">
+        <is>
+          <t>[W9-A] /api/transactions/monthly-counts endpoint 신규</t>
+        </is>
+      </c>
+      <c r="E646" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F646" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B647" s="22" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C647" s="22" t="inlineStr">
+        <is>
+          <t>c9bff6e1</t>
+        </is>
+      </c>
+      <c r="D647" s="23" t="inlineStr">
+        <is>
+          <t>merge: arch-post-demo into main (W3-W7+W9, 22 commits)</t>
+        </is>
+      </c>
+      <c r="E647" s="22" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="F647" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B648" s="22" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="C648" s="22" t="inlineStr">
+        <is>
+          <t>a4deb9ec</t>
+        </is>
+      </c>
+      <c r="D648" s="23" t="inlineStr">
+        <is>
+          <t>[W10-D] bootstrap_db.py 865줄 → bootstrap/ 패키지 분리</t>
+        </is>
+      </c>
+      <c r="E648" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F648" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B649" s="22" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="C649" s="22" t="inlineStr">
+        <is>
+          <t>78bd73ab</t>
+        </is>
+      </c>
+      <c r="D649" s="23" t="inlineStr">
+        <is>
+          <t>[W11-A] Department.io_enabled 필드 + 라우터 + 마이그레이션</t>
+        </is>
+      </c>
+      <c r="E649" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F649" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B650" s="22" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="C650" s="22" t="inlineStr">
+        <is>
+          <t>a5665f36</t>
+        </is>
+      </c>
+      <c r="D650" s="23" t="inlineStr">
+        <is>
+          <t>[W11-B+C] 부서별 입출고 권한 토글 — 프론트엔드</t>
+        </is>
+      </c>
+      <c r="E650" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F650" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B651" s="22" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="C651" s="22" t="inlineStr">
+        <is>
+          <t>c00b662b</t>
+        </is>
+      </c>
+      <c r="D651" s="23" t="inlineStr">
+        <is>
+          <t>[W12-C] .gitignore: 시연 검증용 패턴 추가</t>
+        </is>
+      </c>
+      <c r="E651" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F651" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B652" s="22" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C652" s="22" t="inlineStr">
+        <is>
+          <t>bd8f687e</t>
+        </is>
+      </c>
+      <c r="D652" s="23" t="inlineStr">
+        <is>
+          <t>[W12-A] 시연 데이터 freeze: 진공/고압 격리(DEFECTIVE) 재고 생성 + audit_csv 갱신</t>
+        </is>
+      </c>
+      <c r="E652" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F652" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B653" s="22" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="C653" s="22" t="inlineStr">
+        <is>
+          <t>f7d2ca4e</t>
+        </is>
+      </c>
+      <c r="D653" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3] 시연 D-5 리허설 14건 묶음 fix (12/14 완료 — #2/#7 시연 후 보류)</t>
+        </is>
+      </c>
+      <c r="E653" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F653" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B654" s="22" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C654" s="22" t="inlineStr">
+        <is>
+          <t>aeb47844</t>
+        </is>
+      </c>
+      <c r="D654" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3-followup] BOM 펼침 회귀 fix — 옛 입출고 자식 라인 응답 fallback</t>
+        </is>
+      </c>
+      <c r="E654" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F654" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B655" s="22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C655" s="22" t="inlineStr">
+        <is>
+          <t>13c124d9</t>
+        </is>
+      </c>
+      <c r="D655" s="23" t="inlineStr">
+        <is>
+          <t>[demo #2-BE] 품목 reorder API — PATCH /api/items/reorder (모델 패턴 복제)</t>
+        </is>
+      </c>
+      <c r="E655" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F655" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B656" s="22" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C656" s="22" t="inlineStr">
+        <is>
+          <t>2ba4829b</t>
+        </is>
+      </c>
+      <c r="D656" s="23" t="inlineStr">
+        <is>
+          <t>[demo #2-FE] 품목 드래그 reorder UI — 모델 reorder 패턴 복제</t>
+        </is>
+      </c>
+      <c r="E656" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F656" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B657" s="22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="C657" s="22" t="inlineStr">
+        <is>
+          <t>b629ce0d</t>
+        </is>
+      </c>
+      <c r="D657" s="23" t="inlineStr">
+        <is>
+          <t>[W12-#7-A] 직원별 입출고 권한 io_enabled — 백엔드 모델·마이그레이션·CRUD·테스트</t>
+        </is>
+      </c>
+      <c r="E657" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F657" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B658" s="22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="C658" s="22" t="inlineStr">
+        <is>
+          <t>7cf7adc3</t>
+        </is>
+      </c>
+      <c r="D658" s="23" t="inlineStr">
+        <is>
+          <t>[W12-#7-B] 직원별 입출고 권한 io_enabled — 프론트엔드 UI·가드</t>
+        </is>
+      </c>
+      <c r="E658" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F658" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B659" s="22" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C659" s="22" t="inlineStr">
+        <is>
+          <t>af54e31b</t>
+        </is>
+      </c>
+      <c r="D659" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3-#2] 품목 reorder 신규 — 백엔드 reorder 서비스 일반화 + 프론트 드래그 UI</t>
+        </is>
+      </c>
+      <c r="E659" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F659" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B660" s="22" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C660" s="22" t="inlineStr">
+        <is>
+          <t>900477fd</t>
+        </is>
+      </c>
+      <c r="D660" s="23" t="inlineStr">
+        <is>
+          <t>[PR-3-#7] 직원 io_enabled 신규 — 부서 AND 직원 결합 입출고 권한</t>
+        </is>
+      </c>
+      <c r="E660" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F660" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B661" s="22" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C661" s="22" t="inlineStr">
+        <is>
+          <t>66f82950</t>
+        </is>
+      </c>
+      <c r="D661" s="23" t="inlineStr">
+        <is>
+          <t>[ux] 로그인 콤보박스 꺽쇄 클릭 + 토픽바 로그아웃 여백</t>
+        </is>
+      </c>
+      <c r="E661" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F661" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B662" s="22" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C662" s="22" t="inlineStr">
+        <is>
+          <t>f5bb354e</t>
+        </is>
+      </c>
+      <c r="D662" s="23" t="inlineStr">
+        <is>
+          <t>[history] 입출고 내역 BOM 가독성 개선 + 우측 패널 열림 시 컴팩트 모드</t>
+        </is>
+      </c>
+      <c r="E662" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F662" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B663" s="22" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="C663" s="22" t="inlineStr">
+        <is>
+          <t>4cc8e1c6</t>
+        </is>
+      </c>
+      <c r="D663" s="23" t="inlineStr">
+        <is>
+          <t>[defect] 불량 처리 5종 알약 라벨·색 통일 (전부 빨강 + 아이콘으로 구분)</t>
+        </is>
+      </c>
+      <c r="E663" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F663" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B664" s="22" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="C664" s="22" t="inlineStr">
+        <is>
+          <t>5b606e2f</t>
+        </is>
+      </c>
+      <c r="D664" s="23" t="inlineStr">
+        <is>
+          <t>[weekly] 주간보고 — 달력 주 단위 클릭·카드 컴팩트·생산표 열 고정 + 화면 동결</t>
+        </is>
+      </c>
+      <c r="E664" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F664" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B665" s="22" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C665" s="22" t="inlineStr">
+        <is>
+          <t>06393f8e</t>
+        </is>
+      </c>
+      <c r="D665" s="23" t="inlineStr">
+        <is>
+          <t>[weekly] 공정별 변화 하단 행 grid-cols-3 — 출고가 카드 간 같은 x 에 정렬</t>
+        </is>
+      </c>
+      <c r="E665" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F665" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B666" s="22" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C666" s="22" t="inlineStr">
+        <is>
+          <t>f9a83bc2</t>
+        </is>
+      </c>
+      <c r="D666" s="23" t="inlineStr">
+        <is>
+          <t>[ux] 사이드바·테마토글 비활성 아이콘 배경 transparent</t>
+        </is>
+      </c>
+      <c r="E666" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F666" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B667" s="22" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C667" s="22" t="inlineStr">
+        <is>
+          <t>2fb9bf87</t>
+        </is>
+      </c>
+      <c r="D667" s="23" t="inlineStr">
+        <is>
+          <t>[chore] audit CSV — 2026-05-24 입출고 거래 9건 추가</t>
+        </is>
+      </c>
+      <c r="E667" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F667" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B668" s="22" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="C668" s="22" t="inlineStr">
+        <is>
+          <t>755f100c</t>
+        </is>
+      </c>
+      <c r="D668" s="23" t="inlineStr">
+        <is>
+          <t>[defect][io] 불량 처리·입출고 흐름 종합 개편</t>
+        </is>
+      </c>
+      <c r="E668" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F668" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B669" s="22" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="C669" s="22" t="inlineStr">
+        <is>
+          <t>ccf26079</t>
+        </is>
+      </c>
+      <c r="D669" s="23" t="inlineStr">
+        <is>
+          <t>[chore] audit CSV — 2026-05 거래 누적 반영</t>
+        </is>
+      </c>
+      <c r="E669" s="22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F669" s="24" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B670" s="18" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C670" s="18" t="inlineStr">
+        <is>
+          <t>4f5c3c68</t>
+        </is>
+      </c>
+      <c r="D670" s="19" t="inlineStr">
+        <is>
+          <t>[defect][chore] B/C 체크리스트 마무리 — historyBatchInterpreter defect 버그 수정</t>
+        </is>
+      </c>
+      <c r="E670" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F670" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B671" s="9" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C671" s="9" t="inlineStr">
+        <is>
+          <t>de6317a1</t>
+        </is>
+      </c>
+      <c r="D671" s="10" t="inlineStr">
+        <is>
+          <t>[capacity] 합계 → 모델별 대표 PF 5종 표시로 재설계</t>
+        </is>
+      </c>
+      <c r="E671" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F671" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B672" s="18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C672" s="18" t="inlineStr">
+        <is>
+          <t>b32b6ed5</t>
+        </is>
+      </c>
+      <c r="D672" s="19" t="inlineStr">
+        <is>
+          <t>[admin][item] 품목 소프트 삭제/복구 기능 + 관련 UI 개선</t>
+        </is>
+      </c>
+      <c r="E672" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F672" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B673" s="9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C673" s="9" t="inlineStr">
+        <is>
+          <t>e41815ea</t>
+        </is>
+      </c>
+      <c r="D673" s="10" t="inlineStr">
+        <is>
+          <t>[defect][io] 불량 처리 수량 입력 기능 — 누락 파일 추가</t>
+        </is>
+      </c>
+      <c r="E673" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F673" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B674" s="18" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C674" s="18" t="inlineStr">
+        <is>
+          <t>0eba9ef3</t>
+        </is>
+      </c>
+      <c r="D674" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-26 fix(items): 시리얼 부여 (process_type 단위)·DB 코드 복원·권동환/김건호 엑셀 정합화</t>
+        </is>
+      </c>
+      <c r="E674" s="18" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F674" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B675" s="9" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C675" s="9" t="inlineStr">
+        <is>
+          <t>bb349149</t>
+        </is>
+      </c>
+      <c r="D675" s="10" t="inlineStr">
+        <is>
+          <t>docs: 발표 슬라이드 카운터 / 13 → / 14</t>
+        </is>
+      </c>
+      <c r="E675" s="9" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F675" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B676" s="18" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C676" s="18" t="inlineStr">
+        <is>
+          <t>237cfa75</t>
+        </is>
+      </c>
+      <c r="D676" s="19" t="inlineStr">
+        <is>
+          <t>data: 권동환 5월 재고 확정파일 — 김건호 과장님 확인 반영</t>
+        </is>
+      </c>
+      <c r="E676" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F676" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B677" s="9" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C677" s="9" t="inlineStr">
+        <is>
+          <t>cdcecf99</t>
+        </is>
+      </c>
+      <c r="D677" s="10" t="inlineStr">
+        <is>
+          <t>chore: BOM 깊이 / PF 모델 분포 진단 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="E677" s="9" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F677" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B678" s="18" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C678" s="18" t="inlineStr">
+        <is>
+          <t>fa38c3ad</t>
+        </is>
+      </c>
+      <c r="D678" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-26 docs: CLAUDE.md에 커밋 메시지 형식 규칙 명시</t>
+        </is>
+      </c>
+      <c r="E678" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F678" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B679" s="9" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C679" s="9" t="inlineStr">
+        <is>
+          <t>daf335b4</t>
+        </is>
+      </c>
+      <c r="D679" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 1 — 피드백 11건 반영</t>
+        </is>
+      </c>
+      <c r="E679" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F679" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B680" s="18" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C680" s="18" t="inlineStr">
+        <is>
+          <t>2589f6df</t>
+        </is>
+      </c>
+      <c r="D680" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 2 — 단일 화면 로직 버그 3건</t>
+        </is>
+      </c>
+      <c r="E680" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F680" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B681" s="9" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C681" s="9" t="inlineStr">
+        <is>
+          <t>e80ce354</t>
+        </is>
+      </c>
+      <c r="D681" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 3 — 모달 드래그 닫힘 버그 fix (2번)</t>
+        </is>
+      </c>
+      <c r="E681" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F681" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B682" s="18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="C682" s="18" t="inlineStr">
+        <is>
+          <t>ff548428</t>
+        </is>
+      </c>
+      <c r="D682" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 3 v2 — 모달 드래그 닫힘 양방향 차단 보강</t>
+        </is>
+      </c>
+      <c r="E682" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F682" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B683" s="9" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="C683" s="9" t="inlineStr">
+        <is>
+          <t>e5849f18</t>
+        </is>
+      </c>
+      <c r="D683" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 3 v3 — 모달 backdrop 클릭 닫힘 자체 제거 (2번 의도 재해석)</t>
+        </is>
+      </c>
+      <c r="E683" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F683" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B684" s="18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C684" s="18" t="inlineStr">
+        <is>
+          <t>47683730</t>
+        </is>
+      </c>
+      <c r="D684" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 4 — Toast 일관화 + 에러 메시지 매핑 (3, 15-1, 19-1)</t>
+        </is>
+      </c>
+      <c r="E684" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F684" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B685" s="9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="C685" s="9" t="inlineStr">
+        <is>
+          <t>83c88ec6</t>
+        </is>
+      </c>
+      <c r="D685" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 4 후속 — PIN 변경 성공 안내 Toast → ResultModal</t>
+        </is>
+      </c>
+      <c r="E685" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F685" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B686" s="18" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C686" s="18" t="inlineStr">
+        <is>
+          <t>975a18e3</t>
+        </is>
+      </c>
+      <c r="D686" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 6 — 자동 카트 가드 키 확장 (8-2번 버그 fix)</t>
+        </is>
+      </c>
+      <c r="E686" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F686" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B687" s="9" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C687" s="9" t="inlineStr">
+        <is>
+          <t>c4f0de4e</t>
+        </is>
+      </c>
+      <c r="D687" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 backend: 품목 추가 시 (이름, 카테고리) 중복 사전 체크 (16-2번)</t>
+        </is>
+      </c>
+      <c r="E687" s="9" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F687" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B688" s="18" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C688" s="18" t="inlineStr">
+        <is>
+          <t>a64c7569</t>
+        </is>
+      </c>
+      <c r="D688" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 7 — 직원 선택 가나다순 정렬 (1번)</t>
+        </is>
+      </c>
+      <c r="E688" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F688" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B689" s="9" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="C689" s="9" t="inlineStr">
+        <is>
+          <t>13839645</t>
+        </is>
+      </c>
+      <c r="D689" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 8 — 이미지 라이트박스 + 상세 패널 이미지 슬롯 (7-1, 7-2)</t>
+        </is>
+      </c>
+      <c r="E689" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F689" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B690" s="18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="C690" s="18" t="inlineStr">
+        <is>
+          <t>a098ad82</t>
+        </is>
+      </c>
+      <c r="D690" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 9 — 입출고 작업 중 화면 이동 시 저장 확인 모달 (9번)</t>
+        </is>
+      </c>
+      <c r="E690" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F690" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B691" s="9" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="C691" s="9" t="inlineStr">
+        <is>
+          <t>6581f93a</t>
+        </is>
+      </c>
+      <c r="D691" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 10 — 다른 날짜 거래 클릭 시 필터 이동 + 스크롤 (13-2)</t>
+        </is>
+      </c>
+      <c r="E691" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F691" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B692" s="18" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="C692" s="18" t="inlineStr">
+        <is>
+          <t>0b8717f1</t>
+        </is>
+      </c>
+      <c r="D692" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: Step 11 — 대시보드/내역 필터 UX 통일 (5, 12번)</t>
+        </is>
+      </c>
+      <c r="E692" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F692" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B693" s="9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C693" s="9" t="inlineStr">
+        <is>
+          <t>370e1111</t>
+        </is>
+      </c>
+      <c r="D693" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: 저장하지 않고 이동 시 자동 저장 draft 도 폐기</t>
+        </is>
+      </c>
+      <c r="E693" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F693" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B694" s="18" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C694" s="18" t="inlineStr">
+        <is>
+          <t>00aa968d</t>
+        </is>
+      </c>
+      <c r="D694" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: 부서 색상 DB ↔ 프론트 fallback 정합화</t>
+        </is>
+      </c>
+      <c r="E694" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F694" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B695" s="9" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C695" s="9" t="inlineStr">
+        <is>
+          <t>ba3b998d</t>
+        </is>
+      </c>
+      <c r="D695" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: input inputMode·iOS 자동줌 방지·TYPO.caption 본문 격상</t>
+        </is>
+      </c>
+      <c r="E695" s="9" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F695" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B696" s="18" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C696" s="18" t="inlineStr">
+        <is>
+          <t>9a0c79c5</t>
+        </is>
+      </c>
+      <c r="D696" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: 사용자 메뉴 시트·토스트 큐 추가, URL defect_dept 동기화</t>
+        </is>
+      </c>
+      <c r="E696" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F696" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B697" s="9" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C697" s="9" t="inlineStr">
+        <is>
+          <t>0cdcc81a</t>
+        </is>
+      </c>
+      <c r="D697" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: primitives 44px hit area·접근성·safe-area·위계 일괄 정합화</t>
+        </is>
+      </c>
+      <c r="E697" s="9" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F697" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B698" s="18" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C698" s="18" t="inlineStr">
+        <is>
+          <t>bea17ba9</t>
+        </is>
+      </c>
+      <c r="D698" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: 입출고 Step 5 에 [저장하기] 버튼 추가 — 제출 옆 보조 액션</t>
+        </is>
+      </c>
+      <c r="E698" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F698" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B699" s="9" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C699" s="9" t="inlineStr">
+        <is>
+          <t>c8b79d48</t>
+        </is>
+      </c>
+      <c r="D699" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 defect: 불량 용어 통일 + DisassembleTree 토글 UX + 부분 수량 처리</t>
+        </is>
+      </c>
+      <c r="E699" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F699" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B700" s="18" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C700" s="18" t="inlineStr">
+        <is>
+          <t>8e7d54d6</t>
+        </is>
+      </c>
+      <c r="D700" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: defect_dept prop pass-through·위저드 헤더 fixed 전환</t>
+        </is>
+      </c>
+      <c r="E700" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F700" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B701" s="9" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C701" s="9" t="inlineStr">
+        <is>
+          <t>79d94b94</t>
+        </is>
+      </c>
+      <c r="D701" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: history 뒤로 버튼·로딩 스피너·스켈레톤·위계 정리</t>
+        </is>
+      </c>
+      <c r="E701" s="9" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F701" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B702" s="18" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C702" s="18" t="inlineStr">
+        <is>
+          <t>904726ef</t>
+        </is>
+      </c>
+      <c r="D702" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: 관리자 잠금 + 메시지 대비 토큰 + 토글 색 일관</t>
+        </is>
+      </c>
+      <c r="E702" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F702" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B703" s="9" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C703" s="9" t="inlineStr">
+        <is>
+          <t>f7983c52</t>
+        </is>
+      </c>
+      <c r="D703" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 docs: 모바일 개선 plan·감사·실행·디자인 시스템 문서 4개</t>
+        </is>
+      </c>
+      <c r="E703" s="9" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F703" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B704" s="18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C704" s="18" t="inlineStr">
+        <is>
+          <t>5ca446bc</t>
+        </is>
+      </c>
+      <c r="D704" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: W3 머지 — 관리자 잠금 + 메시지 대비 토큰</t>
+        </is>
+      </c>
+      <c r="E704" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F704" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B705" s="9" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C705" s="9" t="inlineStr">
+        <is>
+          <t>280388f1</t>
+        </is>
+      </c>
+      <c r="D705" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: W4 머지 — primitives 44px hit area·접근성·위계</t>
+        </is>
+      </c>
+      <c r="E705" s="9" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F705" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B706" s="18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C706" s="18" t="inlineStr">
+        <is>
+          <t>1076399b</t>
+        </is>
+      </c>
+      <c r="D706" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: W5 머지 — history 뒤로·로딩·스켈레톤·위계</t>
+        </is>
+      </c>
+      <c r="E706" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F706" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B707" s="9" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C707" s="9" t="inlineStr">
+        <is>
+          <t>a44b70e6</t>
+        </is>
+      </c>
+      <c r="D707" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: W2 머지 — defect prop pass-through·sticky→fixed</t>
+        </is>
+      </c>
+      <c r="E707" s="9" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F707" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B708" s="18" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="C708" s="18" t="inlineStr">
+        <is>
+          <t>61180af5</t>
+        </is>
+      </c>
+      <c r="D708" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 mobile: W1 머지 — 사용자 메뉴 시트·토스트 큐</t>
+        </is>
+      </c>
+      <c r="E708" s="18" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F708" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B709" s="9" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="C709" s="9" t="inlineStr">
+        <is>
+          <t>165a98ac</t>
+        </is>
+      </c>
+      <c r="D709" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 ux: BOM 워크벤치 KPI/헤더 레이아웃 통일 (18-1)</t>
+        </is>
+      </c>
+      <c r="E709" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F709" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B710" s="18" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C710" s="18" t="inlineStr">
+        <is>
+          <t>3ffa3989</t>
+        </is>
+      </c>
+      <c r="D710" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 backend: dept_hierarchy·stock_requests 정비 + 테스트 동기화</t>
+        </is>
+      </c>
+      <c r="E710" s="18" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F710" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B711" s="9" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C711" s="9" t="inlineStr">
+        <is>
+          <t>e1e2c0f0</t>
+        </is>
+      </c>
+      <c r="D711" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 data: audit CSV — 5월 입출고 거래 누적 반영</t>
+        </is>
+      </c>
+      <c r="E711" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F711" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B712" s="18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C712" s="18" t="inlineStr">
+        <is>
+          <t>50cc3d97</t>
+        </is>
+      </c>
+      <c r="D712" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 chore: gitignore — post-merge-*.png 임시 스크린샷 패턴 추가</t>
+        </is>
+      </c>
+      <c r="E712" s="18" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F712" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B713" s="9" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="C713" s="9" t="inlineStr">
+        <is>
+          <t>73aef6f9</t>
+        </is>
+      </c>
+      <c r="D713" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21 desktop: BOM 부모 헤더 카드 보더에 부서 컬러 살짝 액센트</t>
+        </is>
+      </c>
+      <c r="E713" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F713" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B714" s="18" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C714" s="18" t="inlineStr">
+        <is>
+          <t>ced1036e</t>
+        </is>
+      </c>
+      <c r="D714" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-27 backend: 입출고·불량·부서조정·재고요청·마이그레이션 갱신</t>
+        </is>
+      </c>
+      <c r="E714" s="18" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F714" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B715" s="9" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C715" s="9" t="inlineStr">
+        <is>
+          <t>98908593</t>
+        </is>
+      </c>
+      <c r="D715" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-27 desktop: 재고 화면 + 필터바 갱신</t>
+        </is>
+      </c>
+      <c r="E715" s="9" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F715" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B716" s="18" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C716" s="18" t="inlineStr">
+        <is>
+          <t>4f927587</t>
+        </is>
+      </c>
+      <c r="D716" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-28 docs: 발표 후속 자료 — 슬라이드 보완 + 피드백 양식 + 컨닝페이퍼</t>
+        </is>
+      </c>
+      <c r="E716" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F716" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B717" s="9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C717" s="9" t="inlineStr">
+        <is>
+          <t>f5a53eb4</t>
+        </is>
+      </c>
+      <c r="D717" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28 defect: 불량 자동결재·재작업 트리뷰·UI 문구 정리·요청자/승인자 버그</t>
+        </is>
+      </c>
+      <c r="E717" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F717" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B718" s="18" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C718" s="18" t="inlineStr">
+        <is>
+          <t>6c84e1a9</t>
+        </is>
+      </c>
+      <c r="D718" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-28 docs: CLAUDE.md — 커밋 메시지 날짜는 실제 시점(date 명령)으로 확인 규칙 추가</t>
+        </is>
+      </c>
+      <c r="E718" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F718" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B719" s="9" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C719" s="9" t="inlineStr">
+        <is>
+          <t>ba0cd992</t>
+        </is>
+      </c>
+      <c r="D719" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29 weekly: 매트릭스 거래타입 분류 상수화·enum 누락 방어·백엔드 동결</t>
+        </is>
+      </c>
+      <c r="E719" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F719" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B720" s="18" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="C720" s="18" t="inlineStr">
+        <is>
+          <t>f01a0d78</t>
+        </is>
+      </c>
+      <c r="D720" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-29 frontend: 입출고 내역 재작업 우측 패널 title + 불량 BOM 펼침 버튼</t>
+        </is>
+      </c>
+      <c r="E720" s="18" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F720" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B721" s="9" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="C721" s="9" t="inlineStr">
+        <is>
+          <t>d3153887</t>
+        </is>
+      </c>
+      <c r="D721" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29 docs: 피드백 모음 폴더 신설 (허동현·김건호·김민재)</t>
+        </is>
+      </c>
+      <c r="E721" s="9" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F721" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B722" s="18" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C722" s="18" t="inlineStr">
+        <is>
+          <t>2850d27c</t>
+        </is>
+      </c>
+      <c r="D722" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-29 docs: 주간보고 5/23~5/28 메일 + 변환 스크립트 + 양식 규칙</t>
+        </is>
+      </c>
+      <c r="E722" s="18" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F722" s="18" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B723" s="9" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C723" s="9" t="inlineStr">
+        <is>
+          <t>eed246ab</t>
+        </is>
+      </c>
+      <c r="D723" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-29 feedback: 허동현 4건 추가 (사진정책·담당자검증·소수점·PIN자리수)</t>
+        </is>
+      </c>
+      <c r="E723" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F723" s="9" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>740건 (회사 기간 660건)</t>
+          <t>831건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>276건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>304건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -1767,20 +1767,122 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■■■■■■■■■■</t>
+            <t>■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (23)</t>
+            <t xml:space="preserve">  (33)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-01  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (14)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-02  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (51)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-04  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (16)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="50">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -1790,6 +1892,7 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
@@ -1806,6 +1909,7 @@
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A33:E33"/>
@@ -1821,6 +1925,7 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
@@ -2119,7 +2224,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -4264,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5200,7 +5305,7 @@
         </is>
       </c>
       <c r="B40" s="15" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
@@ -5212,6 +5317,78 @@
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="67.5" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 생산·분해 시 BOM 부품을 소속 공정에서 차감 — 타공정 부품 조정 허
+2026-06-01 docs: 기준정보 문서 정합 — 변동수치 제거·유령칸 정리 + facts.py
+2026-06-01 backend: item_code → mes_code 전면 리네임 (DB·스키마·Open
+2026-06-01 frontend: item_code → mes_code 리네임 (백엔드 API 키 loc
+2026-06-01 chore: 활성 ops/dev 스크립트 item_code → mes_code 동기</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="67.5" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 수량 정수화 후속 — 삭제된 보정함수 가리키던 죽은 주석 정리
+2026-06-02 backend: 수량 정수 통일 — 알루미늄 소수 올림 + 선언타입 INTEGER 정합
+2026-06-02 backend: UUID 포맷 혼재 재발 방지 — UUIDString TypeDecora
+2026-06-02 backend: mes_code 생성열 진실소스화 + 모델 마스터 단일화
+2026-06-02 docs: CLAUDE.md 전면 영문화 + 플랜모드 모델 추천 규칙 추가</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="67.5" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 chore: @playwright/test devDep 추가 + handoff·works
+2026-06-04 frontend: 피드백 4건 — BOM 박스 클릭·휴지통·반려 폴링·하위 BOM 트리
+2026-06-04 docs: 남재원·이필욱 피드백 파일 신규 추가
+2026-06-04 test: e2e 전용DB globalSetup + 로그인우회 + 쓰기 4 spec 그린
+2026-06-04 docs: §10 e2e 인프라 발견 → 해소 기록</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -5228,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F741"/>
+  <dimension ref="A1:F832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28951,6 +29128,2918 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B742" s="15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C742" s="15" t="inlineStr">
+        <is>
+          <t>1f141ef2</t>
+        </is>
+      </c>
+      <c r="D742" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-29 docs: 주간보고·개발현황 5/29 갱신 + xlsx 셀 병합 충돌 수정</t>
+        </is>
+      </c>
+      <c r="E742" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F742" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B743" s="7" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C743" s="7" t="inlineStr">
+        <is>
+          <t>b4c4a2f0</t>
+        </is>
+      </c>
+      <c r="D743" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-29 refactor: 머지 — 코드베이스 아키텍처 개선 (P0-1 라벨 단일 사전·P0-2 출하 규칙·P1-1~3·P1-6·P2-1 E2E 스캐폴딩·P3-1 접근성)</t>
+        </is>
+      </c>
+      <c r="E743" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F743" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B744" s="15" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C744" s="15" t="inlineStr">
+        <is>
+          <t>42c53eb7</t>
+        </is>
+      </c>
+      <c r="D744" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-29 db: M1 잔재 3종 제거 — variance_logs / process_flow_rules / items.symbol_slot</t>
+        </is>
+      </c>
+      <c r="E744" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F744" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B745" s="7" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C745" s="7" t="inlineStr">
+        <is>
+          <t>8dd5c9a9</t>
+        </is>
+      </c>
+      <c r="D745" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-29 chore: 루트 정리 — vault·mes.db 제거, docs·ONBOARDING → _attic</t>
+        </is>
+      </c>
+      <c r="E745" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F745" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B746" s="15" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C746" s="15" t="inlineStr">
+        <is>
+          <t>b4b1cf16</t>
+        </is>
+      </c>
+      <c r="D746" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-29 chore: backend 1회성 스크립트 _attic 이전 + sys.path 패치</t>
+        </is>
+      </c>
+      <c r="E746" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F746" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B747" s="7" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="C747" s="7" t="inlineStr">
+        <is>
+          <t>787cd977</t>
+        </is>
+      </c>
+      <c r="D747" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-29 docs: 정리 후 위치 갱신 — CLAUDE·README·ATTIC_POLICY + backend-scripts/README 신설</t>
+        </is>
+      </c>
+      <c r="E747" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F747" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B748" s="15" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C748" s="15" t="inlineStr">
+        <is>
+          <t>15afaa09</t>
+        </is>
+      </c>
+      <c r="D748" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-29 chore: _scratch_dead_scan.py → _attic/scripts/</t>
+        </is>
+      </c>
+      <c r="E748" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F748" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B749" s="7" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C749" s="7" t="inlineStr">
+        <is>
+          <t>6654e21e</t>
+        </is>
+      </c>
+      <c r="D749" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-29 docs: 세션 인수인계 파일 신설 + CLAUDE.md 안내</t>
+        </is>
+      </c>
+      <c r="E749" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F749" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B750" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C750" s="19" t="inlineStr">
+        <is>
+          <t>b4b1ac33</t>
+        </is>
+      </c>
+      <c r="D750" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-29 chore: 머지 — 강제 위치 없는 자료 _attic 통합 (루트·backend 정리 + 안전망 + 인수인계)</t>
+        </is>
+      </c>
+      <c r="E750" s="19" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F750" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B751" s="19" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C751" s="19" t="inlineStr">
+        <is>
+          <t>e81809b5</t>
+        </is>
+      </c>
+      <c r="D751" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-29 db: OptionCode 마스터·items.option_code 폐기 — 옵션 분류 미사용 확정</t>
+        </is>
+      </c>
+      <c r="E751" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F751" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B752" s="15" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="C752" s="15" t="inlineStr">
+        <is>
+          <t>26384c28</t>
+        </is>
+      </c>
+      <c r="D752" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 생산·분해 시 BOM 부품을 소속 공정에서 차감 — 타공정 부품 조정 허용</t>
+        </is>
+      </c>
+      <c r="E752" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F752" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B753" s="7" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C753" s="7" t="inlineStr">
+        <is>
+          <t>b0b47235</t>
+        </is>
+      </c>
+      <c r="D753" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 docs: 기준정보 문서 정합 — 변동수치 제거·유령칸 정리 + facts.py</t>
+        </is>
+      </c>
+      <c r="E753" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F753" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B754" s="15" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C754" s="15" t="inlineStr">
+        <is>
+          <t>658b2515</t>
+        </is>
+      </c>
+      <c r="D754" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: item_code → mes_code 전면 리네임 (DB·스키마·OpenAPI)</t>
+        </is>
+      </c>
+      <c r="E754" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F754" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B755" s="7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C755" s="7" t="inlineStr">
+        <is>
+          <t>30525682</t>
+        </is>
+      </c>
+      <c r="D755" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 frontend: item_code → mes_code 리네임 (백엔드 API 키 lockstep)</t>
+        </is>
+      </c>
+      <c r="E755" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F755" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B756" s="15" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C756" s="15" t="inlineStr">
+        <is>
+          <t>8562061b</t>
+        </is>
+      </c>
+      <c r="D756" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 chore: 활성 ops/dev 스크립트 item_code → mes_code 동기</t>
+        </is>
+      </c>
+      <c r="E756" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F756" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B757" s="7" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C757" s="7" t="inlineStr">
+        <is>
+          <t>04261bb0</t>
+        </is>
+      </c>
+      <c r="D757" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 docs: 주간보고 5/30~6/5 시작 (직원 응대·기준정보 체계)</t>
+        </is>
+      </c>
+      <c r="E757" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F757" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B758" s="15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C758" s="15" t="inlineStr">
+        <is>
+          <t>da8b8d19</t>
+        </is>
+      </c>
+      <c r="D758" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 docs: 기준정보 문서 정합 — 유령칸·죽은경로·변동수치 정리 + mes_code 반영</t>
+        </is>
+      </c>
+      <c r="E758" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F758" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B759" s="7" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="C759" s="7" t="inlineStr">
+        <is>
+          <t>8d7a0982</t>
+        </is>
+      </c>
+      <c r="D759" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 수량 정수 전용 강제 — 소수 입력 422 거부·정수 직렬화</t>
+        </is>
+      </c>
+      <c r="E759" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F759" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B760" s="15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C760" s="15" t="inlineStr">
+        <is>
+          <t>0cc58c2b</t>
+        </is>
+      </c>
+      <c r="D760" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 수량 내부 정수화 — DB 컬럼 Numeric→IntQuantity</t>
+        </is>
+      </c>
+      <c r="E760" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F760" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B761" s="7" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="C761" s="7" t="inlineStr">
+        <is>
+          <t>8c85f148</t>
+        </is>
+      </c>
+      <c r="D761" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 docs: 피드백 6건 정리 — 허동현 3·김현우 2·권동환 1</t>
+        </is>
+      </c>
+      <c r="E761" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F761" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B762" s="15" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C762" s="15" t="inlineStr">
+        <is>
+          <t>52cdb55d</t>
+        </is>
+      </c>
+      <c r="D762" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-01 frontend: 수량 정수화 후속 — 무용지물 된 Decimal→number 보정 제거</t>
+        </is>
+      </c>
+      <c r="E762" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F762" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B763" s="7" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C763" s="7" t="inlineStr">
+        <is>
+          <t>eb0c3dfe</t>
+        </is>
+      </c>
+      <c r="D763" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 가용재고 계산 stock_math 정본화 — wh-pending 우회 제거</t>
+        </is>
+      </c>
+      <c r="E763" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F763" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B764" s="19" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C764" s="19" t="inlineStr">
+        <is>
+          <t>97ae1f72</t>
+        </is>
+      </c>
+      <c r="D764" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-01 chore: 고아 _defect_hub 컴포넌트 격리 — _attic 이동</t>
+        </is>
+      </c>
+      <c r="E764" s="19" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F764" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B765" s="19" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C765" s="19" t="inlineStr">
+        <is>
+          <t>5bb7bf72</t>
+        </is>
+      </c>
+      <c r="D765" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-01 backend: 모델 표현 명료화 — model_symbol(저장)/model_slots(파생) 구분 + 드리프트 가드</t>
+        </is>
+      </c>
+      <c r="E765" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F765" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B766" s="15" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C766" s="15" t="inlineStr">
+        <is>
+          <t>e7da4495</t>
+        </is>
+      </c>
+      <c r="D766" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 수량 정수화 후속 — 삭제된 보정함수 가리키던 죽은 주석 정리</t>
+        </is>
+      </c>
+      <c r="E766" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F766" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B767" s="7" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C767" s="7" t="inlineStr">
+        <is>
+          <t>aa200e28</t>
+        </is>
+      </c>
+      <c r="D767" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: 수량 정수 통일 — 알루미늄 소수 올림 + 선언타입 INTEGER 정합</t>
+        </is>
+      </c>
+      <c r="E767" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F767" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B768" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C768" s="15" t="inlineStr">
+        <is>
+          <t>e042de81</t>
+        </is>
+      </c>
+      <c r="D768" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: UUID 포맷 혼재 재발 방지 — UUIDString TypeDecorator 전 모델 적용</t>
+        </is>
+      </c>
+      <c r="E768" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F768" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B769" s="7" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C769" s="7" t="inlineStr">
+        <is>
+          <t>d67f450c</t>
+        </is>
+      </c>
+      <c r="D769" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: mes_code 생성열 진실소스화 + 모델 마스터 단일화</t>
+        </is>
+      </c>
+      <c r="E769" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F769" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B770" s="15" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C770" s="15" t="inlineStr">
+        <is>
+          <t>df4219ad</t>
+        </is>
+      </c>
+      <c r="D770" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: CLAUDE.md 전면 영문화 + 플랜모드 모델 추천 규칙 추가</t>
+        </is>
+      </c>
+      <c r="E770" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F770" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B771" s="7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C771" s="7" t="inlineStr">
+        <is>
+          <t>de1ee84d</t>
+        </is>
+      </c>
+      <c r="D771" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: 대형 서비스 분리 — stock_requests·inventory 책임별 모듈화</t>
+        </is>
+      </c>
+      <c r="E771" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F771" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B772" s="15" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="C772" s="15" t="inlineStr">
+        <is>
+          <t>7b9a512b</t>
+        </is>
+      </c>
+      <c r="D772" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: 피드백 진행상황 갱신 — 김현우 2건·이지훈 1건 해결 처리</t>
+        </is>
+      </c>
+      <c r="E772" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F772" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B773" s="7" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C773" s="7" t="inlineStr">
+        <is>
+          <t>81b4c36a</t>
+        </is>
+      </c>
+      <c r="D773" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: io.py god-service 분리 (C7) — 책임별 4모듈</t>
+        </is>
+      </c>
+      <c r="E773" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F773" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B774" s="15" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C774" s="15" t="inlineStr">
+        <is>
+          <t>9c9ac5aa</t>
+        </is>
+      </c>
+      <c r="D774" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: 플랜 모델 추천 표기 한국어로 변경</t>
+        </is>
+      </c>
+      <c r="E774" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F774" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B775" s="7" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C775" s="7" t="inlineStr">
+        <is>
+          <t>b88a8190</t>
+        </is>
+      </c>
+      <c r="D775" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: 직접 입출고 사번 감사 보강 (B C6)</t>
+        </is>
+      </c>
+      <c r="E775" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F775" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B776" s="15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="C776" s="15" t="inlineStr">
+        <is>
+          <t>ad396cf2</t>
+        </is>
+      </c>
+      <c r="D776" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 신제품(모델 9) 추가 반응성 — 하드코딩 제거</t>
+        </is>
+      </c>
+      <c r="E776" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F776" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B777" s="7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C777" s="7" t="inlineStr">
+        <is>
+          <t>07259585</t>
+        </is>
+      </c>
+      <c r="D777" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 fix: 미해결 피드백 4건 처리 — 요청함 정렬·스크롤바·라벨 inline·input 키잠김</t>
+        </is>
+      </c>
+      <c r="E777" s="7" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F777" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B778" s="15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C778" s="15" t="inlineStr">
+        <is>
+          <t>4408fa60</t>
+        </is>
+      </c>
+      <c r="D778" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 defect: 불량 전용 탭 신설 — 입출고에서 분리</t>
+        </is>
+      </c>
+      <c r="E778" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F778" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B779" s="7" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C779" s="7" t="inlineStr">
+        <is>
+          <t>0c00a182</t>
+        </is>
+      </c>
+      <c r="D779" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: 코드 리뷰 종합 + 7눈 채점 표준·계획 수립</t>
+        </is>
+      </c>
+      <c r="E779" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F779" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B780" s="15" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C780" s="15" t="inlineStr">
+        <is>
+          <t>5388eca8</t>
+        </is>
+      </c>
+      <c r="D780" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: skills-lock.json gitignore 추가</t>
+        </is>
+      </c>
+      <c r="E780" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F780" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B781" s="7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C781" s="7" t="inlineStr">
+        <is>
+          <t>9514d5d4</t>
+        </is>
+      </c>
+      <c r="D781" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: dev/prod 포트 분리 — dev를 8011/3001로 이동</t>
+        </is>
+      </c>
+      <c r="E781" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F781" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B782" s="15" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C782" s="15" t="inlineStr">
+        <is>
+          <t>eadb5ce4</t>
+        </is>
+      </c>
+      <c r="D782" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: start.bat 포트 원복 (8010/3000)</t>
+        </is>
+      </c>
+      <c r="E782" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F782" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B783" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C783" s="7" t="inlineStr">
+        <is>
+          <t>968dfede</t>
+        </is>
+      </c>
+      <c r="D783" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: start.bat dev 포트 수정 (8011/3001)</t>
+        </is>
+      </c>
+      <c r="E783" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F783" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B784" s="15" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="C784" s="15" t="inlineStr">
+        <is>
+          <t>7eb99b9b</t>
+        </is>
+      </c>
+      <c r="D784" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: start.bat BACKEND_INTERNAL_URL 공백 버그 수정</t>
+        </is>
+      </c>
+      <c r="E784" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F784" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B785" s="7" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C785" s="7" t="inlineStr">
+        <is>
+          <t>2d1b0365</t>
+        </is>
+      </c>
+      <c r="D785" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: stop-backend 포트 격리 — uvicorn 매칭에 --port 8011 조건 추가</t>
+        </is>
+      </c>
+      <c r="E785" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F785" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B786" s="15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C786" s="15" t="inlineStr">
+        <is>
+          <t>8a039c17</t>
+        </is>
+      </c>
+      <c r="D786" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: start.bat 브라우저 자동 실행 제거</t>
+        </is>
+      </c>
+      <c r="E786" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F786" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B787" s="7" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C787" s="7" t="inlineStr">
+        <is>
+          <t>9e93729f</t>
+        </is>
+      </c>
+      <c r="D787" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 브라우저 탭 타이틀 환경별 분리 (NEXT_PUBLIC_APP_TITLE)</t>
+        </is>
+      </c>
+      <c r="E787" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F787" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B788" s="15" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C788" s="15" t="inlineStr">
+        <is>
+          <t>35470a04</t>
+        </is>
+      </c>
+      <c r="D788" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 탭 제목 환경 구분 — ASCII 토글로 인코딩 깨짐 해결</t>
+        </is>
+      </c>
+      <c r="E788" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F788" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B789" s="7" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C789" s="7" t="inlineStr">
+        <is>
+          <t>7c03a572</t>
+        </is>
+      </c>
+      <c r="D789" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02 defect: 불량 탭 작업 화면 "입출고 손맛" 복원</t>
+        </is>
+      </c>
+      <c r="E789" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F789" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B790" s="15" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="C790" s="15" t="inlineStr">
+        <is>
+          <t>014de571</t>
+        </is>
+      </c>
+      <c r="D790" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: prod 배포 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="E790" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F790" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B791" s="7" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C791" s="7" t="inlineStr">
+        <is>
+          <t>455dee55</t>
+        </is>
+      </c>
+      <c r="D791" s="8" t="inlineStr">
+        <is>
+          <t>Merge pull request #17 from Hw-03/refactor/data-foundation</t>
+        </is>
+      </c>
+      <c r="E791" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F791" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B792" s="15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C792" s="15" t="inlineStr">
+        <is>
+          <t>bde2e1d9</t>
+        </is>
+      </c>
+      <c r="D792" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: 주간보고 6/2 진행분 + 피드백 정리(김건호 5건 추가, 김도영 2건 신규)</t>
+        </is>
+      </c>
+      <c r="E792" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F792" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B793" s="19" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C793" s="19" t="inlineStr">
+        <is>
+          <t>1541fe7e</t>
+        </is>
+      </c>
+      <c r="D793" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 test: 안정성 핵심 5개 서비스 회귀 그물 테스트 추가 (110개)</t>
+        </is>
+      </c>
+      <c r="E793" s="19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F793" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B794" s="19" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C794" s="19" t="inlineStr">
+        <is>
+          <t>86f38e78</t>
+        </is>
+      </c>
+      <c r="D794" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 test: inv_calc 집계 + 음수 방어망(DB CHECK) 회귀 테스트 — R2-4 재평가</t>
+        </is>
+      </c>
+      <c r="E794" s="19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F794" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B795" s="19" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="C795" s="19" t="inlineStr">
+        <is>
+          <t>121f0c63</t>
+        </is>
+      </c>
+      <c r="D795" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: symbol 캐시 빈맵 경고 로그 (R2-6)</t>
+        </is>
+      </c>
+      <c r="E795" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F795" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B796" s="19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C796" s="19" t="inlineStr">
+        <is>
+          <t>972391b4</t>
+        </is>
+      </c>
+      <c r="D796" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: production.py 거대 함수 분리 — production_receipt 5단계 헬퍼 + _buildable (동작 보존)</t>
+        </is>
+      </c>
+      <c r="E796" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F796" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B797" s="19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C797" s="19" t="inlineStr">
+        <is>
+          <t>97c1c08a</t>
+        </is>
+      </c>
+      <c r="D797" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: io_preview _direct_item_bundle 4분기 헬퍼 분리 (172→52줄, 동작 보존)</t>
+        </is>
+      </c>
+      <c r="E797" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F797" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B798" s="19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C798" s="19" t="inlineStr">
+        <is>
+          <t>8b2bc069</t>
+        </is>
+      </c>
+      <c r="D798" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: io_dispatch _apply_line 5방향 헬퍼 분리 (73→31줄, 동작 보존)</t>
+        </is>
+      </c>
+      <c r="E798" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F798" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B799" s="19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C799" s="19" t="inlineStr">
+        <is>
+          <t>3b2ebed4</t>
+        </is>
+      </c>
+      <c r="D799" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: sr_execution _execute_line 14핸들러 디스패치 분리 (165→50줄, 동작 보존)</t>
+        </is>
+      </c>
+      <c r="E799" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F799" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B800" s="19" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C800" s="19" t="inlineStr">
+        <is>
+          <t>dc6fedfe</t>
+        </is>
+      </c>
+      <c r="D800" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: 출입고 내역 용어 통일 — 새 격리/격리 해제/폐기 → 새 불량/불량 해제/불량 처리 (glossary 기준)</t>
+        </is>
+      </c>
+      <c r="E800" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F800" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B801" s="19" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C801" s="19" t="inlineStr">
+        <is>
+          <t>4bbbb7c8</t>
+        </is>
+      </c>
+      <c r="D801" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: transactions list/summary 공통 필터 빌더로 중복 제거 (동작 보존)</t>
+        </is>
+      </c>
+      <c r="E801" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F801" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B802" s="19" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C802" s="19" t="inlineStr">
+        <is>
+          <t>2297682e</t>
+        </is>
+      </c>
+      <c r="D802" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: defects list_defect_locations N+1 제거 — 사유 로그 일괄 조회 (동작 보존)</t>
+        </is>
+      </c>
+      <c r="E802" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F802" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B803" s="19" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C803" s="19" t="inlineStr">
+        <is>
+          <t>aee2707e</t>
+        </is>
+      </c>
+      <c r="D803" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: inv_defective scrap/return 분기 중복을 _consume_normal_source 로 추출 (동작 보존)</t>
+        </is>
+      </c>
+      <c r="E803" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F803" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B804" s="19" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C804" s="19" t="inlineStr">
+        <is>
+          <t>ce186907</t>
+        </is>
+      </c>
+      <c r="D804" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: 작성 표준(CODING_STYLE) 신설 + CONTEXT 폴더 명칭 가이드</t>
+        </is>
+      </c>
+      <c r="E804" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F804" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B805" s="19" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C805" s="19" t="inlineStr">
+        <is>
+          <t>d81160f7</t>
+        </is>
+      </c>
+      <c r="D805" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: sr_approval 지연 import 5/6 정적화 — io_persist(무순환) 직접 import, 순환 1건은 좁힌 지연+주석</t>
+        </is>
+      </c>
+      <c r="E805" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F805" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B806" s="19" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C806" s="19" t="inlineStr">
+        <is>
+          <t>fcd5797d</t>
+        </is>
+      </c>
+      <c r="D806" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 chore: 죽은 코드 정리 — UKAlert/CategoryCard/AppHeader _attic 이동 + 미사용 toNumber 제거</t>
+        </is>
+      </c>
+      <c r="E806" s="19" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F806" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B807" s="19" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="C807" s="19" t="inlineStr">
+        <is>
+          <t>9f8700be</t>
+        </is>
+      </c>
+      <c r="D807" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: useEffect/useMemo 의존성 회피 의도 주석 보강 (3곳, 동작 무변경)</t>
+        </is>
+      </c>
+      <c r="E807" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F807" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B808" s="19" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="C808" s="19" t="inlineStr">
+        <is>
+          <t>4426342c</t>
+        </is>
+      </c>
+      <c r="D808" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: R2-1 staleTime 도메인별 차등 — VOLATILE 30s/MASTER 30m (기본 5분·invalidate 보존)</t>
+        </is>
+      </c>
+      <c r="E808" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F808" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B809" s="19" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="C809" s="19" t="inlineStr">
+        <is>
+          <t>e984a90e</t>
+        </is>
+      </c>
+      <c r="D809" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: R2-3 getModels 7곳 useModelsQuery 캐시 공유로 교체 (Promise.all·고아 2곳 보류)</t>
+        </is>
+      </c>
+      <c r="E809" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F809" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B810" s="19" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="C810" s="19" t="inlineStr">
+        <is>
+          <t>b1a7b7c1</t>
+        </is>
+      </c>
+      <c r="D810" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: code-review §9 처리 결과 — Wave 0~4 자율 실행 (완료 13·보류 5·재평가 3)</t>
+        </is>
+      </c>
+      <c r="E810" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F810" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B811" s="19" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C811" s="19" t="inlineStr">
+        <is>
+          <t>a01a13d6</t>
+        </is>
+      </c>
+      <c r="D811" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: R2-3 마무리 — 고아 useModels _attic 이동 + useAdminBootstrap getModels→useModelsQuery(enabled)</t>
+        </is>
+      </c>
+      <c r="E811" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F811" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B812" s="19" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C812" s="19" t="inlineStr">
+        <is>
+          <t>224ad043</t>
+        </is>
+      </c>
+      <c r="D812" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 frontend: R2-2 — useAdminDepartmentsList(pass-through) useAdminDepartments 로 통합</t>
+        </is>
+      </c>
+      <c r="E812" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F812" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B813" s="19" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="C813" s="19" t="inlineStr">
+        <is>
+          <t>f641a91f</t>
+        </is>
+      </c>
+      <c r="D813" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: inv_defective 인자 dataclass(ReasonContext/DefectSource/NormalSource) + 호출처 전체 갱신</t>
+        </is>
+      </c>
+      <c r="E813" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F813" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B814" s="19" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="C814" s="19" t="inlineStr">
+        <is>
+          <t>507fc98c</t>
+        </is>
+      </c>
+      <c r="D814" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 refactor: 에러표준 통일 — departments·admin_audit_csv raise HTTPException 7곳 → http_error (프론트 extractErrorMessage 호환)</t>
+        </is>
+      </c>
+      <c r="E814" s="19" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F814" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B815" s="19" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C815" s="19" t="inlineStr">
+        <is>
+          <t>274a2e0a</t>
+        </is>
+      </c>
+      <c r="D815" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 backend: mes_code 부분 unique (WHERE deleted_at IS NULL) — 소프트삭제 후 재등록 허용 (R2-5)</t>
+        </is>
+      </c>
+      <c r="E815" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F815" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B816" s="19" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="C816" s="19" t="inlineStr">
+        <is>
+          <t>f982d2d5</t>
+        </is>
+      </c>
+      <c r="D816" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-02 docs: §10 잔여 이슈 2차 해소 — 보류 5건 전부 구현 + e2e 인프라 발견 기록</t>
+        </is>
+      </c>
+      <c r="E816" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F816" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B817" s="7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C817" s="7" t="inlineStr">
+        <is>
+          <t>325d9fbe</t>
+        </is>
+      </c>
+      <c r="D817" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 chore: @playwright/test devDep 추가 + handoff·workspace 백업 커밋</t>
+        </is>
+      </c>
+      <c r="E817" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F817" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B818" s="15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C818" s="15" t="inlineStr">
+        <is>
+          <t>15c243a1</t>
+        </is>
+      </c>
+      <c r="D818" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 frontend: 피드백 4건 — BOM 박스 클릭·휴지통·반려 폴링·하위 BOM 트리</t>
+        </is>
+      </c>
+      <c r="E818" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F818" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B819" s="7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C819" s="7" t="inlineStr">
+        <is>
+          <t>8d9f497e</t>
+        </is>
+      </c>
+      <c r="D819" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 남재원·이필욱 피드백 파일 신규 추가</t>
+        </is>
+      </c>
+      <c r="E819" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F819" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B820" s="15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C820" s="15" t="inlineStr">
+        <is>
+          <t>4c152b9b</t>
+        </is>
+      </c>
+      <c r="D820" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 test: e2e 전용DB globalSetup + 로그인우회 + 쓰기 4 spec 그린</t>
+        </is>
+      </c>
+      <c r="E820" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F820" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B821" s="7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C821" s="7" t="inlineStr">
+        <is>
+          <t>6627bef3</t>
+        </is>
+      </c>
+      <c r="D821" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: §10 e2e 인프라 발견 → 해소 기록</t>
+        </is>
+      </c>
+      <c r="E821" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F821" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B822" s="15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C822" s="15" t="inlineStr">
+        <is>
+          <t>d81ed4d6</t>
+        </is>
+      </c>
+      <c r="D822" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 test: e2e 커버리지 확장 — 불량·결재 풀사이클·produce 잠김 + CI job</t>
+        </is>
+      </c>
+      <c r="E822" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F822" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B823" s="7" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C823" s="7" t="inlineStr">
+        <is>
+          <t>113045db</t>
+        </is>
+      </c>
+      <c r="D823" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 refactor: 결재 규칙 단일 원천(approval_rules) + FE↔BE drift 가드 (ADR-0005)</t>
+        </is>
+      </c>
+      <c r="E823" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F823" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B824" s="15" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C824" s="15" t="inlineStr">
+        <is>
+          <t>4e29ad3c</t>
+        </is>
+      </c>
+      <c r="D824" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 backend: 내역 export(csv/xlsx) 요청자/승인자명 동기화 (D1)</t>
+        </is>
+      </c>
+      <c r="E824" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F824" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B825" s="7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C825" s="7" t="inlineStr">
+        <is>
+          <t>936a345d</t>
+        </is>
+      </c>
+      <c r="D825" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 세션 핸드오프 — e2e 확장·결재규칙 deepening·export 동기화 + D3/D4 스코핑</t>
+        </is>
+      </c>
+      <c r="E825" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F825" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B826" s="15" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C826" s="15" t="inlineStr">
+        <is>
+          <t>8bfaddc1</t>
+        </is>
+      </c>
+      <c r="D826" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 불량 화면 개선(D3) 전용 핸드오프 — 거의 완성, 남은 건 부서간 격리이동 1건</t>
+        </is>
+      </c>
+      <c r="E826" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F826" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B827" s="7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C827" s="7" t="inlineStr">
+        <is>
+          <t>1dc3d0fc</t>
+        </is>
+      </c>
+      <c r="D827" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 warehouse: 창고 지도 실데이터 통합 — 앵글/박스 모델·API·지도뷰·관리(구조편집/위치배정)·재고대조</t>
+        </is>
+      </c>
+      <c r="E827" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F827" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B828" s="15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="C828" s="15" t="inlineStr">
+        <is>
+          <t>fe5bf449</t>
+        </is>
+      </c>
+      <c r="D828" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 피드백 현황 갱신 — 구현 완료 항목 해결 처리</t>
+        </is>
+      </c>
+      <c r="E828" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F828" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B829" s="7" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C829" s="7" t="inlineStr">
+        <is>
+          <t>6d01ec26</t>
+        </is>
+      </c>
+      <c r="D829" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 chore: _attic/verify_out.log gitignore 추가</t>
+        </is>
+      </c>
+      <c r="E829" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F829" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B830" s="15" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C830" s="15" t="inlineStr">
+        <is>
+          <t>a943faef</t>
+        </is>
+      </c>
+      <c r="D830" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 핸드오프 — 김현우 audit 로그 묶음 (재작업 소실·덮어쓰기)</t>
+        </is>
+      </c>
+      <c r="E830" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F830" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B831" s="7" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C831" s="7" t="inlineStr">
+        <is>
+          <t>3debca48</t>
+        </is>
+      </c>
+      <c r="D831" s="8" t="inlineStr">
+        <is>
+          <t>Merge pull request #20 from Hw-03/cleanup/code-review-fixes</t>
+        </is>
+      </c>
+      <c r="E831" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F831" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B832" s="15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C832" s="15" t="inlineStr">
+        <is>
+          <t>fb542093</t>
+        </is>
+      </c>
+      <c r="D832" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 items: mes_code 전역 unique 복원 — 삭제 코드 재사용 차단</t>
+        </is>
+      </c>
+      <c r="E832" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F832" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>831건 (회사 기간 670건)</t>
+          <t>876건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>304건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>325건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -1869,20 +1869,61 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■■■■■■■</t>
+            <t>■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (16)</t>
+            <t xml:space="preserve">  (29)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-05  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (32)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -1919,6 +1960,7 @@
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="B8:E8"/>
@@ -4369,7 +4411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5377,7 +5419,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
@@ -5390,7 +5432,31 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="67.5" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 인수인계 UX 개선 + 인수인계 도착 알림
+2026-06-05 docs: 피드백 현황 갱신 — F1~F5 구현 반영 (해결 5건)
+2026-06-05 chore: gitignore .understand-anything 산출물
+2026-06-05 backend: schemas.py → schemas/ 도메인별 패키지 분리
+2026-06-05 docs: legacy/_warehouse_v2 폴더 오해 방지 README 추가</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Backend</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F832"/>
+  <dimension ref="A1:F877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32040,6 +32106,1446 @@
         </is>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B833" s="7" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C833" s="7" t="inlineStr">
+        <is>
+          <t>1bea7ea7</t>
+        </is>
+      </c>
+      <c r="D833" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 이지훈 피드백 2건 추가 + 직원연락망·인수인계 자료 보관</t>
+        </is>
+      </c>
+      <c r="E833" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F833" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B834" s="15" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C834" s="15" t="inlineStr">
+        <is>
+          <t>4a3e549b</t>
+        </is>
+      </c>
+      <c r="D834" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 docs: 주간보고 5/30~6/4 최종 — 호칭 정정 + 사용자 수정분 반영</t>
+        </is>
+      </c>
+      <c r="E834" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F834" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B835" s="7" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C835" s="7" t="inlineStr">
+        <is>
+          <t>2abe513a</t>
+        </is>
+      </c>
+      <c r="D835" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04 frontend: 창고 지도 — 브라우저 뒤로가기·박스 hover·줄 구분·다중 품목코드</t>
+        </is>
+      </c>
+      <c r="E835" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F835" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B836" s="19" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C836" s="19" t="inlineStr">
+        <is>
+          <t>ff0c1f2e</t>
+        </is>
+      </c>
+      <c r="D836" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-04 io: 입출고 임시저장 덮어쓰기 제거 — batch_id 분기로 새 슬롯 누적</t>
+        </is>
+      </c>
+      <c r="E836" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F836" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B837" s="19" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C837" s="19" t="inlineStr">
+        <is>
+          <t>cd621bc3</t>
+        </is>
+      </c>
+      <c r="D837" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-04 defect: 재작업 분해 시 회수 외 자식 → 격리 이동 (소실 차단)</t>
+        </is>
+      </c>
+      <c r="E837" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F837" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B838" s="19" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="C838" s="19" t="inlineStr">
+        <is>
+          <t>494fb287</t>
+        </is>
+      </c>
+      <c r="D838" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-04 notify: 결재 알림 시스템 — 요청 도착/승인/반려 (F2·F3)</t>
+        </is>
+      </c>
+      <c r="E838" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F838" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B839" s="19" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C839" s="19" t="inlineStr">
+        <is>
+          <t>03cd6fb3</t>
+        </is>
+      </c>
+      <c r="D839" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-04 handover: 튜브→고압/진공 인수인계서 (작성·인수확인·자동이동·인쇄) (F1)</t>
+        </is>
+      </c>
+      <c r="E839" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F839" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B840" s="19" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C840" s="19" t="inlineStr">
+        <is>
+          <t>5ab1634f</t>
+        </is>
+      </c>
+      <c r="D840" s="20" t="inlineStr">
+        <is>
+          <t>Merge feat/io-draft-stacking (F5): 입출고 임시저장 누적</t>
+        </is>
+      </c>
+      <c r="E840" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F840" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B841" s="19" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C841" s="19" t="inlineStr">
+        <is>
+          <t>d9a360cb</t>
+        </is>
+      </c>
+      <c r="D841" s="20" t="inlineStr">
+        <is>
+          <t>Merge feat/rework-quarantine (F4): 재작업 회수 외 자식 격리 이동</t>
+        </is>
+      </c>
+      <c r="E841" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F841" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B842" s="19" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C842" s="19" t="inlineStr">
+        <is>
+          <t>3130c356</t>
+        </is>
+      </c>
+      <c r="D842" s="20" t="inlineStr">
+        <is>
+          <t>Merge feat/approval-notifications (F2·F3): 결재 알림 시스템</t>
+        </is>
+      </c>
+      <c r="E842" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F842" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B843" s="19" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C843" s="19" t="inlineStr">
+        <is>
+          <t>0f1fcb1b</t>
+        </is>
+      </c>
+      <c r="D843" s="20" t="inlineStr">
+        <is>
+          <t>Merge feat/handover-doc (F1): 튜브→고압/진공 인수인계서</t>
+        </is>
+      </c>
+      <c r="E843" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F843" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B844" s="15" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C844" s="15" t="inlineStr">
+        <is>
+          <t>6302eeec</t>
+        </is>
+      </c>
+      <c r="D844" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-04 frontend: 창고 지도 — 브라우저 뒤로가기·박스 hover·줄 구분·다중 품목코드</t>
+        </is>
+      </c>
+      <c r="E844" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F844" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B845" s="19" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C845" s="19" t="inlineStr">
+        <is>
+          <t>796578de</t>
+        </is>
+      </c>
+      <c r="D845" s="20" t="inlineStr">
+        <is>
+          <t>Merge pull request #21 from Hw-03/docs/feedback-handover-2026-06-04</t>
+        </is>
+      </c>
+      <c r="E845" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F845" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B846" s="15" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C846" s="15" t="inlineStr">
+        <is>
+          <t>9ab9e66a</t>
+        </is>
+      </c>
+      <c r="D846" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 인수인계 UX 개선 + 인수인계 도착 알림</t>
+        </is>
+      </c>
+      <c r="E846" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F846" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B847" s="7" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="C847" s="7" t="inlineStr">
+        <is>
+          <t>51db7f8e</t>
+        </is>
+      </c>
+      <c r="D847" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 docs: 피드백 현황 갱신 — F1~F5 구현 반영 (해결 5건)</t>
+        </is>
+      </c>
+      <c r="E847" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F847" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B848" s="15" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C848" s="15" t="inlineStr">
+        <is>
+          <t>3bba6cbf</t>
+        </is>
+      </c>
+      <c r="D848" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 chore: gitignore .understand-anything 산출물</t>
+        </is>
+      </c>
+      <c r="E848" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F848" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B849" s="7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C849" s="7" t="inlineStr">
+        <is>
+          <t>4333ee7d</t>
+        </is>
+      </c>
+      <c r="D849" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 backend: schemas.py → schemas/ 도메인별 패키지 분리</t>
+        </is>
+      </c>
+      <c r="E849" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F849" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B850" s="15" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C850" s="15" t="inlineStr">
+        <is>
+          <t>6ffbdf6e</t>
+        </is>
+      </c>
+      <c r="D850" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 docs: legacy/_warehouse_v2 폴더 오해 방지 README 추가</t>
+        </is>
+      </c>
+      <c r="E850" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F850" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B851" s="7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C851" s="7" t="inlineStr">
+        <is>
+          <t>59f656f4</t>
+        </is>
+      </c>
+      <c r="D851" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 backend: transactions.py 필터/응답 헬퍼 → _tx_filters.py 분리</t>
+        </is>
+      </c>
+      <c r="E851" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F851" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B852" s="15" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C852" s="15" t="inlineStr">
+        <is>
+          <t>b7e3b330</t>
+        </is>
+      </c>
+      <c r="D852" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 인수인계 인쇄 — 로고 base64 임베드 + A4 문서 레이아웃</t>
+        </is>
+      </c>
+      <c r="E852" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F852" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B853" s="7" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C853" s="7" t="inlineStr">
+        <is>
+          <t>5f36fa1a</t>
+        </is>
+      </c>
+      <c r="D853" s="8" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/refactor/cleancode-review-prep'</t>
+        </is>
+      </c>
+      <c r="E853" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F853" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B854" s="15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C854" s="15" t="inlineStr">
+        <is>
+          <t>a9388922</t>
+        </is>
+      </c>
+      <c r="D854" s="16" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/docs/feedback-f1f5-resolved'</t>
+        </is>
+      </c>
+      <c r="E854" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F854" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B855" s="7" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C855" s="7" t="inlineStr">
+        <is>
+          <t>34ac5d93</t>
+        </is>
+      </c>
+      <c r="D855" s="8" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/feat/handover-print-template'</t>
+        </is>
+      </c>
+      <c r="E855" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F855" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B856" s="15" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C856" s="15" t="inlineStr">
+        <is>
+          <t>d16218f3</t>
+        </is>
+      </c>
+      <c r="D856" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 data: 튜브-고압 인수인계서 보관 (pdf·docx)</t>
+        </is>
+      </c>
+      <c r="E856" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F856" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B857" s="7" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="C857" s="7" t="inlineStr">
+        <is>
+          <t>5b1058a9</t>
+        </is>
+      </c>
+      <c r="D857" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 chore: 완료 플랜 _attic/docs/research 보관 (cleancode-review-prep)</t>
+        </is>
+      </c>
+      <c r="E857" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F857" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B858" s="15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="C858" s="15" t="inlineStr">
+        <is>
+          <t>7b3f968e</t>
+        </is>
+      </c>
+      <c r="D858" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: Pretendard 폰트 self-host 로드</t>
+        </is>
+      </c>
+      <c r="E858" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F858" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B859" s="7" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr">
+        <is>
+          <t>e37cf2d9</t>
+        </is>
+      </c>
+      <c r="D859" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 docs: 모바일 디자인 시스템 문서 실측 정정</t>
+        </is>
+      </c>
+      <c r="E859" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F859" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B860" s="15" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C860" s="15" t="inlineStr">
+        <is>
+          <t>5b85a2ba</t>
+        </is>
+      </c>
+      <c r="D860" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 refactor: 모바일 중복 primitive 정리 — 죽은 EmptyState 제거·분리 명시</t>
+        </is>
+      </c>
+      <c r="E860" s="15" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F860" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B861" s="7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C861" s="7" t="inlineStr">
+        <is>
+          <t>3a4becc3</t>
+        </is>
+      </c>
+      <c r="D861" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: features/mes 디자인 규칙 ESLint 가드 추가</t>
+        </is>
+      </c>
+      <c r="E861" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F861" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B862" s="15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C862" s="15" t="inlineStr">
+        <is>
+          <t>7eae9897</t>
+        </is>
+      </c>
+      <c r="D862" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'feat/design-consistency'</t>
+        </is>
+      </c>
+      <c r="E862" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F862" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B863" s="7" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C863" s="7" t="inlineStr">
+        <is>
+          <t>0cadee07</t>
+        </is>
+      </c>
+      <c r="D863" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 불량 탭 디자인 정합 — 표준 primitive·토큰으로 통일</t>
+        </is>
+      </c>
+      <c r="E863" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F863" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B864" s="15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C864" s="15" t="inlineStr">
+        <is>
+          <t>95f6a989</t>
+        </is>
+      </c>
+      <c r="D864" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 불량 탭 3장 카드 진입 화면 + 바로 폐기 전 품목화</t>
+        </is>
+      </c>
+      <c r="E864" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F864" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B865" s="7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C865" s="7" t="inlineStr">
+        <is>
+          <t>328e313e</t>
+        </is>
+      </c>
+      <c r="D865" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05 docs: 이계숙 주임 피드백 2건 등록 (구두)</t>
+        </is>
+      </c>
+      <c r="E865" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F865" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B866" s="19" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C866" s="19" t="inlineStr">
+        <is>
+          <t>b577189a</t>
+        </is>
+      </c>
+      <c r="D866" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 미사용 features/mes 빈 골조 7파일 제거</t>
+        </is>
+      </c>
+      <c r="E866" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F866" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B867" s="19" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C867" s="19" t="inlineStr">
+        <is>
+          <t>1c402557</t>
+        </is>
+      </c>
+      <c r="D867" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: 죽은 _archive 컴포넌트 4파일 제거 (import 깨짐·미사용)</t>
+        </is>
+      </c>
+      <c r="E867" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F867" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B868" s="19" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C868" s="19" t="inlineStr">
+        <is>
+          <t>e61e12c4</t>
+        </is>
+      </c>
+      <c r="D868" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: features/mes 전용 ESLint overrides 블록 제거</t>
+        </is>
+      </c>
+      <c r="E868" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F868" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B869" s="19" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="C869" s="19" t="inlineStr">
+        <is>
+          <t>6e7a637e</t>
+        </is>
+      </c>
+      <c r="D869" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: app/legacy → app/mes 개명 + 앱 라우트 /legacy→/mes</t>
+        </is>
+      </c>
+      <c r="E869" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F869" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B870" s="19" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="C870" s="19" t="inlineStr">
+        <is>
+          <t>bbd7ed0f</t>
+        </is>
+      </c>
+      <c r="D870" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: e2e·모바일 스크립트 라우트 /legacy→/mes 갱신</t>
+        </is>
+      </c>
+      <c r="E870" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F870" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B871" s="19" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C871" s="19" t="inlineStr">
+        <is>
+          <t>a4a74eaa</t>
+        </is>
+      </c>
+      <c r="D871" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 fix: app/legacy→mes 개명 누락 참조 수정 (drift 테스트 경로·docstring·CLAUDE.md·README)</t>
+        </is>
+      </c>
+      <c r="E871" s="19" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F871" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B872" s="19" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C872" s="19" t="inlineStr">
+        <is>
+          <t>a7a99eb4</t>
+        </is>
+      </c>
+      <c r="D872" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: e2e io-defect 로케이터 수정 — filter 방식으로 공백 의존성 제거</t>
+        </is>
+      </c>
+      <c r="E872" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F872" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B873" s="19" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C873" s="19" t="inlineStr">
+        <is>
+          <t>0dfff902</t>
+        </is>
+      </c>
+      <c r="D873" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 frontend: e2e io-defect 로케이터 수정 — filter 방식으로 공백 의존성 제거</t>
+        </is>
+      </c>
+      <c r="E873" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F873" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B874" s="19" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C874" s="19" t="inlineStr">
+        <is>
+          <t>e0a29b5d</t>
+        </is>
+      </c>
+      <c r="D874" s="20" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/main' into refactor/legacy-to-mes</t>
+        </is>
+      </c>
+      <c r="E874" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F874" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B875" s="19" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C875" s="19" t="inlineStr">
+        <is>
+          <t>04d4ab17</t>
+        </is>
+      </c>
+      <c r="D875" s="20" t="inlineStr">
+        <is>
+          <t>Merge branch 'refactor/legacy-to-mes' into HEAD</t>
+        </is>
+      </c>
+      <c r="E875" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F875" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B876" s="19" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="C876" s="19" t="inlineStr">
+        <is>
+          <t>7f7815f5</t>
+        </is>
+      </c>
+      <c r="D876" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05 docs: legacy→mes 개명 완료 플랜 _attic/docs/research 보관</t>
+        </is>
+      </c>
+      <c r="E876" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F876" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B877" s="19" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="C877" s="19" t="inlineStr">
+        <is>
+          <t>e5a612b9</t>
+        </is>
+      </c>
+      <c r="D877" s="20" t="inlineStr">
+        <is>
+          <t>Merge branch 'docs/feedback-lee-gye-suk-2026-06-05'</t>
+        </is>
+      </c>
+      <c r="E877" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F877" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>876건 (회사 기간 670건)</t>
+          <t>920건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>325건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>326건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -1922,8 +1922,89 @@
         </is>
       </c>
     </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-08  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (31)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-09  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-10  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (4)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="54">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -1940,6 +2021,7 @@
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="B7:E7"/>
@@ -1948,7 +2030,9 @@
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
@@ -4411,7 +4495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5457,6 +5541,77 @@
       <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="67.5" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: add useToggleSet hook (필터 토글 중복 통합용)
+2026-06-08 frontend: 필터 토글 12개를 useToggleSet 로 치환 (중복 제거)
+2026-06-08 chore: coverage 문서 임계 정정(50→75) + io_dispatch exc
+2026-06-08 frontend: 부서결재·draft React Query 훅 추가 (useDraftCa
+2026-06-08 frontend: 창고 패널 3종 손수 fetch→React Query 이관 (중복 제거</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="67.5" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09 dev: add stop-frontend.ps1 + start.bat preflight 
+2026-06-09 frontend: 불량 탭 피드백 개선 — 부분 수량 복귀·부서 필터·KPI 카드 분리
+2026-06-09 frontend: 불량 탭 헤더 제거 + 뷰 전환 슬라이드 애니메이션
+2026-06-09 frontend: 창고 지도 UX 개선 (열 클릭·자리 분할·슬롯 번호)
+2026-06-09 defect: 불량 탭 UX 개선 (카트 흐름·뒤로가기·필터 정리)</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 defect: 처리 패널 재설계 + 부서 접기/펼치기 UX
+2026-06-10 backend: unquarantine reason_category optional 처리
+2026-06-10 test: io-defect E2E 안정화 — 정상복귀 제출 셀렉터 모호성 해소
+2026-06-10 docs: 주간보고 6/7~6/10 갱신</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F877"/>
+  <dimension ref="A1:F921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33546,6 +33701,1414 @@
         </is>
       </c>
     </row>
+    <row r="878">
+      <c r="A878" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B878" s="15" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C878" s="15" t="inlineStr">
+        <is>
+          <t>62ab44cb</t>
+        </is>
+      </c>
+      <c r="D878" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: add useToggleSet hook (필터 토글 중복 통합용)</t>
+        </is>
+      </c>
+      <c r="E878" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F878" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B879" s="7" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C879" s="7" t="inlineStr">
+        <is>
+          <t>17bd57e2</t>
+        </is>
+      </c>
+      <c r="D879" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 필터 토글 12개를 useToggleSet 로 치환 (중복 제거)</t>
+        </is>
+      </c>
+      <c r="E879" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F879" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B880" s="15" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C880" s="15" t="inlineStr">
+        <is>
+          <t>c888a0d3</t>
+        </is>
+      </c>
+      <c r="D880" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 chore: coverage 문서 임계 정정(50→75) + io_dispatch except 의도 주석</t>
+        </is>
+      </c>
+      <c r="E880" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F880" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B881" s="7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C881" s="7" t="inlineStr">
+        <is>
+          <t>13218771</t>
+        </is>
+      </c>
+      <c r="D881" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 부서결재·draft React Query 훅 추가 (useDraftCartQuery 신설)</t>
+        </is>
+      </c>
+      <c r="E881" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F881" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B882" s="15" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C882" s="15" t="inlineStr">
+        <is>
+          <t>70412baf</t>
+        </is>
+      </c>
+      <c r="D882" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 창고 패널 3종 손수 fetch→React Query 이관 (중복 제거)</t>
+        </is>
+      </c>
+      <c r="E882" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F882" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B883" s="7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C883" s="7" t="inlineStr">
+        <is>
+          <t>e656dd1c</t>
+        </is>
+      </c>
+      <c r="D883" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: AdminDepartmentsSection 하위 컴포넌트 분리 (큰 파일 정리)</t>
+        </is>
+      </c>
+      <c r="E883" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F883" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B884" s="15" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C884" s="15" t="inlineStr">
+        <is>
+          <t>f8b97196</t>
+        </is>
+      </c>
+      <c r="D884" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: AdminEmployeesSection 하위 컴포넌트 분리 (큰 파일 정리)</t>
+        </is>
+      </c>
+      <c r="E884" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F884" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B885" s="7" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="C885" s="7" t="inlineStr">
+        <is>
+          <t>1e80dcda</t>
+        </is>
+      </c>
+      <c r="D885" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 docs: 주간보고 6/1~6/5 갱신 + 자동화 스킬 추가</t>
+        </is>
+      </c>
+      <c r="E885" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F885" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B886" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C886" s="15" t="inlineStr">
+        <is>
+          <t>366c584a</t>
+        </is>
+      </c>
+      <c r="D886" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: EmployeeItemOrder 모델 추가 (직원별 품목 순서 저장 테이블)</t>
+        </is>
+      </c>
+      <c r="E886" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F886" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B887" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C887" s="7" t="inlineStr">
+        <is>
+          <t>11617983</t>
+        </is>
+      </c>
+      <c r="D887" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: MyItemOrder 스키마 추가 (개인 품목 순서 입출력)</t>
+        </is>
+      </c>
+      <c r="E887" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F887" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B888" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C888" s="15" t="inlineStr">
+        <is>
+          <t>2e739bbf</t>
+        </is>
+      </c>
+      <c r="D888" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: /api/items/my-order 라우터 추가 (GET/PUT/DELETE, 개인 순서·PIN 불필요)</t>
+        </is>
+      </c>
+      <c r="E888" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F888" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B889" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C889" s="7" t="inlineStr">
+        <is>
+          <t>7c15195e</t>
+        </is>
+      </c>
+      <c r="D889" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: my-order 엔드포인트 테스트 8건 추가</t>
+        </is>
+      </c>
+      <c r="E889" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F889" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B890" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C890" s="15" t="inlineStr">
+        <is>
+          <t>e6e8eb8f</t>
+        </is>
+      </c>
+      <c r="D890" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 chore: OpenAPI baseline 갱신 (my-order 엔드포인트 반영)</t>
+        </is>
+      </c>
+      <c r="E890" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F890" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B891" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C891" s="7" t="inlineStr">
+        <is>
+          <t>bdca6aef</t>
+        </is>
+      </c>
+      <c r="D891" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: my-order API 함수·쿼리키 추가</t>
+        </is>
+      </c>
+      <c r="E891" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F891" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B892" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C892" s="15" t="inlineStr">
+        <is>
+          <t>529dbfe4</t>
+        </is>
+      </c>
+      <c r="D892" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: useMyItemOrderQuery 훅 추가 (조회·저장·초기화)</t>
+        </is>
+      </c>
+      <c r="E892" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F892" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B893" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C893" s="7" t="inlineStr">
+        <is>
+          <t>f20db273</t>
+        </is>
+      </c>
+      <c r="D893" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: useItemOrderDrag 드래그 훅 추가 (포인터 기반 재정렬)</t>
+        </is>
+      </c>
+      <c r="E893" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F893" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B894" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C894" s="15" t="inlineStr">
+        <is>
+          <t>963cb4a8</t>
+        </is>
+      </c>
+      <c r="D894" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: buildEmployeeOrderRank 정렬 헬퍼 추가</t>
+        </is>
+      </c>
+      <c r="E894" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F894" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B895" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C895" s="7" t="inlineStr">
+        <is>
+          <t>070bd67f</t>
+        </is>
+      </c>
+      <c r="D895" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 입출고 품목창에 직원별 순서 정렬·편집 UI 적용</t>
+        </is>
+      </c>
+      <c r="E895" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F895" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B896" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C896" s="15" t="inlineStr">
+        <is>
+          <t>7bb33fb5</t>
+        </is>
+      </c>
+      <c r="D896" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 불량 품목창에 직원별 순서 정렬·편집 UI 적용 (테스트 QueryClient 주입)</t>
+        </is>
+      </c>
+      <c r="E896" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F896" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B897" s="7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C897" s="7" t="inlineStr">
+        <is>
+          <t>6733cc67</t>
+        </is>
+      </c>
+      <c r="D897" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 격리 추가 검색결과에 직원별 순서 정렬 적용 (테스트 QueryClient 주입)</t>
+        </is>
+      </c>
+      <c r="E897" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F897" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B898" s="15" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C898" s="15" t="inlineStr">
+        <is>
+          <t>48f0c0b3</t>
+        </is>
+      </c>
+      <c r="D898" s="16" t="inlineStr">
+        <is>
+          <t>Merge pull request #29 from Hw-03/feat/employee-item-order</t>
+        </is>
+      </c>
+      <c r="E898" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F898" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B899" s="7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C899" s="7" t="inlineStr">
+        <is>
+          <t>98eca70d</t>
+        </is>
+      </c>
+      <c r="D899" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: warehouse_map 라우터·서비스 테스트 신설</t>
+        </is>
+      </c>
+      <c r="E899" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F899" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B900" s="15" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C900" s="15" t="inlineStr">
+        <is>
+          <t>d285764b</t>
+        </is>
+      </c>
+      <c r="D900" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: io_preview 라우팅·BOM 전개 단위 테스트 신설</t>
+        </is>
+      </c>
+      <c r="E900" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F900" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B901" s="7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C901" s="7" t="inlineStr">
+        <is>
+          <t>9c039233</t>
+        </is>
+      </c>
+      <c r="D901" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: ItemDetailSheet fetch→React Query 이관 (+ useTransactionsQuery enabled 옵션)</t>
+        </is>
+      </c>
+      <c r="E901" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F901" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B902" s="15" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C902" s="15" t="inlineStr">
+        <is>
+          <t>63270d42</t>
+        </is>
+      </c>
+      <c r="D902" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: io 제출 원자성 회귀 테스트 추가</t>
+        </is>
+      </c>
+      <c r="E902" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F902" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B903" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C903" s="7" t="inlineStr">
+        <is>
+          <t>94508dd2</t>
+        </is>
+      </c>
+      <c r="D903" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: Item·Inventory 조회 repository 도입·중복 통합</t>
+        </is>
+      </c>
+      <c r="E903" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F903" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B904" s="15" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="C904" s="15" t="inlineStr">
+        <is>
+          <t>892c1701</t>
+        </is>
+      </c>
+      <c r="D904" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-08 docs: 허동현·이지훈 피드백 등록 (불량처리·창고지도·BOM)</t>
+        </is>
+      </c>
+      <c r="E904" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F904" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B905" s="7" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="C905" s="7" t="inlineStr">
+        <is>
+          <t>fde59b0d</t>
+        </is>
+      </c>
+      <c r="D905" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 docs: ERD 전면 현행화 — 25개 테이블 8개 도메인</t>
+        </is>
+      </c>
+      <c r="E905" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F905" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B906" s="15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="C906" s="15" t="inlineStr">
+        <is>
+          <t>51760207</t>
+        </is>
+      </c>
+      <c r="D906" s="16" t="inlineStr">
+        <is>
+          <t>Merge pull request #30 from Hw-03/docs/feedback-huh-lee-20260608</t>
+        </is>
+      </c>
+      <c r="E906" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F906" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B907" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C907" s="7" t="inlineStr">
+        <is>
+          <t>9f3d31b2</t>
+        </is>
+      </c>
+      <c r="D907" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08 frontend: 창고 지도 위치 안내 UX 개선</t>
+        </is>
+      </c>
+      <c r="E907" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F907" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B908" s="19" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="C908" s="19" t="inlineStr">
+        <is>
+          <t>5c83271f</t>
+        </is>
+      </c>
+      <c r="D908" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-08 backend: fix unhandled exception handler logging (exc_info=exc)</t>
+        </is>
+      </c>
+      <c r="E908" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F908" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B909" s="7" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="C909" s="7" t="inlineStr">
+        <is>
+          <t>f452da9e</t>
+        </is>
+      </c>
+      <c r="D909" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09 dev: add stop-frontend.ps1 + start.bat preflight 연동</t>
+        </is>
+      </c>
+      <c r="E909" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F909" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B910" s="15" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="C910" s="15" t="inlineStr">
+        <is>
+          <t>1ca2f201</t>
+        </is>
+      </c>
+      <c r="D910" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09 frontend: 불량 탭 피드백 개선 — 부분 수량 복귀·부서 필터·KPI 카드 분리</t>
+        </is>
+      </c>
+      <c r="E910" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F910" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B911" s="7" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C911" s="7" t="inlineStr">
+        <is>
+          <t>a6874b75</t>
+        </is>
+      </c>
+      <c r="D911" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09 frontend: 불량 탭 헤더 제거 + 뷰 전환 슬라이드 애니메이션</t>
+        </is>
+      </c>
+      <c r="E911" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F911" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B912" s="15" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C912" s="15" t="inlineStr">
+        <is>
+          <t>e9e169a5</t>
+        </is>
+      </c>
+      <c r="D912" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09 frontend: 창고 지도 UX 개선 (열 클릭·자리 분할·슬롯 번호)</t>
+        </is>
+      </c>
+      <c r="E912" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F912" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B913" s="7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C913" s="7" t="inlineStr">
+        <is>
+          <t>b88954e6</t>
+        </is>
+      </c>
+      <c r="D913" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09 defect: 불량 탭 UX 개선 (카트 흐름·뒤로가기·필터 정리)</t>
+        </is>
+      </c>
+      <c r="E913" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F913" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B914" s="15" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C914" s="15" t="inlineStr">
+        <is>
+          <t>d3440b9a</t>
+        </is>
+      </c>
+      <c r="D914" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09 frontend: fix E2E test — update io-defect spec for hub 3-card flow</t>
+        </is>
+      </c>
+      <c r="E914" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F914" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B915" s="7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C915" s="7" t="inlineStr">
+        <is>
+          <t>167f5dcb</t>
+        </is>
+      </c>
+      <c r="D915" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09 defect: 격리 목록 UX 개선 — 출처 기본값·제목·배지·체크박스</t>
+        </is>
+      </c>
+      <c r="E915" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F915" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B916" s="15" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="C916" s="15" t="inlineStr">
+        <is>
+          <t>4e8d018a</t>
+        </is>
+      </c>
+      <c r="D916" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09 defect: 창고 격리 → department='창고' 그룹 표시</t>
+        </is>
+      </c>
+      <c r="E916" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F916" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B917" s="7" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C917" s="7" t="inlineStr">
+        <is>
+          <t>2c7b40fa</t>
+        </is>
+      </c>
+      <c r="D917" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09 defect: 창고 담당자 격리 목록 기본 스코프 전체로 변경</t>
+        </is>
+      </c>
+      <c r="E917" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F917" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B918" s="15" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C918" s="15" t="inlineStr">
+        <is>
+          <t>4282e7f5</t>
+        </is>
+      </c>
+      <c r="D918" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 defect: 처리 패널 재설계 + 부서 접기/펼치기 UX</t>
+        </is>
+      </c>
+      <c r="E918" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F918" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B919" s="7" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="C919" s="7" t="inlineStr">
+        <is>
+          <t>ff39db2f</t>
+        </is>
+      </c>
+      <c r="D919" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 backend: unquarantine reason_category optional 처리</t>
+        </is>
+      </c>
+      <c r="E919" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F919" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B920" s="15" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C920" s="15" t="inlineStr">
+        <is>
+          <t>34870c58</t>
+        </is>
+      </c>
+      <c r="D920" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 test: io-defect E2E 안정화 — 정상복귀 제출 셀렉터 모호성 해소</t>
+        </is>
+      </c>
+      <c r="E920" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F920" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B921" s="7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C921" s="7" t="inlineStr">
+        <is>
+          <t>30c4b20b</t>
+        </is>
+      </c>
+      <c r="D921" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 docs: 주간보고 6/7~6/10 갱신</t>
+        </is>
+      </c>
+      <c r="E921" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F921" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>920건 (회사 기간 670건)</t>
+          <t>964건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>326건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>333건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -1991,20 +1991,54 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■</t>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (4)</t>
+            <t xml:space="preserve">  (19)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-11  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (29)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="55">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -2036,6 +2070,7 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A47:E47"/>
@@ -2070,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2330,7 +2365,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>사내 시연 + 양식 정비 + 운영 정책 맞춤 + 사번 audit</t>
+          <t>사내 시연 + 양식 정비 + 운영 정책 맞춤 + 사번 감사</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2351,6 +2386,59 @@
       </c>
       <c r="D12" s="7" t="n">
         <v>177</v>
+      </c>
+    </row>
+    <row r="13" ht="113.4" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-30 ~ 06-05</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>코드 품질 + 아키텍처 정비</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>수량 정수 전용(IntQuantity) 아키텍처 정비 — 입력 422·출력·내부 일관화
+ItemCode → mes_code 전면 리네임 완료
+legacy → mes 폴더 개명 (프론트엔드 라우트 전면 재정리)
+클린코드 Phase 1 — schemas/ 분리·_tx_filters·README 정비
+디자인 일관성 정비 — Pretendard 실로딩 확인·EmptyState 중복 정리
+useToggleSet 훅으로 토글 중복 12개 통합, React Query 패널 3종 이관
+Admin Depts/Employees 하위 분리, 불량 처리 재설계 착수</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" ht="129.6" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-06 ~ 06-11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>모바일 구성 + 불량 처리 재설계</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>불량 처리 패널 전면 재설계 + KPI 2개로 압축·부서 범위 명시
+격리 목록 기본 스코프 '전체' 전환·배지·체크박스 UX 개선
+창고 지도 열 클릭·슬롯 번호·박스 편집 기능 — 실사용 기반 마련
+직원별 품목 순서 커스터마이징 (드래그 재정렬·초기화)
+모바일 핵심 화면 구성 — 하단 탭 4개 + 더보기 시트
+모바일 불량 처리 카트 방식 전환 — 다품목 일괄 처리 가능
+io_preview·창고지도·불량 카트 단위 테스트 신설
+코드 품질 정비 — verify_local 전체 통과 확인</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -4495,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5592,24 +5680,49 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="54" customHeight="1">
+    <row r="47" ht="67.5" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
           <t>2026-06-10 defect: 처리 패널 재설계 + 부서 접기/펼치기 UX
 2026-06-10 backend: unquarantine reason_category optional 처리
 2026-06-10 test: io-defect E2E 안정화 — 정상복귀 제출 셀렉터 모호성 해소
-2026-06-10 docs: 주간보고 6/7~6/10 갱신</t>
+2026-06-10 docs: 주간보고 6/8~6/10 갱신
+2026-06-10 frontend: trim BACKEND_INTERNAL_URL — .env 공백/CRL</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="67.5" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 하단 더보기 탭화·활성표시 강화 + 입출고 토스트 자동소멸
+2026-06-11 mobile: 불량 처리 데스크톱 정합 — 통합 처리 패널 모바일 신설
+2026-06-11 mobile: 입출고 저장슬롯 분리(손실 수정) + Step2 버튼 정합
+2026-06-11 mobile: 내역 상세 링크 날짜 자동 전환 + 뒤로가기 스택 pop
+2026-06-11 mobile: 내역 카드 최소 터치 높이(min-h-60) 보장</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -5626,7 +5739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F921"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35085,17 +35198,17 @@
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="C921" s="7" t="inlineStr">
         <is>
-          <t>30c4b20b</t>
+          <t>9cf2b98a</t>
         </is>
       </c>
       <c r="D921" s="8" t="inlineStr">
         <is>
-          <t>2026-06-10 docs: 주간보고 6/7~6/10 갱신</t>
+          <t>2026-06-10 docs: 주간보고 6/8~6/10 갱신</t>
         </is>
       </c>
       <c r="E921" s="7" t="inlineStr">
@@ -35104,6 +35217,1414 @@
         </is>
       </c>
       <c r="F921" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B922" s="15" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C922" s="15" t="inlineStr">
+        <is>
+          <t>d8eeaaa1</t>
+        </is>
+      </c>
+      <c r="D922" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 frontend: trim BACKEND_INTERNAL_URL — .env 공백/CRLF 로그인 먹통 방어</t>
+        </is>
+      </c>
+      <c r="E922" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F922" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B923" s="7" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C923" s="7" t="inlineStr">
+        <is>
+          <t>58141e34</t>
+        </is>
+      </c>
+      <c r="D923" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 warehouse: 박스 편집 UI + 재고 배치 시드</t>
+        </is>
+      </c>
+      <c r="E923" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F923" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B924" s="15" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="C924" s="15" t="inlineStr">
+        <is>
+          <t>2d03c451</t>
+        </is>
+      </c>
+      <c r="D924" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 defect: KPI 카드 결재대기·오늘처리 제거 (2개→격리중·1년이상만)</t>
+        </is>
+      </c>
+      <c r="E924" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F924" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B925" s="7" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C925" s="7" t="inlineStr">
+        <is>
+          <t>b2d7d795</t>
+        </is>
+      </c>
+      <c r="D925" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 frontend: 불량 KPI 건 단위·부서범위 부제·필터 연동</t>
+        </is>
+      </c>
+      <c r="E925" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F925" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B926" s="15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C926" s="15" t="inlineStr">
+        <is>
+          <t>ea571ec3</t>
+        </is>
+      </c>
+      <c r="D926" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 docs: 불량 피드백 5건 해결 반영 + 권동환 복귀일 정정</t>
+        </is>
+      </c>
+      <c r="E926" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F926" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B927" s="7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr">
+        <is>
+          <t>8904d1cf</t>
+        </is>
+      </c>
+      <c r="D927" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 refactor: DesktopLegacyShell→MesShell 이름 정리 + 복귀 리뷰 준비 문서 (#31)</t>
+        </is>
+      </c>
+      <c r="E927" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F927" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B928" s="15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="C928" s="15" t="inlineStr">
+        <is>
+          <t>40ac636f</t>
+        </is>
+      </c>
+      <c r="D928" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-10 defect: reason_category 필수 검증 제거 (선택 필드로 전환)</t>
+        </is>
+      </c>
+      <c r="E928" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F928" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B929" s="7" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C929" s="7" t="inlineStr">
+        <is>
+          <t>41da22bd</t>
+        </is>
+      </c>
+      <c r="D929" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 ux: 목록·테이블 줄 호버 하이라이트 일관 적용</t>
+        </is>
+      </c>
+      <c r="E929" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F929" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B930" s="19" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C930" s="19" t="inlineStr">
+        <is>
+          <t>f7f0b5ae</t>
+        </is>
+      </c>
+      <c r="D930" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 docs: 모바일 벤치마킹 리서치 문서 추가</t>
+        </is>
+      </c>
+      <c r="E930" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F930" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B931" s="19" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C931" s="19" t="inlineStr">
+        <is>
+          <t>90136f32</t>
+        </is>
+      </c>
+      <c r="D931" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 warehouse: 단품 입출고 판별 헬퍼 isSingleInlineSubType 추가</t>
+        </is>
+      </c>
+      <c r="E931" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F931" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B932" s="19" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C932" s="19" t="inlineStr">
+        <is>
+          <t>f5e80f9e</t>
+        </is>
+      </c>
+      <c r="D932" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 mobile: 입출고 스캔-우선 동선 + 단품 인라인 폼</t>
+        </is>
+      </c>
+      <c r="E932" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F932" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B933" s="19" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C933" s="19" t="inlineStr">
+        <is>
+          <t>16360a30</t>
+        </is>
+      </c>
+      <c r="D933" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 mobile: 주간보고 모바일 전용 뷰 신설</t>
+        </is>
+      </c>
+      <c r="E933" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F933" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B934" s="19" t="inlineStr">
+        <is>
+          <t>22:16</t>
+        </is>
+      </c>
+      <c r="C934" s="19" t="inlineStr">
+        <is>
+          <t>d5b92afe</t>
+        </is>
+      </c>
+      <c r="D934" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 mobile: 창고지도 모바일 뷰 신설</t>
+        </is>
+      </c>
+      <c r="E934" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F934" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B935" s="19" t="inlineStr">
+        <is>
+          <t>22:16</t>
+        </is>
+      </c>
+      <c r="C935" s="19" t="inlineStr">
+        <is>
+          <t>92517f6b</t>
+        </is>
+      </c>
+      <c r="D935" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 mobile: 하단 탭 4개로 축소 + 더보기 시트</t>
+        </is>
+      </c>
+      <c r="E935" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F935" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B936" s="19" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="C936" s="19" t="inlineStr">
+        <is>
+          <t>07d1d05d</t>
+        </is>
+      </c>
+      <c r="D936" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10 defect: 해제 reason_memo 선택 허용 — E2E 불량 복귀 복구</t>
+        </is>
+      </c>
+      <c r="E936" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F936" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B937" s="7" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="C937" s="7" t="inlineStr">
+        <is>
+          <t>b6f0ebab</t>
+        </is>
+      </c>
+      <c r="D937" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 하단 더보기 탭화·활성표시 강화 + 입출고 토스트 자동소멸</t>
+        </is>
+      </c>
+      <c r="E937" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F937" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B938" s="15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="C938" s="15" t="inlineStr">
+        <is>
+          <t>3964a2d3</t>
+        </is>
+      </c>
+      <c r="D938" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 불량 처리 데스크톱 정합 — 통합 처리 패널 모바일 신설</t>
+        </is>
+      </c>
+      <c r="E938" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F938" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B939" s="7" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C939" s="7" t="inlineStr">
+        <is>
+          <t>43224017</t>
+        </is>
+      </c>
+      <c r="D939" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 저장슬롯 분리(손실 수정) + Step2 버튼 정합</t>
+        </is>
+      </c>
+      <c r="E939" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F939" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B940" s="15" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C940" s="15" t="inlineStr">
+        <is>
+          <t>b826e06f</t>
+        </is>
+      </c>
+      <c r="D940" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 내역 상세 링크 날짜 자동 전환 + 뒤로가기 스택 pop</t>
+        </is>
+      </c>
+      <c r="E940" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F940" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B941" s="7" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C941" s="7" t="inlineStr">
+        <is>
+          <t>8ab8e8bb</t>
+        </is>
+      </c>
+      <c r="D941" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 내역 카드 최소 터치 높이(min-h-60) 보장</t>
+        </is>
+      </c>
+      <c r="E941" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F941" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B942" s="15" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C942" s="15" t="inlineStr">
+        <is>
+          <t>1a6c8e6a</t>
+        </is>
+      </c>
+      <c r="D942" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 대시보드 불량(DEFECT) 공정 필터 동작 복구</t>
+        </is>
+      </c>
+      <c r="E942" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F942" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B943" s="7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C943" s="7" t="inlineStr">
+        <is>
+          <t>31302638</t>
+        </is>
+      </c>
+      <c r="D943" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 관리 드릴다운 단일컬럼 가드 + 메시지 배너 sticky</t>
+        </is>
+      </c>
+      <c r="E943" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F943" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B944" s="15" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C944" s="15" t="inlineStr">
+        <is>
+          <t>c35bff1b</t>
+        </is>
+      </c>
+      <c r="D944" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: primitive 인라인 색 토큰화</t>
+        </is>
+      </c>
+      <c r="E944" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F944" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B945" s="7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="C945" s="7" t="inlineStr">
+        <is>
+          <t>9949c33e</t>
+        </is>
+      </c>
+      <c r="D945" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 알림 네비 탭 검증(딥링크 가드) + VALID_TAB_IDS 상수화</t>
+        </is>
+      </c>
+      <c r="E945" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F945" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B946" s="15" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C946" s="15" t="inlineStr">
+        <is>
+          <t>1bd56575</t>
+        </is>
+      </c>
+      <c r="D946" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 작성 중 섹션 이탈 가드</t>
+        </is>
+      </c>
+      <c r="E946" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F946" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B947" s="7" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="C947" s="7" t="inlineStr">
+        <is>
+          <t>afef8101</t>
+        </is>
+      </c>
+      <c r="D947" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 서브탭(승인함·장바구니 등) 터치 타깃 44px 보장</t>
+        </is>
+      </c>
+      <c r="E947" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F947" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B948" s="15" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C948" s="15" t="inlineStr">
+        <is>
+          <t>a5e8b76e</t>
+        </is>
+      </c>
+      <c r="D948" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 인수인계 섹션 모바일 노출</t>
+        </is>
+      </c>
+      <c r="E948" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F948" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B949" s="7" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C949" s="7" t="inlineStr">
+        <is>
+          <t>55f7aab5</t>
+        </is>
+      </c>
+      <c r="D949" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 불량 격리·바로폐기 다품목 카트 모바일 신설(MobileDefectCartFlow)</t>
+        </is>
+      </c>
+      <c r="E949" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F949" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B950" s="15" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C950" s="15" t="inlineStr">
+        <is>
+          <t>419a8d1a</t>
+        </is>
+      </c>
+      <c r="D950" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 불량 허브 격리추가·바로폐기를 다품목 카트로 배선</t>
+        </is>
+      </c>
+      <c r="E950" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F950" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B951" s="7" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C951" s="7" t="inlineStr">
+        <is>
+          <t>0d3be79d</t>
+        </is>
+      </c>
+      <c r="D951" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 불량 화면 품목/모델 로드 + defaultSource(데스크톱 분리 패턴)</t>
+        </is>
+      </c>
+      <c r="E951" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F951" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B952" s="15" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C952" s="15" t="inlineStr">
+        <is>
+          <t>8da005f1</t>
+        </is>
+      </c>
+      <c r="D952" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: DefectHubPanel 테스트 — 격리추가/바로폐기 카트 전환 검증</t>
+        </is>
+      </c>
+      <c r="E952" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F952" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B953" s="7" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="C953" s="7" t="inlineStr">
+        <is>
+          <t>37943d31</t>
+        </is>
+      </c>
+      <c r="D953" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 관리 4섹션 크래시 수정 + 마스터-디테일 단일컬럼</t>
+        </is>
+      </c>
+      <c r="E953" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F953" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B954" s="15" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C954" s="15" t="inlineStr">
+        <is>
+          <t>720114b4</t>
+        </is>
+      </c>
+      <c r="D954" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 위저드 헤더가 셸 헤더 덮던 문제 수정</t>
+        </is>
+      </c>
+      <c r="E954" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F954" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B955" s="7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="C955" s="7" t="inlineStr">
+        <is>
+          <t>0a5551d0</t>
+        </is>
+      </c>
+      <c r="D955" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 섹션 탭 과밀 해소 — 모바일 가로 스크롤</t>
+        </is>
+      </c>
+      <c r="E955" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F955" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B956" s="15" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C956" s="15" t="inlineStr">
+        <is>
+          <t>e4338316</t>
+        </is>
+      </c>
+      <c r="D956" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 대시보드 생산가능 패널 칩↔자세히보기 겹침 수정</t>
+        </is>
+      </c>
+      <c r="E956" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F956" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B957" s="7" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C957" s="7" t="inlineStr">
+        <is>
+          <t>de2cf545</t>
+        </is>
+      </c>
+      <c r="D957" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 비율 폴리시 — 알림 시간 가독성·패널 폭 안전·카트 삭제 터치</t>
+        </is>
+      </c>
+      <c r="E957" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F957" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B958" s="15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C958" s="15" t="inlineStr">
+        <is>
+          <t>940e6c3f</t>
+        </is>
+      </c>
+      <c r="D958" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 관리(admin) 화면을 모바일에서 제거</t>
+        </is>
+      </c>
+      <c r="E958" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F958" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B959" s="7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C959" s="7" t="inlineStr">
+        <is>
+          <t>9850f4ff</t>
+        </is>
+      </c>
+      <c r="D959" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 입출고 Step4 라인 세로글자 수정 — IoLineRow 반응형</t>
+        </is>
+      </c>
+      <c r="E959" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F959" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B960" s="15" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C960" s="15" t="inlineStr">
+        <is>
+          <t>0eb4b52a</t>
+        </is>
+      </c>
+      <c r="D960" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 폴리시 — 불량 BOM 트리 품목명 줄바꿈 + 입출고 picker 필터 폭</t>
+        </is>
+      </c>
+      <c r="E960" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F960" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B961" s="7" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C961" s="7" t="inlineStr">
+        <is>
+          <t>2b46b2ff</t>
+        </is>
+      </c>
+      <c r="D961" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 비율 정리 — 불량 피커 필터·BOM 하위트리 폭·내역 캘린더 셀높이 반응형</t>
+        </is>
+      </c>
+      <c r="E961" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F961" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B962" s="15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C962" s="15" t="inlineStr">
+        <is>
+          <t>9f8a434b</t>
+        </is>
+      </c>
+      <c r="D962" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 불량 화면이 화면 폭을 꽉 채우도록 수정 (w-full)</t>
+        </is>
+      </c>
+      <c r="E962" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F962" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B963" s="7" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C963" s="7" t="inlineStr">
+        <is>
+          <t>147ac4e5</t>
+        </is>
+      </c>
+      <c r="D963" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 품목 피커 목록이 화면 폭을 꽉 채우도록 colgroup 반응형화</t>
+        </is>
+      </c>
+      <c r="E963" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F963" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B964" s="15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C964" s="15" t="inlineStr">
+        <is>
+          <t>9c9c23d0</t>
+        </is>
+      </c>
+      <c r="D964" s="16" t="inlineStr">
+        <is>
+          <t>@ 2026-06-11 docs: ERD를 발표 스타일 HTML 문서로 추가</t>
+        </is>
+      </c>
+      <c r="E964" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F964" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B965" s="7" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="C965" s="7" t="inlineStr">
+        <is>
+          <t>cb357d2b</t>
+        </is>
+      </c>
+      <c r="D965" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 mobile: 원시 라벨·JSON 노출 정리 + 대시보드 현재고 우측정렬</t>
+        </is>
+      </c>
+      <c r="E965" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F965" s="7" t="inlineStr">
         <is>
           <t>근무</t>
         </is>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>964건 (회사 기간 670건)</t>
+          <t>1044건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>333건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>342건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>77 / 87개 (89%)</t>
+          <t>78 / 88개 (89%)</t>
         </is>
       </c>
     </row>
@@ -2025,27 +2025,144 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■■■■■■■■■■■■■</t>
+            <t>■■■■■■■■■■■■■■■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (29)</t>
+            <t xml:space="preserve">  (31)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-12  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (10)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-15  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (31)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-16  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-17  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (26)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="59">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
@@ -2053,6 +2170,7 @@
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A54:E54"/>
@@ -2093,6 +2211,7 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2105,7 +2224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2438,7 +2557,34 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>88</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" ht="129.6" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12 ~ 06-19</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>입출고 취소 + 모바일 탭바 + 현장 기준 개선</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>입출고 취소 기능 신설 — 생산·분해 포함 모든 유형 취소, 원본 기록 보존
+생산 가능 수량 표시 AF 단위 기준 개선 중 (출하준비·빠른조립·총생산 구분)
+인수인계서 임시저장 + 수신 권한을 실제 수령 부서로 제한
+주간보고 화면 집계 오류 수정 (입고 건 생산 실적 혼입 제거)
+데스크톱 빠른 작업 탭 튕김·검색 깜빡임 수정, 창고 관리 탭 통합
+모바일 하단 탭바 슬라이딩 pill 디자인 완성
+모바일 화면 전반 정비 진행 중 (더보기 탭 전환·불량 허브·저장 확인)
+SOLO 테스트 지원으로 개발 시간 제한적</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2452,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4356,27 +4502,27 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="n">
+      <c r="A80" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E80" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>입출고 취소 기능</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>생산·분해 포함 모든 유형 취소 — 원본 보존·재고 역방향 복원</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4532,12 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>불량 처리 흐름 Phase 2</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -4401,7 +4547,7 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>부서 결재·집계·자동화</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4557,12 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>역할별 접근 권한 연동</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
@@ -4426,7 +4572,7 @@
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+          <t>부서 결재·집계·자동화</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4582,12 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -4451,7 +4597,7 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>재고 가용성 계산 고도화</t>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
@@ -4461,12 +4607,12 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -4476,7 +4622,7 @@
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4632,12 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>외부 접근 환경 구성</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -4499,7 +4645,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr"/>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n">
@@ -4507,12 +4657,12 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>발주 관리</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -4528,12 +4678,12 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>생산 실적 / 원가 관리</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -4541,11 +4691,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>사장님 요청 — 검토 중</t>
-        </is>
-      </c>
+      <c r="E87" s="13" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n">
@@ -4553,20 +4699,45 @@
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
+      <c r="D89" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -4583,7 +4754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5711,7 +5882,7 @@
         </is>
       </c>
       <c r="B48" s="15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
@@ -5723,6 +5894,102 @@
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="67.5" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12 docs: 주간보고 06/06~06/12 전사공유 버전 갱신 + 피드백 회신 초안
+2026-06-12 mobile: 불량 카트 멱등성 보강 + 쓰기 타임아웃
+2026-06-12 docs: 주간보고 협조요청 문구 보완 (연습용 데이터 안내)
+2026-06-10 docs: 이형진 피드백 2건 등록 (대시보드 BOM 하위·빠른작업)
+2026-06-12 frontend: 대시보드 BOM 펼침 + 빠른작업 입고/출고 분리 (이형진 피드백)</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="67.5" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 대시보드 BOM 하위구성 좁은 패널 표시 정합
+2026-06-15 frontend: 빠른작업 입출고 진입 개선 (탭 튕김·선택품목 검색/깜빡·낱개 Step
+Merge branch 'feat/mobile-desktop-parity'
+2026-06-15 ux: 입출고내역 "수량보정 출고" 레이블 → "출고"
+2026-06-15 frontend: 대시보드·재고 상세 우측 패널 최근 이력 제거</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="67.5" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 backend: 부분 승인 알림 제거 (현 단일단계 정책상 미도달)
+2026-06-16 fix: export 테스트 시간대 의존 flake 수정 (UTC 기준 범위)
+2026-06-16 mes: 인수인계 인수 확인 권한을 받는 부서(고압/진공) 소속으로 제한
+2026-06-16 weekly: 생산=PRODUCE 전용·입고 분리·전주재고 정확화·인쇄/CSV 제거
+2026-06-16 docs: 피드백 기록 정리 (이계숙 해결·권동환 보류·이필욱 커밋해시)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="67.5" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 더보기 탭 시 pill 이동 후 시트 펼침 딜레이
+2026-06-17 mobile: 바텀시트 본문 탭 시 화면 깜빡임 수정
+2026-06-17 test: io E2E 헬퍼 보이는 요소 선택으로 모바일 숨김 중복 회피
+2026-06-17 docs: add mobile PC flow parity review
+2026-06-17 docs: remove review screenshots</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -5739,7 +6006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F965"/>
+  <dimension ref="A1:F1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36630,6 +36897,2566 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B966" s="15" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C966" s="15" t="inlineStr">
+        <is>
+          <t>3011db9c</t>
+        </is>
+      </c>
+      <c r="D966" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-11 backend: 부서 enum 누출 원인 수정 + 알림 본문 라벨 + 더티 정리 스크립트</t>
+        </is>
+      </c>
+      <c r="E966" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F966" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B967" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C967" s="7" t="inlineStr">
+        <is>
+          <t>ed806192</t>
+        </is>
+      </c>
+      <c r="D967" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11 docs: 주간보고 06/06~06/11 전사공유 버전 + 개발현황 5/30~6/11 행 추가</t>
+        </is>
+      </c>
+      <c r="E967" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F967" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B968" s="15" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C968" s="15" t="inlineStr">
+        <is>
+          <t>d01ad0a4</t>
+        </is>
+      </c>
+      <c r="D968" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12 docs: 주간보고 06/06~06/12 전사공유 버전 갱신 + 피드백 회신 초안</t>
+        </is>
+      </c>
+      <c r="E968" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F968" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B969" s="7" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C969" s="7" t="inlineStr">
+        <is>
+          <t>144131ed</t>
+        </is>
+      </c>
+      <c r="D969" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12 mobile: 불량 카트 멱등성 보강 + 쓰기 타임아웃</t>
+        </is>
+      </c>
+      <c r="E969" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F969" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B970" s="15" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C970" s="15" t="inlineStr">
+        <is>
+          <t>10670054</t>
+        </is>
+      </c>
+      <c r="D970" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12 docs: 주간보고 협조요청 문구 보완 (연습용 데이터 안내)</t>
+        </is>
+      </c>
+      <c r="E970" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F970" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B971" s="7" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C971" s="7" t="inlineStr">
+        <is>
+          <t>89d32c24</t>
+        </is>
+      </c>
+      <c r="D971" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10 docs: 이형진 피드백 2건 등록 (대시보드 BOM 하위·빠른작업)</t>
+        </is>
+      </c>
+      <c r="E971" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F971" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B972" s="15" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="C972" s="15" t="inlineStr">
+        <is>
+          <t>1b4b9322</t>
+        </is>
+      </c>
+      <c r="D972" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12 frontend: 대시보드 BOM 펼침 + 빠른작업 입고/출고 분리 (이형진 피드백)</t>
+        </is>
+      </c>
+      <c r="E972" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F972" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B973" s="7" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C973" s="7" t="inlineStr">
+        <is>
+          <t>730dea7a</t>
+        </is>
+      </c>
+      <c r="D973" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12 backend: pending 고아 방지 — 재고 리셋 전 미결 요청 자동 취소</t>
+        </is>
+      </c>
+      <c r="E973" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F973" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B974" s="15" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C974" s="15" t="inlineStr">
+        <is>
+          <t>85033260</t>
+        </is>
+      </c>
+      <c r="D974" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12 history: 요청/승인 시각 표시 + DB client_request_id 컬럼 추가</t>
+        </is>
+      </c>
+      <c r="E974" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F974" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B975" s="7" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="C975" s="7" t="inlineStr">
+        <is>
+          <t>44ceb2bf</t>
+        </is>
+      </c>
+      <c r="D975" s="8" t="inlineStr">
+        <is>
+          <t>@ 2026-06-12 backend: 고아 예약 일회성 정리 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="E975" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F975" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B976" s="15" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C976" s="15" t="inlineStr">
+        <is>
+          <t>c4f8901c</t>
+        </is>
+      </c>
+      <c r="D976" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12 docs: 주간보고 06/06~06/12 항목 보강 + 발송본 동기화</t>
+        </is>
+      </c>
+      <c r="E976" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F976" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B977" s="7" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C977" s="7" t="inlineStr">
+        <is>
+          <t>af5e5993</t>
+        </is>
+      </c>
+      <c r="D977" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12 docs: 피드백 처리방침 반영 (정렬 해결·창고지도 해결·바코드/불량인쇄 보류)</t>
+        </is>
+      </c>
+      <c r="E977" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F977" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B978" s="15" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C978" s="15" t="inlineStr">
+        <is>
+          <t>d1a2502b</t>
+        </is>
+      </c>
+      <c r="D978" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 대시보드 BOM 하위구성 좁은 패널 표시 정합</t>
+        </is>
+      </c>
+      <c r="E978" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F978" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B979" s="7" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="C979" s="7" t="inlineStr">
+        <is>
+          <t>2e2b5491</t>
+        </is>
+      </c>
+      <c r="D979" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 빠른작업 입출고 진입 개선 (탭 튕김·선택품목 검색/깜빡·낱개 Step4)</t>
+        </is>
+      </c>
+      <c r="E979" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F979" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B980" s="15" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C980" s="15" t="inlineStr">
+        <is>
+          <t>32932a57</t>
+        </is>
+      </c>
+      <c r="D980" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'feat/mobile-desktop-parity'</t>
+        </is>
+      </c>
+      <c r="E980" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F980" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B981" s="7" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C981" s="7" t="inlineStr">
+        <is>
+          <t>c87748c9</t>
+        </is>
+      </c>
+      <c r="D981" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 ux: 입출고내역 "수량보정 출고" 레이블 → "출고"</t>
+        </is>
+      </c>
+      <c r="E981" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F981" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B982" s="15" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C982" s="15" t="inlineStr">
+        <is>
+          <t>6a35b87e</t>
+        </is>
+      </c>
+      <c r="D982" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 대시보드·재고 상세 우측 패널 최근 이력 제거</t>
+        </is>
+      </c>
+      <c r="E982" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F982" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B983" s="7" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C983" s="7" t="inlineStr">
+        <is>
+          <t>6025cce7</t>
+        </is>
+      </c>
+      <c r="D983" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 admin: 창고 관리 메뉴 통합(구조 편집·위치 배정 탭) + 품목 관리 설명 "BOM 관리" 문구 제거</t>
+        </is>
+      </c>
+      <c r="E983" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F983" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B984" s="15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C984" s="15" t="inlineStr">
+        <is>
+          <t>0afa5820</t>
+        </is>
+      </c>
+      <c r="D984" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 직원 등급(level) 제거 — 결재 권한을 창고/부서 role 기준으로 일원화</t>
+        </is>
+      </c>
+      <c r="E984" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F984" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B985" s="7" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C985" s="7" t="inlineStr">
+        <is>
+          <t>72aed411</t>
+        </is>
+      </c>
+      <c r="D985" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 입출고 탭 저장 경고 오동작 수정 — 드래프트 복원·자동저장 후 미경고</t>
+        </is>
+      </c>
+      <c r="E985" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F985" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B986" s="15" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C986" s="15" t="inlineStr">
+        <is>
+          <t>62bcb91e</t>
+        </is>
+      </c>
+      <c r="D986" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 거래 취소 기능 신설(내역 유지+재고 롤백) + 창고/부서 수량 분리 표시</t>
+        </is>
+      </c>
+      <c r="E986" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F986" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B987" s="7" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C987" s="7" t="inlineStr">
+        <is>
+          <t>051145ee</t>
+        </is>
+      </c>
+      <c r="D987" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 docs: 김현우 피드백 9건 해결 표기 갱신</t>
+        </is>
+      </c>
+      <c r="E987" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F987" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B988" s="15" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="C988" s="15" t="inlineStr">
+        <is>
+          <t>3d8f1bd0</t>
+        </is>
+      </c>
+      <c r="D988" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'feat/self-feedback-2026-06-15'</t>
+        </is>
+      </c>
+      <c r="E988" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F988" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B989" s="7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C989" s="7" t="inlineStr">
+        <is>
+          <t>995c23d3</t>
+        </is>
+      </c>
+      <c r="D989" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 docs: align archive docs with current repo layout</t>
+        </is>
+      </c>
+      <c r="E989" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F989" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B990" s="15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C990" s="15" t="inlineStr">
+        <is>
+          <t>9a9cc908</t>
+        </is>
+      </c>
+      <c r="D990" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: BOM 가계도 인터랙티브 그래프 HTML 생성기 추가</t>
+        </is>
+      </c>
+      <c r="E990" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F990" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B991" s="7" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C991" s="7" t="inlineStr">
+        <is>
+          <t>b60fd022</t>
+        </is>
+      </c>
+      <c r="D991" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 입출고 탭 저장 경고 오동작 수정 — 수정했을 때만 경고</t>
+        </is>
+      </c>
+      <c r="E991" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F991" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B992" s="15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C992" s="15" t="inlineStr">
+        <is>
+          <t>56a06426</t>
+        </is>
+      </c>
+      <c r="D992" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 거래 취소 전면 재구현 — 재고 효과 기록·일반 역재생</t>
+        </is>
+      </c>
+      <c r="E992" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F992" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B993" s="7" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C993" s="7" t="inlineStr">
+        <is>
+          <t>6317a7a1</t>
+        </is>
+      </c>
+      <c r="D993" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 docs: 커밋 메시지 셸 안전 규칙 추가 (Bash에서 PowerShell here-string 금지)</t>
+        </is>
+      </c>
+      <c r="E993" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F993" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B994" s="15" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C994" s="15" t="inlineStr">
+        <is>
+          <t>01df1e2f</t>
+        </is>
+      </c>
+      <c r="D994" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'feat/transaction-cancel-rework'</t>
+        </is>
+      </c>
+      <c r="E994" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F994" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B995" s="7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C995" s="7" t="inlineStr">
+        <is>
+          <t>bc136625</t>
+        </is>
+      </c>
+      <c r="D995" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 입출고 저장 경고 오동작 수정 2건 — 자동저장 제거·빈 카트 이탈 팝업 누락</t>
+        </is>
+      </c>
+      <c r="E995" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F995" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B996" s="15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C996" s="15" t="inlineStr">
+        <is>
+          <t>60dbdc0e</t>
+        </is>
+      </c>
+      <c r="D996" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 거래 취소 전면 재구현 — 재고 효과 기록·일반 역재생</t>
+        </is>
+      </c>
+      <c r="E996" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F996" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B997" s="7" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C997" s="7" t="inlineStr">
+        <is>
+          <t>fa6aae4f</t>
+        </is>
+      </c>
+      <c r="D997" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: BOM 가계도 개선 — 레이아웃·노드크기·클릭 하이라이트</t>
+        </is>
+      </c>
+      <c r="E997" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F997" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B998" s="15" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C998" s="15" t="inlineStr">
+        <is>
+          <t>8a299cb4</t>
+        </is>
+      </c>
+      <c r="D998" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 창고 탭 섹션 레이아웃 쪼그라듦 수정 — h-full→flex-1, 탭래퍼 flex 추가</t>
+        </is>
+      </c>
+      <c r="E998" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F998" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B999" s="7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C999" s="7" t="inlineStr">
+        <is>
+          <t>278b28e4</t>
+        </is>
+      </c>
+      <c r="D999" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15 docs: AF 생산 가능 수량 재정의 문서 추가</t>
+        </is>
+      </c>
+      <c r="E999" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F999" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1000" s="19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C1000" s="19" t="inlineStr">
+        <is>
+          <t>00c89516</t>
+        </is>
+      </c>
+      <c r="D1000" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 생산 가능 수량 AF 기준 재정의 (legacy 병행)</t>
+        </is>
+      </c>
+      <c r="E1000" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1000" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1001" s="19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C1001" s="19" t="inlineStr">
+        <is>
+          <t>e8867ada</t>
+        </is>
+      </c>
+      <c r="D1001" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 생산 가능 수량 AF 기준 3수량 표시</t>
+        </is>
+      </c>
+      <c r="E1001" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1001" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1002" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1002" s="19" t="inlineStr">
+        <is>
+          <t>f6612849</t>
+        </is>
+      </c>
+      <c r="D1002" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 모든 거래 경로에 작업자 사번(producer_employee_id) 기록</t>
+        </is>
+      </c>
+      <c r="E1002" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1002" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1003" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1003" s="19" t="inlineStr">
+        <is>
+          <t>7222e356</t>
+        </is>
+      </c>
+      <c r="D1003" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 외부 감사 CSV에 처리자사번 컬럼 추가</t>
+        </is>
+      </c>
+      <c r="E1003" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1003" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1004" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1004" s="19" t="inlineStr">
+        <is>
+          <t>1ea1c0a0</t>
+        </is>
+      </c>
+      <c r="D1004" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 재고 리셋 스크립트에 미결 요청 고아 방지 가드</t>
+        </is>
+      </c>
+      <c r="E1004" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1004" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1005" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1005" s="19" t="inlineStr">
+        <is>
+          <t>815393f2</t>
+        </is>
+      </c>
+      <c r="D1005" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 backend: 부분 승인 시 다음 결재자 알림 + 리셋 가드 docstring</t>
+        </is>
+      </c>
+      <c r="E1005" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1005" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1006" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1006" s="19" t="inlineStr">
+        <is>
+          <t>baf92a73</t>
+        </is>
+      </c>
+      <c r="D1006" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 mes: 인수인계서 임시저장(draft) 단계 추가</t>
+        </is>
+      </c>
+      <c r="E1006" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1006" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1007" s="19" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C1007" s="19" t="inlineStr">
+        <is>
+          <t>5f9573b6</t>
+        </is>
+      </c>
+      <c r="D1007" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 chore: OpenAPI baseline 재생성 (사번 필드·인수인계 draft 반영)</t>
+        </is>
+      </c>
+      <c r="E1007" s="19" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1007" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1008" s="19" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C1008" s="19" t="inlineStr">
+        <is>
+          <t>b12a135c</t>
+        </is>
+      </c>
+      <c r="D1008" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-15 frontend: 생산 가능 수량 패널·모달 모델별 표시</t>
+        </is>
+      </c>
+      <c r="E1008" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1008" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1009" s="7" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C1009" s="7" t="inlineStr">
+        <is>
+          <t>a269a7bf</t>
+        </is>
+      </c>
+      <c r="D1009" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 backend: 부분 승인 알림 제거 (현 단일단계 정책상 미도달)</t>
+        </is>
+      </c>
+      <c r="E1009" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1009" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1010" s="15" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C1010" s="15" t="inlineStr">
+        <is>
+          <t>d5a6dfbc</t>
+        </is>
+      </c>
+      <c r="D1010" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16 fix: export 테스트 시간대 의존 flake 수정 (UTC 기준 범위)</t>
+        </is>
+      </c>
+      <c r="E1010" s="15" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1010" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1011" s="7" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="C1011" s="7" t="inlineStr">
+        <is>
+          <t>f4eb3ac1</t>
+        </is>
+      </c>
+      <c r="D1011" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 mes: 인수인계 인수 확인 권한을 받는 부서(고압/진공) 소속으로 제한</t>
+        </is>
+      </c>
+      <c r="E1011" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1011" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1012" s="15" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C1012" s="15" t="inlineStr">
+        <is>
+          <t>d1592d0d</t>
+        </is>
+      </c>
+      <c r="D1012" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16 weekly: 생산=PRODUCE 전용·입고 분리·전주재고 정확화·인쇄/CSV 제거</t>
+        </is>
+      </c>
+      <c r="E1012" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1012" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1013" s="7" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C1013" s="7" t="inlineStr">
+        <is>
+          <t>3ccec937</t>
+        </is>
+      </c>
+      <c r="D1013" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 docs: 피드백 기록 정리 (이계숙 해결·권동환 보류·이필욱 커밋해시)</t>
+        </is>
+      </c>
+      <c r="E1013" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1013" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1014" s="15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C1014" s="15" t="inlineStr">
+        <is>
+          <t>9f6ff3d5</t>
+        </is>
+      </c>
+      <c r="D1014" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16 docs: 이지훈 주간보고 피드백 2건 해결 반영</t>
+        </is>
+      </c>
+      <c r="E1014" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1014" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1015" s="7" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1015" s="7" t="inlineStr">
+        <is>
+          <t>35faec22</t>
+        </is>
+      </c>
+      <c r="D1015" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 ux: 모바일 하단 탭바 플로팅 pill 디자인 + UI 감사 수정</t>
+        </is>
+      </c>
+      <c r="E1015" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1015" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1016" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C1016" s="15" t="inlineStr">
+        <is>
+          <t>ffa245f3</t>
+        </is>
+      </c>
+      <c r="D1016" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16 ux: 모바일 탭바 활성 버튼 사각형 inset 그림자 제거</t>
+        </is>
+      </c>
+      <c r="E1016" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1016" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1017" s="7" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="C1017" s="7" t="inlineStr">
+        <is>
+          <t>32c72ab4</t>
+        </is>
+      </c>
+      <c r="D1017" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 chore: 모바일 하단 탭바 동결 명시</t>
+        </is>
+      </c>
+      <c r="E1017" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1017" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1018" s="15" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C1018" s="15" t="inlineStr">
+        <is>
+          <t>4b64173a</t>
+        </is>
+      </c>
+      <c r="D1018" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16 mobile: 모바일 렌더링 이탈 5건 수정</t>
+        </is>
+      </c>
+      <c r="E1018" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1018" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1019" s="7" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C1019" s="7" t="inlineStr">
+        <is>
+          <t>e662c2a4</t>
+        </is>
+      </c>
+      <c r="D1019" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16 mobile: 하단 탭바 슬라이딩 pill 애니메이션</t>
+        </is>
+      </c>
+      <c r="E1019" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1019" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1020" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1020" s="15" t="inlineStr">
+        <is>
+          <t>6a031675</t>
+        </is>
+      </c>
+      <c r="D1020" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 더보기 탭 시 pill 이동 후 시트 펼침 딜레이</t>
+        </is>
+      </c>
+      <c r="E1020" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1020" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1021" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1021" s="7" t="inlineStr">
+        <is>
+          <t>3e23dc22</t>
+        </is>
+      </c>
+      <c r="D1021" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 바텀시트 본문 탭 시 화면 깜빡임 수정</t>
+        </is>
+      </c>
+      <c r="E1021" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1021" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1022" s="15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C1022" s="15" t="inlineStr">
+        <is>
+          <t>9c1f86f7</t>
+        </is>
+      </c>
+      <c r="D1022" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 test: io E2E 헬퍼 보이는 요소 선택으로 모바일 숨김 중복 회피</t>
+        </is>
+      </c>
+      <c r="E1022" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1022" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1023" s="7" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C1023" s="7" t="inlineStr">
+        <is>
+          <t>f4ffc3d6</t>
+        </is>
+      </c>
+      <c r="D1023" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 docs: add mobile PC flow parity review</t>
+        </is>
+      </c>
+      <c r="E1023" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1023" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1024" s="15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C1024" s="15" t="inlineStr">
+        <is>
+          <t>d4968d01</t>
+        </is>
+      </c>
+      <c r="D1024" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 docs: remove review screenshots</t>
+        </is>
+      </c>
+      <c r="E1024" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1024" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1025" s="7" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C1025" s="7" t="inlineStr">
+        <is>
+          <t>de0c354c</t>
+        </is>
+      </c>
+      <c r="D1025" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 불량 처리 실행 버튼 하단 고정(StickyFooter)</t>
+        </is>
+      </c>
+      <c r="E1025" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1025" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1026" s="15" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C1026" s="15" t="inlineStr">
+        <is>
+          <t>496945b9</t>
+        </is>
+      </c>
+      <c r="D1026" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 더보기 BottomSheet → 전폭 탭 전환</t>
+        </is>
+      </c>
+      <c r="E1026" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1026" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1027" s="7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C1027" s="7" t="inlineStr">
+        <is>
+          <t>52fbdc5b</t>
+        </is>
+      </c>
+      <c r="D1027" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 불량 허브 첫 화면에 KPI·격리목록 노출</t>
+        </is>
+      </c>
+      <c r="E1027" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1027" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1028" s="15" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C1028" s="15" t="inlineStr">
+        <is>
+          <t>bb68c546</t>
+        </is>
+      </c>
+      <c r="D1028" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 Step1 진행 단계 안내 추가</t>
+        </is>
+      </c>
+      <c r="E1028" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1028" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1029" s="7" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="C1029" s="7" t="inlineStr">
+        <is>
+          <t>8b5713c2</t>
+        </is>
+      </c>
+      <c r="D1029" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 대시보드 생산가능 현황 기본 접힘</t>
+        </is>
+      </c>
+      <c r="E1029" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1029" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1030" s="15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C1030" s="15" t="inlineStr">
+        <is>
+          <t>8ffeecfe</t>
+        </is>
+      </c>
+      <c r="D1030" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 Step3 품목명 모바일 2줄 표시</t>
+        </is>
+      </c>
+      <c r="E1030" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1030" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1031" s="7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C1031" s="7" t="inlineStr">
+        <is>
+          <t>ec7e510e</t>
+        </is>
+      </c>
+      <c r="D1031" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 test: io-defect E2E dual-shell 보이는 요소 필터</t>
+        </is>
+      </c>
+      <c r="E1031" s="7" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1031" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1032" s="15" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="C1032" s="15" t="inlineStr">
+        <is>
+          <t>ce4aa000</t>
+        </is>
+      </c>
+      <c r="D1032" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 frontend: 데스크톱 사이드바 메뉴 순서 조정</t>
+        </is>
+      </c>
+      <c r="E1032" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1032" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1033" s="7" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C1033" s="7" t="inlineStr">
+        <is>
+          <t>bae1ebc1</t>
+        </is>
+      </c>
+      <c r="D1033" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 Step1 진행 안내 블록 제거</t>
+        </is>
+      </c>
+      <c r="E1033" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1033" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1034" s="15" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C1034" s="15" t="inlineStr">
+        <is>
+          <t>b942fb07</t>
+        </is>
+      </c>
+      <c r="D1034" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 스캔 시작 버튼 UI 숨김(코드 유지)</t>
+        </is>
+      </c>
+      <c r="E1034" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1034" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1035" s="7" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="C1035" s="7" t="inlineStr">
+        <is>
+          <t>fbc3409c</t>
+        </is>
+      </c>
+      <c r="D1035" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 대시보드 필터 sticky 밖으로 분리(목록 가림 해소)</t>
+        </is>
+      </c>
+      <c r="E1035" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1035" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1036" s="15" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C1036" s="15" t="inlineStr">
+        <is>
+          <t>2b0097f1</t>
+        </is>
+      </c>
+      <c r="D1036" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 생산 가능 현황 헤더 정리·상태 배지·라벨 통일</t>
+        </is>
+      </c>
+      <c r="E1036" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1036" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1037" s="7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C1037" s="7" t="inlineStr">
+        <is>
+          <t>dbade552</t>
+        </is>
+      </c>
+      <c r="D1037" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 진행 바 가독성 개선·헤더 톤 정리</t>
+        </is>
+      </c>
+      <c r="E1037" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1037" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1038" s="15" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C1038" s="15" t="inlineStr">
+        <is>
+          <t>fdca45f5</t>
+        </is>
+      </c>
+      <c r="D1038" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 Step1·2 버튼 화면 높이 균등 분할</t>
+        </is>
+      </c>
+      <c r="E1038" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1038" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1039" s="7" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1039" s="7" t="inlineStr">
+        <is>
+          <t>3f0afd90</t>
+        </is>
+      </c>
+      <c r="D1039" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 섹션 탭 모바일 grid 균등분할</t>
+        </is>
+      </c>
+      <c r="E1039" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1039" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1040" s="15" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C1040" s="15" t="inlineStr">
+        <is>
+          <t>9ff0c232</t>
+        </is>
+      </c>
+      <c r="D1040" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: Step4 안내문구 모바일 숨김·제출확인 하단 고정</t>
+        </is>
+      </c>
+      <c r="E1040" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1040" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1041" s="7" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1041" s="7" t="inlineStr">
+        <is>
+          <t>eafc29b6</t>
+        </is>
+      </c>
+      <c r="D1041" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: Step3 드롭다운 전폭·수량 조정 버튼 하단 고정</t>
+        </is>
+      </c>
+      <c r="E1041" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1041" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1042" s="15" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C1042" s="15" t="inlineStr">
+        <is>
+          <t>eebbb76c</t>
+        </is>
+      </c>
+      <c r="D1042" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 빠른 작업 출고 빨강·서브옵션 전폭 파스텔(모바일 분기)</t>
+        </is>
+      </c>
+      <c r="E1042" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1042" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1043" s="7" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C1043" s="7" t="inlineStr">
+        <is>
+          <t>01c278d5</t>
+        </is>
+      </c>
+      <c r="D1043" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: Step4 수량 버튼 터치 타깃 확대·재고/휴지통 배치 정리</t>
+        </is>
+      </c>
+      <c r="E1043" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1043" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1044" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1044" s="15" t="inlineStr">
+        <is>
+          <t>e1a75929</t>
+        </is>
+      </c>
+      <c r="D1044" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 헤더 상태 칩 도입(info는 칩·에러만 토스트)</t>
+        </is>
+      </c>
+      <c r="E1044" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1044" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1045" s="7" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="C1045" s="7" t="inlineStr">
+        <is>
+          <t>009aaa30</t>
+        </is>
+      </c>
+      <c r="D1045" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17 mobile: 입출고 작성 중 하단 네비 이탈 시 저장 확인 시트</t>
+        </is>
+      </c>
+      <c r="E1045" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1045" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1044건 (회사 기간 670건)</t>
+          <t>1173건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>342건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>357건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>78 / 88개 (89%)</t>
+          <t>86 / 96개 (90%)</t>
         </is>
       </c>
     </row>
@@ -2152,8 +2152,191 @@
         </is>
       </c>
     </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-19  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (16)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-22  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (45)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-23  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (34)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-24  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-25  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (15)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-26  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (8)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="65">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -2161,6 +2344,7 @@
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A11:E11"/>
@@ -2171,6 +2355,7 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A54:E54"/>
@@ -2180,6 +2365,7 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A56:E56"/>
@@ -2204,15 +2390,18 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2224,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2584,7 +2773,33 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>78</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" ht="113.4" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20 ~ 06-26</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>전환 안전·피드백 반영</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>창고 박스 단위 재고 관리 기반 구축
+생산 가능 수량 기준 및 표시 방식 개선
+재고 전환 전 운영 안전장치 강화
+입출고 승인 전 수정·낱개 출고 집계 정확도 개선
+알림 삭제 기능 추가
+모바일 화면 정비 5·6·7·8차 진행
+부적합품 관리 기획과 오류 보완</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2598,7 +2813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4527,194 +4742,202 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="n">
+      <c r="A81" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>창고 박스 단위 재고 관리 기반</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>박스 차감·복원·이동·미배치 알림</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="n">
+      <c r="A82" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>생산 가능 수량 기준 제품 지정</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E82" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>모델별 기준 제품 지정·출하 대기 수량 보정</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E83" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>승인 전 입출고 요청 수정</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>작성자가 승인 전 요청을 수정 가능</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="n">
+      <c r="A84" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="13" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>재고 가용성 계산 고도화</t>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>알림 삭제 기능</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>개별 삭제·읽은 알림 전체 정리</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="n">
+      <c r="A85" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>외부 접근 환경 구성</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>모바일 화면 정비 5~8차</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>입출고·불량·대시보드·로그인 화면 보강</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>재고 전환 안전 점검</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>발주 관리</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="D86" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E86" s="13" t="inlineStr"/>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>위험 취소 차단·감사 준비·백업 확인</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="n">
+      <c r="A87" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>생산 실적 / 원가 관리</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D87" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr"/>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>출고·출하 창고 가져오기 확장</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>분해 작업까지 부족 품목 가져오기 지원</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="n">
+      <c r="A88" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>부서별 생산진행도 대시보드</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>창고 지도 권한 보존</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="inlineStr">
-        <is>
-          <t>사장님 요청 — 검토 중</t>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>구조 편집 후 권한 설정 유지</t>
         </is>
       </c>
     </row>
@@ -4724,20 +4947,212 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>BOM·입출고 정리 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>불량 처리 흐름 Phase 2</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>역할별 접근 권한 연동</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E89" s="13" t="inlineStr">
+      <c r="E97" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -4754,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5990,6 +6405,150 @@
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="67.5" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: 주간보고 6/13~6/19 작성 및 개발현황 엑셀 갱신
+2026-06-19 mobile: 섹션 탭 버튼 크기·글씨 확대(text-sm, min-h-60px)
+2026-06-19 docs: CLAUDE.md 전체 영어화 + 드리프트 방지 규칙 2건, 아키텍처 후보 검
+2026-06-19 inventory: 현재고/안전재고 정렬 버튼 제거(PC·모바일)
+2026-06-19 mobile: BOM 하위구성 긴 이름 탭 펼침</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="67.5" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: BOM 하위구성 탭 행 테두리 제거
+2026-06-22 mobile: 더보기 주간보고·창고지도 세로 큰 타일
+2026-06-22 mobile: 품목 상세 이미지 보기 버튼(없으면 이미지 없음 표시)
+2026-06-22 ux: 입출고·PC 사이드바 아이콘 색상
+2026-06-22 mobile: 불량 카트 1단계 전폭·하단 버튼 고정</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="67.5" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 피드백 상태 갱신 (오세현 2건 해결, 허동현 재작업 종결)
+2026-06-23 frontend: 창고 편집 탭 통합(박스 관리·앵글 편집 2개)
+2026-06-23 capacity: 기준 PF 지정 버튼 즉각 반영 버그 수정
+2026-06-23 frontend: 모바일 5차 로그인 로고 - maxWidth 캡 해제(378px) + 
+2026-06-23 frontend: 모바일 5차 불량 Step1 출처 토글 확대(SegmentedContr</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="67.5" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 피드백 추가 (이계숙 요청수정, 김현우 더보기)
+2026-06-24 docs: 포트·경로·모듈 수 정정 (README·OPERATIONS·ONBOARDING
+2026-06-24 backend: pf-pins UUID roundtrip 회귀 테스트 신설
+2026-06-24 docs: legacy 필드·복제 헬퍼 의도 주석
+2026-06-24 frontend: 출고출하(disassemble) 창고에서 가져오기 지원</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="67.5" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: 모바일 수정 추적 8차 수집 갱신
+2026-06-25 docs: 출하 관리 개선안 추가
+2026-06-25 backend: 알림 개별 삭제 + 읽은 알림 전체 삭제 API
+2026-06-25 frontend: 알림 창 삭제 기능 — X 버튼 + 읽은 알림 삭제
+2026-06-25 docs: add Codex agent skills</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="67.5" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-26 safety: prepare inventory cutover
+2026-06-26 feedback: update resolved feedback statuses
+Merge remote-tracking branch 'origin/codex/screen-cleanup-a'
+2026-06-26 fix: E2E global-setup에 X-Admin-Pin 헤더 추가 — CI 복구
+2026-06-26 docs: 커밋 메시지 한국어 작성 규칙 추가 (CLAUDE.md + AGENTS.md </t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -6006,7 +6565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1045"/>
+  <dimension ref="A1:F1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39457,6 +40016,4134 @@
         </is>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1046" s="15" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C1046" s="15" t="inlineStr">
+        <is>
+          <t>85237421</t>
+        </is>
+      </c>
+      <c r="D1046" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: 주간보고 6/13~6/19 작성 및 개발현황 엑셀 갱신</t>
+        </is>
+      </c>
+      <c r="E1046" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1046" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1047" s="7" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C1047" s="7" t="inlineStr">
+        <is>
+          <t>7cdb04c6</t>
+        </is>
+      </c>
+      <c r="D1047" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 섹션 탭 버튼 크기·글씨 확대(text-sm, min-h-60px)</t>
+        </is>
+      </c>
+      <c r="E1047" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1047" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1048" s="15" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="C1048" s="15" t="inlineStr">
+        <is>
+          <t>f5d4b34e</t>
+        </is>
+      </c>
+      <c r="D1048" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: CLAUDE.md 전체 영어화 + 드리프트 방지 규칙 2건, 아키텍처 후보 검증 기록</t>
+        </is>
+      </c>
+      <c r="E1048" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1048" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1049" s="7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1049" s="7" t="inlineStr">
+        <is>
+          <t>9e7caaa5</t>
+        </is>
+      </c>
+      <c r="D1049" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 inventory: 현재고/안전재고 정렬 버튼 제거(PC·모바일)</t>
+        </is>
+      </c>
+      <c r="E1049" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1049" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1050" s="15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1050" s="15" t="inlineStr">
+        <is>
+          <t>1e1bcbc8</t>
+        </is>
+      </c>
+      <c r="D1050" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: BOM 하위구성 긴 이름 탭 펼침</t>
+        </is>
+      </c>
+      <c r="E1050" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1050" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1051" s="7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1051" s="7" t="inlineStr">
+        <is>
+          <t>0566d955</t>
+        </is>
+      </c>
+      <c r="D1051" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 입출고 위저드 스크롤 제거·Step1 콘텐츠 확대</t>
+        </is>
+      </c>
+      <c r="E1051" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1051" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1052" s="15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1052" s="15" t="inlineStr">
+        <is>
+          <t>ffea99ac</t>
+        </is>
+      </c>
+      <c r="D1052" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 불량 허브 첫 화면 카드 3장 키오스크화</t>
+        </is>
+      </c>
+      <c r="E1052" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1052" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1053" s="7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1053" s="7" t="inlineStr">
+        <is>
+          <t>0fdeff9d</t>
+        </is>
+      </c>
+      <c r="D1053" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 내역 달력 주말 제거(월~금 5열, 모바일 전용)</t>
+        </is>
+      </c>
+      <c r="E1053" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1053" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1054" s="15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1054" s="15" t="inlineStr">
+        <is>
+          <t>d423ffd6</t>
+        </is>
+      </c>
+      <c r="D1054" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 더보기 큰 카드·계정 제거·네비 동적 라벨</t>
+        </is>
+      </c>
+      <c r="E1054" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1054" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1055" s="7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1055" s="7" t="inlineStr">
+        <is>
+          <t>6327540a</t>
+        </is>
+      </c>
+      <c r="D1055" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: 모바일 2차 정비 진행상태 갱신</t>
+        </is>
+      </c>
+      <c r="E1055" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1055" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1056" s="15" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C1056" s="15" t="inlineStr">
+        <is>
+          <t>3ccb00f4</t>
+        </is>
+      </c>
+      <c r="D1056" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 mobile: 창고지도 가로 전용 전면 재설계</t>
+        </is>
+      </c>
+      <c r="E1056" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1056" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1057" s="7" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C1057" s="7" t="inlineStr">
+        <is>
+          <t>e26ad8b6</t>
+        </is>
+      </c>
+      <c r="D1057" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: 2-10 실기 확인 대기로 표기</t>
+        </is>
+      </c>
+      <c r="E1057" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1057" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1058" s="15" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1058" s="15" t="inlineStr">
+        <is>
+          <t>0513a3eb</t>
+        </is>
+      </c>
+      <c r="D1058" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 refactor: 품목 정렬 comparator를 sortItemsForPicker 순수함수로 추출</t>
+        </is>
+      </c>
+      <c r="E1058" s="15" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F1058" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1059" s="7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1059" s="7" t="inlineStr">
+        <is>
+          <t>86bde79c</t>
+        </is>
+      </c>
+      <c r="D1059" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-19 refactor: 생산 입고 오케스트레이션을 services/production_receipt.py로 추출</t>
+        </is>
+      </c>
+      <c r="E1059" s="7" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+      <c r="F1059" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1060" s="15" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1060" s="15" t="inlineStr">
+        <is>
+          <t>00e507ed</t>
+        </is>
+      </c>
+      <c r="D1060" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: review-map 향후 후보 갱신 — 처리분 반영</t>
+        </is>
+      </c>
+      <c r="E1060" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1060" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1061" s="19" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1061" s="19" t="inlineStr">
+        <is>
+          <t>b01da4fc</t>
+        </is>
+      </c>
+      <c r="D1061" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-19 docs: 모바일 3차 수집 항목(3-1~3-7) 추가</t>
+        </is>
+      </c>
+      <c r="E1061" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1061" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1062" s="15" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1062" s="15" t="inlineStr">
+        <is>
+          <t>8d3a3a99</t>
+        </is>
+      </c>
+      <c r="D1062" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: BOM 하위구성 탭 행 테두리 제거</t>
+        </is>
+      </c>
+      <c r="E1062" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1062" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1063" s="7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1063" s="7" t="inlineStr">
+        <is>
+          <t>638aa97f</t>
+        </is>
+      </c>
+      <c r="D1063" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 더보기 주간보고·창고지도 세로 큰 타일</t>
+        </is>
+      </c>
+      <c r="E1063" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1063" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1064" s="15" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1064" s="15" t="inlineStr">
+        <is>
+          <t>52b17d9a</t>
+        </is>
+      </c>
+      <c r="D1064" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 품목 상세 이미지 보기 버튼(없으면 이미지 없음 표시)</t>
+        </is>
+      </c>
+      <c r="E1064" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1064" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1065" s="7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1065" s="7" t="inlineStr">
+        <is>
+          <t>3a72907d</t>
+        </is>
+      </c>
+      <c r="D1065" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 ux: 입출고·PC 사이드바 아이콘 색상</t>
+        </is>
+      </c>
+      <c r="E1065" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1065" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1066" s="15" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1066" s="15" t="inlineStr">
+        <is>
+          <t>c91e6e33</t>
+        </is>
+      </c>
+      <c r="D1066" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 불량 카트 1단계 전폭·하단 버튼 고정</t>
+        </is>
+      </c>
+      <c r="E1066" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1066" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1067" s="7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1067" s="7" t="inlineStr">
+        <is>
+          <t>0611bc68</t>
+        </is>
+      </c>
+      <c r="D1067" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 헤더 상태 데스크톱 통일 + 입출고 저장·이탈 보강</t>
+        </is>
+      </c>
+      <c r="E1067" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1067" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1068" s="15" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1068" s="15" t="inlineStr">
+        <is>
+          <t>18e300c7</t>
+        </is>
+      </c>
+      <c r="D1068" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 3차 항목(3-1~3-7) 완료 마킹</t>
+        </is>
+      </c>
+      <c r="E1068" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1068" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1069" s="7" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C1069" s="7" t="inlineStr">
+        <is>
+          <t>389363b0</t>
+        </is>
+      </c>
+      <c r="D1069" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 backend: 품목 추가 시 초기 재고 부서별 분배 API</t>
+        </is>
+      </c>
+      <c r="E1069" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1069" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1070" s="15" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C1070" s="15" t="inlineStr">
+        <is>
+          <t>c3cf3a86</t>
+        </is>
+      </c>
+      <c r="D1070" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 품목 추가 폼 초기 재고 위치별 입력 UX</t>
+        </is>
+      </c>
+      <c r="E1070" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1070" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1071" s="7" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C1071" s="7" t="inlineStr">
+        <is>
+          <t>cc9d9927</t>
+        </is>
+      </c>
+      <c r="D1071" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 품목 검색 공백 무시 매칭 + 검색 필드 축소 (김건호 5·6)</t>
+        </is>
+      </c>
+      <c r="E1071" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1071" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1072" s="15" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C1072" s="15" t="inlineStr">
+        <is>
+          <t>76e4ffd2</t>
+        </is>
+      </c>
+      <c r="D1072" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 삭제 품목 대시보드·입출고 숨김 + BOM 취소선 (김건호 1)</t>
+        </is>
+      </c>
+      <c r="E1072" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1072" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1073" s="7" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C1073" s="7" t="inlineStr">
+        <is>
+          <t>9c9fcbc5</t>
+        </is>
+      </c>
+      <c r="D1073" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 입출고 부족품목 창고 가져오기·이어서하기 복원·BOM 상위코드·휴지통 (김건호 3·2·4-2·7)</t>
+        </is>
+      </c>
+      <c r="E1073" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1073" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1074" s="15" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C1074" s="15" t="inlineStr">
+        <is>
+          <t>60800584</t>
+        </is>
+      </c>
+      <c r="D1074" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 backend: 입출고 내역 요청일시 순 정렬 (김현우·허동현)</t>
+        </is>
+      </c>
+      <c r="E1074" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1074" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1075" s="7" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C1075" s="7" t="inlineStr">
+        <is>
+          <t>74bc8b24</t>
+        </is>
+      </c>
+      <c r="D1075" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 피드백 기록 — 김건호 7건·입출고 내역 정렬(김현우·허동현)</t>
+        </is>
+      </c>
+      <c r="E1075" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1075" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1076" s="15" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C1076" s="15" t="inlineStr">
+        <is>
+          <t>b4110662</t>
+        </is>
+      </c>
+      <c r="D1076" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 주간보고 발송 양식 개편</t>
+        </is>
+      </c>
+      <c r="E1076" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1076" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1077" s="7" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C1077" s="7" t="inlineStr">
+        <is>
+          <t>81adb366</t>
+        </is>
+      </c>
+      <c r="D1077" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 fix: 비보안 HTTP 컨텍스트 불량 카트 crypto.randomUUID 오류 수정</t>
+        </is>
+      </c>
+      <c r="E1077" s="7" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1077" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1078" s="15" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C1078" s="15" t="inlineStr">
+        <is>
+          <t>3ec8a48e</t>
+        </is>
+      </c>
+      <c r="D1078" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 backend: 안전재고 200대분 재계산 스크립트(미리보기·적용)</t>
+        </is>
+      </c>
+      <c r="E1078" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1078" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1079" s="7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C1079" s="7" t="inlineStr">
+        <is>
+          <t>f8afba30</t>
+        </is>
+      </c>
+      <c r="D1079" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 로그인 직원검색 영타→한글 실시간 변환</t>
+        </is>
+      </c>
+      <c r="E1079" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1079" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1080" s="15" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C1080" s="15" t="inlineStr">
+        <is>
+          <t>232cbb74</t>
+        </is>
+      </c>
+      <c r="D1080" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 test: io-process-produce E2E — BOM 상위 mes_code span 끼임 흡수</t>
+        </is>
+      </c>
+      <c r="E1080" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1080" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1081" s="7" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C1081" s="7" t="inlineStr">
+        <is>
+          <t>6d3ee255</t>
+        </is>
+      </c>
+      <c r="D1081" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 부족품목 창고 가져오기 모바일 확장 (김건호 7번)</t>
+        </is>
+      </c>
+      <c r="E1081" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1081" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1082" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1082" s="15" t="inlineStr">
+        <is>
+          <t>a6b2e5d7</t>
+        </is>
+      </c>
+      <c r="D1082" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: StickyFooter flat prop 추가(배경·그림자 제거 옵션)</t>
+        </is>
+      </c>
+      <c r="E1082" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1082" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1083" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1083" s="7" t="inlineStr">
+        <is>
+          <t>d5fc0ad7</t>
+        </is>
+      </c>
+      <c r="D1083" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 위저드 헤더 단계명 제거·STEP 우측 정렬</t>
+        </is>
+      </c>
+      <c r="E1083" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1083" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1084" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1084" s="15" t="inlineStr">
+        <is>
+          <t>deed2a19</t>
+        </is>
+      </c>
+      <c r="D1084" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 로그인 로고 확대(scale 0.45)</t>
+        </is>
+      </c>
+      <c r="E1084" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1084" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1085" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1085" s="7" t="inlineStr">
+        <is>
+          <t>0cb60f6f</t>
+        </is>
+      </c>
+      <c r="D1085" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 Step1·2 작업유형/세부작업 버튼 확대·꽉채움</t>
+        </is>
+      </c>
+      <c r="E1085" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1085" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1086" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1086" s="15" t="inlineStr">
+        <is>
+          <t>8a2dfa01</t>
+        </is>
+      </c>
+      <c r="D1086" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 Step2 다음 버튼 푸터 배경 제거(flat)</t>
+        </is>
+      </c>
+      <c r="E1086" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1086" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1087" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1087" s="7" t="inlineStr">
+        <is>
+          <t>3224ddfa</t>
+        </is>
+      </c>
+      <c r="D1087" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 Step3 순서편집 숨김·수량조정 푸터 배경 제거</t>
+        </is>
+      </c>
+      <c r="E1087" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1087" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1088" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1088" s="15" t="inlineStr">
+        <is>
+          <t>8bf74b51</t>
+        </is>
+      </c>
+      <c r="D1088" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 Step4 제출 푸터 배경 제거(flat)</t>
+        </is>
+      </c>
+      <c r="E1088" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1088" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1089" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1089" s="7" t="inlineStr">
+        <is>
+          <t>b83bcd39</t>
+        </is>
+      </c>
+      <c r="D1089" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 번들카드 가능재고/실행후 가운데 정렬</t>
+        </is>
+      </c>
+      <c r="E1089" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1089" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1090" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1090" s="15" t="inlineStr">
+        <is>
+          <t>f690bdd6</t>
+        </is>
+      </c>
+      <c r="D1090" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 긴 품목명 탭 펼침(ExpandableItemName)·재고 가운데 정렬</t>
+        </is>
+      </c>
+      <c r="E1090" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1090" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1091" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1091" s="7" t="inlineStr">
+        <is>
+          <t>51d7fabd</t>
+        </is>
+      </c>
+      <c r="D1091" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 입출고 Step5 저장/결재 버튼 Step4 스타일 통일</t>
+        </is>
+      </c>
+      <c r="E1091" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1091" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1092" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1092" s="15" t="inlineStr">
+        <is>
+          <t>e0a2ea1f</t>
+        </is>
+      </c>
+      <c r="D1092" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 불량 품목선택 순서편집 숨김·담김/추가 버튼 색 구분</t>
+        </is>
+      </c>
+      <c r="E1092" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1092" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1093" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1093" s="7" t="inlineStr">
+        <is>
+          <t>a94d4f53</t>
+        </is>
+      </c>
+      <c r="D1093" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 불량 출처·부서 버튼 꽉채움·푸터 배경 제거(flat)</t>
+        </is>
+      </c>
+      <c r="E1093" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1093" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1094" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1094" s="15" t="inlineStr">
+        <is>
+          <t>5366ce8d</t>
+        </is>
+      </c>
+      <c r="D1094" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 내역 달력 카운트 건 줄바꿈 방지</t>
+        </is>
+      </c>
+      <c r="E1094" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1094" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1095" s="7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1095" s="7" t="inlineStr">
+        <is>
+          <t>643339a2</t>
+        </is>
+      </c>
+      <c r="D1095" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 주간보고 생산현황 PC 매트릭스 표로 통일</t>
+        </is>
+      </c>
+      <c r="E1095" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1095" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1096" s="15" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1096" s="15" t="inlineStr">
+        <is>
+          <t>f014f324</t>
+        </is>
+      </c>
+      <c r="D1096" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 mobile: 대시보드 검색바 card 밖 풀폭 sticky 분리(스크롤 틈 제거)</t>
+        </is>
+      </c>
+      <c r="E1096" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1096" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1097" s="7" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C1097" s="7" t="inlineStr">
+        <is>
+          <t>f7819af7</t>
+        </is>
+      </c>
+      <c r="D1097" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 capacity: 모델별 기준 PF 지정 기능</t>
+        </is>
+      </c>
+      <c r="E1097" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1097" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1098" s="15" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C1098" s="15" t="inlineStr">
+        <is>
+          <t>c01ba5bf</t>
+        </is>
+      </c>
+      <c r="D1098" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 피드백 해결마킹·모바일 4차 수집 시작·창고 박스 차감 설계</t>
+        </is>
+      </c>
+      <c r="E1098" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1098" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1099" s="7" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="C1099" s="7" t="inlineStr">
+        <is>
+          <t>b8dee4a4</t>
+        </is>
+      </c>
+      <c r="D1099" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 backend: 창고 박스 자동 차감 엔진(Phase 1)</t>
+        </is>
+      </c>
+      <c r="E1099" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1099" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1100" s="15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C1100" s="15" t="inlineStr">
+        <is>
+          <t>57194685</t>
+        </is>
+      </c>
+      <c r="D1100" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 창고 지도 편집 통합 + 권한 전환(Phase 2)</t>
+        </is>
+      </c>
+      <c r="E1100" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1100" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1101" s="7" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C1101" s="7" t="inlineStr">
+        <is>
+          <t>006e99e6</t>
+        </is>
+      </c>
+      <c r="D1101" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 창고 지도 박스 드래그 이동(Phase 3a)</t>
+        </is>
+      </c>
+      <c r="E1101" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1101" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1102" s="15" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C1102" s="15" t="inlineStr">
+        <is>
+          <t>b22dd1bb</t>
+        </is>
+      </c>
+      <c r="D1102" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 미배치 알림 + R5 출고 차단 바로가기(Phase 3b)</t>
+        </is>
+      </c>
+      <c r="E1102" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1102" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1103" s="7" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C1103" s="7" t="inlineStr">
+        <is>
+          <t>1167b781</t>
+        </is>
+      </c>
+      <c r="D1103" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 부적합품 관리 업무 흐름 이해안 초안</t>
+        </is>
+      </c>
+      <c r="E1103" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1103" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1104" s="15" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1104" s="15" t="inlineStr">
+        <is>
+          <t>eebe3934</t>
+        </is>
+      </c>
+      <c r="D1104" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 창고 박스 드래그 스택 재정렬·중간 삽입(Phase 3c)</t>
+        </is>
+      </c>
+      <c r="E1104" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1104" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1105" s="7" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C1105" s="7" t="inlineStr">
+        <is>
+          <t>732950b0</t>
+        </is>
+      </c>
+      <c r="D1105" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22 frontend: 오세현 피드백 2건 버그 수정</t>
+        </is>
+      </c>
+      <c r="E1105" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1105" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1106" s="15" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C1106" s="15" t="inlineStr">
+        <is>
+          <t>d6738942</t>
+        </is>
+      </c>
+      <c r="D1106" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 docs: 오세현 피드백 기록</t>
+        </is>
+      </c>
+      <c r="E1106" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1106" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1107" s="7" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1107" s="7" t="inlineStr">
+        <is>
+          <t>e4c7e34d</t>
+        </is>
+      </c>
+      <c r="D1107" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 피드백 상태 갱신 (오세현 2건 해결, 허동현 재작업 종결)</t>
+        </is>
+      </c>
+      <c r="E1107" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1107" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1108" s="15" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C1108" s="15" t="inlineStr">
+        <is>
+          <t>73e4ccfd</t>
+        </is>
+      </c>
+      <c r="D1108" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 창고 편집 탭 통합(박스 관리·앵글 편집 2개)</t>
+        </is>
+      </c>
+      <c r="E1108" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1108" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1109" s="7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C1109" s="7" t="inlineStr">
+        <is>
+          <t>1ff2354c</t>
+        </is>
+      </c>
+      <c r="D1109" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 capacity: 기준 PF 지정 버튼 즉각 반영 버그 수정</t>
+        </is>
+      </c>
+      <c r="E1109" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1109" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1110" s="15" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="C1110" s="15" t="inlineStr">
+        <is>
+          <t>e856422e</t>
+        </is>
+      </c>
+      <c r="D1110" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 로그인 로고 - maxWidth 캡 해제(378px) + 인트로 모바일만 작게→크게 반전</t>
+        </is>
+      </c>
+      <c r="E1110" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1110" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1111" s="7" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C1111" s="7" t="inlineStr">
+        <is>
+          <t>5522b920</t>
+        </is>
+      </c>
+      <c r="D1111" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 불량 Step1 출처 토글 확대(SegmentedControl size=lg opt-in)</t>
+        </is>
+      </c>
+      <c r="E1111" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1111" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1112" s="15" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C1112" s="15" t="inlineStr">
+        <is>
+          <t>69a8576c</t>
+        </is>
+      </c>
+      <c r="D1112" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 입출고 Step3/4/5 푸터 하단 네비바 근접(pb 축소)</t>
+        </is>
+      </c>
+      <c r="E1112" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1112" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1113" s="7" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C1113" s="7" t="inlineStr">
+        <is>
+          <t>326f2193</t>
+        </is>
+      </c>
+      <c r="D1113" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 휴지통 버튼 축소(lg: PC유지) + Step4 저장 버튼 Save 아이콘</t>
+        </is>
+      </c>
+      <c r="E1113" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1113" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1114" s="15" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C1114" s="15" t="inlineStr">
+        <is>
+          <t>cdaa23f4</t>
+        </is>
+      </c>
+      <c r="D1114" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 입출고 Step4 자식 라인 가능재고·실행후 가운데 정렬(lg:contents)</t>
+        </is>
+      </c>
+      <c r="E1114" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1114" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1115" s="7" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C1115" s="7" t="inlineStr">
+        <is>
+          <t>627078ab</t>
+        </is>
+      </c>
+      <c r="D1115" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 5차 주간보고 공정 전환 가로 오버플로우 고정(min-w-0)</t>
+        </is>
+      </c>
+      <c r="E1115" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1115" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1116" s="15" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="C1116" s="15" t="inlineStr">
+        <is>
+          <t>4df41ffb</t>
+        </is>
+      </c>
+      <c r="D1116" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 capacity: GET /pf-pins UUID 포맷 정규화 (새로고침 후 지정 사라지는 버그 수정)</t>
+        </is>
+      </c>
+      <c r="E1116" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1116" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1117" s="7" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="C1117" s="7" t="inlineStr">
+        <is>
+          <t>e46323c6</t>
+        </is>
+      </c>
+      <c r="D1117" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 피드백 상태 갱신 (이지훈 BOM종결, 권동환 안전재고해결)</t>
+        </is>
+      </c>
+      <c r="E1117" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1117" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1118" s="15" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C1118" s="15" t="inlineStr">
+        <is>
+          <t>5c73889e</t>
+        </is>
+      </c>
+      <c r="D1118" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 생산 가능수량 모달 병목 표시 제거</t>
+        </is>
+      </c>
+      <c r="E1118" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1118" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1119" s="7" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C1119" s="7" t="inlineStr">
+        <is>
+          <t>89804bd8</t>
+        </is>
+      </c>
+      <c r="D1119" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 scripts: BOM 패밀리 그래프 model_pf_pins 기반 재생성</t>
+        </is>
+      </c>
+      <c r="E1119" s="7" t="inlineStr">
+        <is>
+          <t>scripts</t>
+        </is>
+      </c>
+      <c r="F1119" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1120" s="15" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="C1120" s="15" t="inlineStr">
+        <is>
+          <t>a91fdc02</t>
+        </is>
+      </c>
+      <c r="D1120" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 전체 KPI 소프트삭제 제외(정상/부족/품절 합과 일치, 모바일·PC 공통 훅)</t>
+        </is>
+      </c>
+      <c r="E1120" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1120" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1121" s="7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C1121" s="7" t="inlineStr">
+        <is>
+          <t>b743042d</t>
+        </is>
+      </c>
+      <c r="D1121" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 부적합품 관리 기획 발표자료 완성</t>
+        </is>
+      </c>
+      <c r="E1121" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1121" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1122" s="15" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C1122" s="15" t="inlineStr">
+        <is>
+          <t>9de3bf5e</t>
+        </is>
+      </c>
+      <c r="D1122" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 생산 가능수량 모달 고정 높이 + 여백 확대</t>
+        </is>
+      </c>
+      <c r="E1122" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1122" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1123" s="7" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C1123" s="7" t="inlineStr">
+        <is>
+          <t>71260c67</t>
+        </is>
+      </c>
+      <c r="D1123" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 data: 창고 박스 정합성 배치·차감 검증 스크립트</t>
+        </is>
+      </c>
+      <c r="E1123" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1123" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1124" s="15" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="C1124" s="15" t="inlineStr">
+        <is>
+          <t>41cc32c3</t>
+        </is>
+      </c>
+      <c r="D1124" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 6-1·6-4 입출고 Step2 텍스트 확대·입력방식 블록 제거</t>
+        </is>
+      </c>
+      <c r="E1124" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1124" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1125" s="7" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="C1125" s="7" t="inlineStr">
+        <is>
+          <t>2a7a15f1</t>
+        </is>
+      </c>
+      <c r="D1125" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 6-2·6-3 입출고 Step5 저장 라벨 통일·요약 박스 축소</t>
+        </is>
+      </c>
+      <c r="E1125" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1125" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1126" s="15" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="C1126" s="15" t="inlineStr">
+        <is>
+          <t>055aa89d</t>
+        </is>
+      </c>
+      <c r="D1126" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 6-5 입출고 번들 카드 재고/실행후 가운데 정렬</t>
+        </is>
+      </c>
+      <c r="E1126" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1126" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1127" s="7" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="C1127" s="7" t="inlineStr">
+        <is>
+          <t>eab0bc09</t>
+        </is>
+      </c>
+      <c r="D1127" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 6-6 입출고/불량 sticky 푸터 배경 비침 차단</t>
+        </is>
+      </c>
+      <c r="E1127" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1127" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1128" s="15" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C1128" s="15" t="inlineStr">
+        <is>
+          <t>b2a6d818</t>
+        </is>
+      </c>
+      <c r="D1128" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 모바일 6차 TODO 상태 갱신 (6-1~6-6 완료·푸시)</t>
+        </is>
+      </c>
+      <c r="E1128" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1128" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1129" s="7" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C1129" s="7" t="inlineStr">
+        <is>
+          <t>3b5ea829</t>
+        </is>
+      </c>
+      <c r="D1129" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 입출고 화면 접근 권한(io_enabled) 로그인 연동·관리자 라벨 정리</t>
+        </is>
+      </c>
+      <c r="E1129" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1129" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1130" s="15" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C1130" s="15" t="inlineStr">
+        <is>
+          <t>5773fb22</t>
+        </is>
+      </c>
+      <c r="D1130" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 기준 PF 해제 시 확인 팝업 추가</t>
+        </is>
+      </c>
+      <c r="E1130" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1130" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1131" s="7" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C1131" s="7" t="inlineStr">
+        <is>
+          <t>97868060</t>
+        </is>
+      </c>
+      <c r="D1131" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 backend: ship_ready에 PF 자체 재고 합산 (출하 대기 = PF재고 + 조립가능)</t>
+        </is>
+      </c>
+      <c r="E1131" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1131" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1132" s="15" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C1132" s="15" t="inlineStr">
+        <is>
+          <t>ad1de8ed</t>
+        </is>
+      </c>
+      <c r="D1132" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 생산 가능수량 모달 헤더 재디자인 (수량 3종 친근한 설명)</t>
+        </is>
+      </c>
+      <c r="E1132" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1132" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1133" s="7" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C1133" s="7" t="inlineStr">
+        <is>
+          <t>6d9afcc9</t>
+        </is>
+      </c>
+      <c r="D1133" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend,backend: 생산 가능수량 3지표 PF 기준 통일 (fast_production)</t>
+        </is>
+      </c>
+      <c r="E1133" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1133" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1134" s="15" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C1134" s="15" t="inlineStr">
+        <is>
+          <t>ea098750</t>
+        </is>
+      </c>
+      <c r="D1134" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 창고 지도 검색 미리보기 품목 단위 개편·칸 패널 폭 정합</t>
+        </is>
+      </c>
+      <c r="E1134" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1134" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1135" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C1135" s="19" t="inlineStr">
+        <is>
+          <t>aa58bef3</t>
+        </is>
+      </c>
+      <c r="D1135" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 모바일 뷰포트/스크롤 안정화</t>
+        </is>
+      </c>
+      <c r="E1135" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1135" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1136" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C1136" s="19" t="inlineStr">
+        <is>
+          <t>e7837156</t>
+        </is>
+      </c>
+      <c r="D1136" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 mobile: 불량 화면 정리 (허브 헤더 제거·격리 버튼 크기 통일)</t>
+        </is>
+      </c>
+      <c r="E1136" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1136" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1137" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C1137" s="19" t="inlineStr">
+        <is>
+          <t>230ae02d</t>
+        </is>
+      </c>
+      <c r="D1137" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 입출고 Step4·5 저장 버튼 위치 통일</t>
+        </is>
+      </c>
+      <c r="E1137" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1137" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1138" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C1138" s="19" t="inlineStr">
+        <is>
+          <t>97a712e0</t>
+        </is>
+      </c>
+      <c r="D1138" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 로그인 직원 이름 초성검색 지원</t>
+        </is>
+      </c>
+      <c r="E1138" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1138" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1139" s="19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C1139" s="19" t="inlineStr">
+        <is>
+          <t>9b355644</t>
+        </is>
+      </c>
+      <c r="D1139" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 docs: 모바일 7차 TODO 수집·구현 상태 갱신</t>
+        </is>
+      </c>
+      <c r="E1139" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1139" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1140" s="19" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C1140" s="19" t="inlineStr">
+        <is>
+          <t>71ce3df2</t>
+        </is>
+      </c>
+      <c r="D1140" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 frontend: 생산 가능수량 UI 개선 (병목 mes_code·필터 제거·경고 아이콘 제거·글씨 확대)</t>
+        </is>
+      </c>
+      <c r="E1140" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1140" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1141" s="7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C1141" s="7" t="inlineStr">
+        <is>
+          <t>b04c8eb7</t>
+        </is>
+      </c>
+      <c r="D1141" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 피드백 추가 (이계숙 요청수정, 김현우 더보기)</t>
+        </is>
+      </c>
+      <c r="E1141" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1141" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1142" s="15" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="C1142" s="15" t="inlineStr">
+        <is>
+          <t>dd0b17b8</t>
+        </is>
+      </c>
+      <c r="D1142" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 포트·경로·모듈 수 정정 (README·OPERATIONS·ONBOARDING·CONTEXT)</t>
+        </is>
+      </c>
+      <c r="E1142" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1142" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1143" s="7" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="C1143" s="7" t="inlineStr">
+        <is>
+          <t>6c559c08</t>
+        </is>
+      </c>
+      <c r="D1143" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 backend: pf-pins UUID roundtrip 회귀 테스트 신설</t>
+        </is>
+      </c>
+      <c r="E1143" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1143" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1144" s="15" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C1144" s="15" t="inlineStr">
+        <is>
+          <t>31e81f1c</t>
+        </is>
+      </c>
+      <c r="D1144" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: legacy 필드·복제 헬퍼 의도 주석</t>
+        </is>
+      </c>
+      <c r="E1144" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1144" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1145" s="7" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1145" s="7" t="inlineStr">
+        <is>
+          <t>5443a031</t>
+        </is>
+      </c>
+      <c r="D1145" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 frontend: 출고출하(disassemble) 창고에서 가져오기 지원</t>
+        </is>
+      </c>
+      <c r="E1145" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1145" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1146" s="15" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1146" s="15" t="inlineStr">
+        <is>
+          <t>4870783f</t>
+        </is>
+      </c>
+      <c r="D1146" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 김건호 피드백 7번 disassemble 확장 기록</t>
+        </is>
+      </c>
+      <c r="E1146" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1146" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1147" s="7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C1147" s="7" t="inlineStr">
+        <is>
+          <t>3fc3c446</t>
+        </is>
+      </c>
+      <c r="D1147" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 chore: 머지 cleanup-doc-truth-20260624 — 권동환 사원 복귀 전 정비 + disassemble 가져오기</t>
+        </is>
+      </c>
+      <c r="E1147" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1147" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1148" s="15" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="C1148" s="15" t="inlineStr">
+        <is>
+          <t>f3277a64</t>
+        </is>
+      </c>
+      <c r="D1148" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 김건호 낱개 출고 주간보고 미반영 버그 추가</t>
+        </is>
+      </c>
+      <c r="E1148" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1148" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1149" s="7" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C1149" s="7" t="inlineStr">
+        <is>
+          <t>a2eebff8</t>
+        </is>
+      </c>
+      <c r="D1149" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 backend: 낱개 출고 주간보고 집계 + 승인 전 요청 수정 API</t>
+        </is>
+      </c>
+      <c r="E1149" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1149" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1150" s="15" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C1150" s="15" t="inlineStr">
+        <is>
+          <t>a50c8a70</t>
+        </is>
+      </c>
+      <c r="D1150" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24 frontend: 내 요청 더보기 + 승인 전 요청 수정</t>
+        </is>
+      </c>
+      <c r="E1150" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1150" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1151" s="7" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C1151" s="7" t="inlineStr">
+        <is>
+          <t>accd9677</t>
+        </is>
+      </c>
+      <c r="D1151" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24 docs: 이계숙·김현우·김건호 피드백 해결 처리</t>
+        </is>
+      </c>
+      <c r="E1151" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1151" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1152" s="15" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C1152" s="15" t="inlineStr">
+        <is>
+          <t>e60a9f99</t>
+        </is>
+      </c>
+      <c r="D1152" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: 모바일 수정 추적 8차 수집 갱신</t>
+        </is>
+      </c>
+      <c r="E1152" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1152" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1153" s="7" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C1153" s="7" t="inlineStr">
+        <is>
+          <t>88a066bf</t>
+        </is>
+      </c>
+      <c r="D1153" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: 출하 관리 개선안 추가</t>
+        </is>
+      </c>
+      <c r="E1153" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1153" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1154" s="15" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C1154" s="15" t="inlineStr">
+        <is>
+          <t>50815cb1</t>
+        </is>
+      </c>
+      <c r="D1154" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25 backend: 알림 개별 삭제 + 읽은 알림 전체 삭제 API</t>
+        </is>
+      </c>
+      <c r="E1154" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1154" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1155" s="7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C1155" s="7" t="inlineStr">
+        <is>
+          <t>31c899c3</t>
+        </is>
+      </c>
+      <c r="D1155" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25 frontend: 알림 창 삭제 기능 — X 버튼 + 읽은 알림 삭제</t>
+        </is>
+      </c>
+      <c r="E1155" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1155" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1156" s="15" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C1156" s="15" t="inlineStr">
+        <is>
+          <t>c4f1848a</t>
+        </is>
+      </c>
+      <c r="D1156" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: add Codex agent skills</t>
+        </is>
+      </c>
+      <c r="E1156" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1156" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1157" s="7" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C1157" s="7" t="inlineStr">
+        <is>
+          <t>926cd7d8</t>
+        </is>
+      </c>
+      <c r="D1157" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25 mobile: 8차 UX 정비 (8-1~8-5)</t>
+        </is>
+      </c>
+      <c r="E1157" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1157" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1158" s="15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C1158" s="15" t="inlineStr">
+        <is>
+          <t>ce2d51ac</t>
+        </is>
+      </c>
+      <c r="D1158" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: 모바일 8차 TODO 구현·검증 상태 갱신</t>
+        </is>
+      </c>
+      <c r="E1158" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1158" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1159" s="7" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C1159" s="7" t="inlineStr">
+        <is>
+          <t>56d56d06</t>
+        </is>
+      </c>
+      <c r="D1159" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: 오세현 피드백 — 불량 격리 진입 부서 고정 UX 2건 추가</t>
+        </is>
+      </c>
+      <c r="E1159" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1159" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1160" s="15" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C1160" s="15" t="inlineStr">
+        <is>
+          <t>c0f24498</t>
+        </is>
+      </c>
+      <c r="D1160" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25 docs: AGENTS.md Codex 호환성 3건 개선 (스킬 직접읽기·셸안전·메모리gap)</t>
+        </is>
+      </c>
+      <c r="E1160" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1160" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1161" s="19" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C1161" s="19" t="inlineStr">
+        <is>
+          <t>fc248779</t>
+        </is>
+      </c>
+      <c r="D1161" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 feedback: implement unresolved MES feedback</t>
+        </is>
+      </c>
+      <c r="E1161" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1161" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1162" s="19" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="C1162" s="19" t="inlineStr">
+        <is>
+          <t>bc5ad563</t>
+        </is>
+      </c>
+      <c r="D1162" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 safety: harden inventory operations</t>
+        </is>
+      </c>
+      <c r="E1162" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1162" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1163" s="19" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="C1163" s="19" t="inlineStr">
+        <is>
+          <t>c2ec588a</t>
+        </is>
+      </c>
+      <c r="D1163" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 ops: harden backup integrity checks</t>
+        </is>
+      </c>
+      <c r="E1163" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1163" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1164" s="19" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="C1164" s="19" t="inlineStr">
+        <is>
+          <t>a2e0c62c</t>
+        </is>
+      </c>
+      <c r="D1164" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 safety: expose inventory audit readiness</t>
+        </is>
+      </c>
+      <c r="E1164" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1164" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1165" s="19" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="C1165" s="19" t="inlineStr">
+        <is>
+          <t>98f4d7b1</t>
+        </is>
+      </c>
+      <c r="D1165" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 safety: harden operational readiness</t>
+        </is>
+      </c>
+      <c r="E1165" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1165" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1166" s="19" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C1166" s="19" t="inlineStr">
+        <is>
+          <t>4290d51d</t>
+        </is>
+      </c>
+      <c r="D1166" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-25 safety: block unsafe legacy cancel</t>
+        </is>
+      </c>
+      <c r="E1166" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1166" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1167" s="19" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C1167" s="19" t="inlineStr">
+        <is>
+          <t>ee0512ce</t>
+        </is>
+      </c>
+      <c r="D1167" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26 safety: prepare inventory cutover</t>
+        </is>
+      </c>
+      <c r="E1167" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1167" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1168" s="19" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C1168" s="19" t="inlineStr">
+        <is>
+          <t>98234ec5</t>
+        </is>
+      </c>
+      <c r="D1168" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26 feedback: update resolved feedback statuses</t>
+        </is>
+      </c>
+      <c r="E1168" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1168" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1169" s="7" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C1169" s="7" t="inlineStr">
+        <is>
+          <t>8b003557</t>
+        </is>
+      </c>
+      <c r="D1169" s="8" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/codex/screen-cleanup-a'</t>
+        </is>
+      </c>
+      <c r="E1169" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1169" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1170" s="15" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C1170" s="15" t="inlineStr">
+        <is>
+          <t>b34df2c8</t>
+        </is>
+      </c>
+      <c r="D1170" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-26 fix: E2E global-setup에 X-Admin-Pin 헤더 추가 — CI 복구</t>
+        </is>
+      </c>
+      <c r="E1170" s="15" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1170" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1171" s="7" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="C1171" s="7" t="inlineStr">
+        <is>
+          <t>74b739b3</t>
+        </is>
+      </c>
+      <c r="D1171" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26 docs: 커밋 메시지 한국어 작성 규칙 추가 (CLAUDE.md + AGENTS.md 동기)</t>
+        </is>
+      </c>
+      <c r="E1171" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1171" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1172" s="15" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C1172" s="15" t="inlineStr">
+        <is>
+          <t>5f96c5ea</t>
+        </is>
+      </c>
+      <c r="D1172" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-26 warehouse: 창고 지도 구조 편집과 권한 보존 수정</t>
+        </is>
+      </c>
+      <c r="E1172" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1172" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1173" s="7" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C1173" s="7" t="inlineStr">
+        <is>
+          <t>a5519e40</t>
+        </is>
+      </c>
+      <c r="D1173" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26 frontend: 입출고 내역 안정화와 피드백 문서 갱신</t>
+        </is>
+      </c>
+      <c r="E1173" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1173" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1174" s="15" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C1174" s="15" t="inlineStr">
+        <is>
+          <t>fe3fbdc2</t>
+        </is>
+      </c>
+      <c r="D1174" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-26 safety: 운영 검증 안정화</t>
+        </is>
+      </c>
+      <c r="E1174" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1174" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1173건 (회사 기간 670건)</t>
+          <t>1222건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>86 / 96개 (90%)</t>
+          <t>91 / 100개 (91%)</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■■</t>
+            <t>■■■■</t>
           </r>
           <r>
             <rPr>
@@ -2330,13 +2330,148 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (8)</t>
+            <t xml:space="preserve">  (10)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-29  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (18)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-06-30  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (7)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-01  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-02  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (6)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-03  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (7)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="70">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -2355,6 +2490,8 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
@@ -2377,6 +2514,7 @@
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
@@ -2394,8 +2532,10 @@
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A44:E44"/>
@@ -2413,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2799,7 +2939,34 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>113</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" ht="129.6" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27 ~ 07-03</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>출하 관리 신설 + 현장 피드백</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>출하 관리 화면 신설 및 개선 (진행 중)
+대시보드 재고 표시 개편 — 권동환 사원님 피드백
+불량 처리 개선 — 김건호 과장님 피드백
+입출고 내역 화면 개선
+로그인·탭 이동 방식 개선 — 김건호 과장님 피드백
+창고 지도·승인함 사용성 개선 — 권동환 사원님 피드백
+품목 관리·검색 편의 개선 — 권동환 사원님 피드백
+원자재 입출고 사용성 개선 — 권동환 사원님 피드백</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2813,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4942,102 +5109,102 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>로그인 알림 팝업</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>로그아웃 중 알림을 로그인 시 1회 팝업 표시 + 개인 켜기/끄기 설정</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="n">
+      <c r="A90" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D90" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E90" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>대시보드 부서별 재고 표시</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>창고·조립·불량 위치별 수량 알약 표시로 개편</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="n">
+      <c r="A91" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>창고 지도 전체화면</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>PC 창고 지도를 넓게 보는 전체화면 모드</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="n">
+      <c r="A92" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D92" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>재고 가용성 계산 고도화</t>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>입출고·출하 탭 이동 확인</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>탭 재클릭 시 첫 화면 복귀 + 작업 중 이탈 확인</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5214,12 @@
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
@@ -5062,7 +5229,7 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5239,12 @@
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
@@ -5085,7 +5252,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E94" s="13" t="inlineStr"/>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
@@ -5093,12 +5264,12 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -5106,7 +5277,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E95" s="13" t="inlineStr"/>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
@@ -5114,12 +5289,12 @@
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -5129,7 +5304,7 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
@@ -5139,20 +5314,112 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C97" s="12" t="inlineStr">
+      <c r="C101" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
+      <c r="D101" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E97" s="13" t="inlineStr">
+      <c r="E101" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -5169,7 +5436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6537,18 +6804,138 @@
         </is>
       </c>
       <c r="B58" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-26 safety: prepare inventory cutover
+          <t>2026-06-26 safety: prepare inventory cutover
 2026-06-26 feedback: update resolved feedback statuses
 Merge remote-tracking branch 'origin/codex/screen-cleanup-a'
-2026-06-26 fix: E2E global-setup에 X-Admin-Pin 헤더 추가 — CI 복구
-2026-06-26 docs: 커밋 메시지 한국어 작성 규칙 추가 (CLAUDE.md + AGENTS.md </t>
+2026-06-26 frontend: show employee code in admin
+2026-06-26 docs: 피드백 6건 갱신 + codex playwright MCP 설정</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="67.5" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 shipping: 출하 관리 탭과 탭 표시 권한 추가
+2026-06-29 admin: 직원 표시 탭 권한 정리
+2026-06-29 docs: 6/20~26 주간보고 마감 및 개발현황 갱신
+Merge remote-tracking branch 'origin/main' into codex/screen
+Merge pull request #32 from Hw-03/codex/screen-cleanup-a</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="67.5" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30 shipping: 출하 요청 전환 복구와 화면 정리
+2026-06-30 frontend: 출하 PC 화면 흐름 개선
+2026-06-30 frontend: 출하 PC UI 3차 개선
+2026-06-30 frontend: 출하 작성 화면 4차 개선
+2026-06-30 defect: 바로 재작업 품목 선택 UX 정리</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="67.5" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01 shipping: 출하 수량과 준비 화면 개선
+2026-07-01 docs: 클린코드 5원칙 CLAUDE.md·AGENTS.md 규칙화 + 적용 보고서 작
+2026-07-01 backend: 라우터 헬퍼 함수 반환 타입힌트 보강 (11곳)
+2026-07-01 history: 입출고 내역 PC UX 개선 통합
+2026-07-01 mes: 김건호 피드백 처리</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="67.5" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02 frontend: 출하 요청 작성 UX 개선
+2026-07-02 history: 수량 조정 승인자 표시 수정
+2026-07-02 frontend: 권동환 피드백 UI 개선
+2026-07-02 test: 생산 E2E 시드 부서 수정
+2026-07-02 ux: 로그인 알림 팝업 기본값 개선</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="67.5" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03 chore: 직원 서버 동기화 스크립트 + start-backend 좀비 방지
+2026-07-03 frontend: 개발 서버 종료 덤프 기록 추가
+2026-07-03 shipping: 구성품 변경 백엔드 원장 추가
+2026-07-03 shipping: 구성품 변경 독립 화면 추가
+2026-07-03 history: 구성품 변경 내역 표현 정리</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -6565,7 +6952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1174"/>
+  <dimension ref="A1:F1223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43992,22 +44379,22 @@
       </c>
       <c r="B1170" s="15" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C1170" s="15" t="inlineStr">
         <is>
-          <t>b34df2c8</t>
+          <t>e69cc904</t>
         </is>
       </c>
       <c r="D1170" s="16" t="inlineStr">
         <is>
-          <t>2026-06-26 fix: E2E global-setup에 X-Admin-Pin 헤더 추가 — CI 복구</t>
+          <t>2026-06-26 frontend: show employee code in admin</t>
         </is>
       </c>
       <c r="E1170" s="15" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="F1170" s="15" t="inlineStr">
@@ -44024,17 +44411,17 @@
       </c>
       <c r="B1171" s="7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="C1171" s="7" t="inlineStr">
         <is>
-          <t>74b739b3</t>
+          <t>83340cc6</t>
         </is>
       </c>
       <c r="D1171" s="8" t="inlineStr">
         <is>
-          <t>2026-06-26 docs: 커밋 메시지 한국어 작성 규칙 추가 (CLAUDE.md + AGENTS.md 동기)</t>
+          <t>2026-06-26 docs: 피드백 6건 갱신 + codex playwright MCP 설정</t>
         </is>
       </c>
       <c r="E1171" s="7" t="inlineStr">
@@ -44056,22 +44443,22 @@
       </c>
       <c r="B1172" s="15" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="C1172" s="15" t="inlineStr">
         <is>
-          <t>5f96c5ea</t>
+          <t>b34df2c8</t>
         </is>
       </c>
       <c r="D1172" s="16" t="inlineStr">
         <is>
-          <t>2026-06-26 warehouse: 창고 지도 구조 편집과 권한 보존 수정</t>
+          <t>2026-06-26 fix: E2E global-setup에 X-Admin-Pin 헤더 추가 — CI 복구</t>
         </is>
       </c>
       <c r="E1172" s="15" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="F1172" s="15" t="inlineStr">
@@ -44088,22 +44475,22 @@
       </c>
       <c r="B1173" s="7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="C1173" s="7" t="inlineStr">
         <is>
-          <t>a5519e40</t>
+          <t>74b739b3</t>
         </is>
       </c>
       <c r="D1173" s="8" t="inlineStr">
         <is>
-          <t>2026-06-26 frontend: 입출고 내역 안정화와 피드백 문서 갱신</t>
+          <t>2026-06-26 docs: 커밋 메시지 한국어 작성 규칙 추가 (CLAUDE.md + AGENTS.md 동기)</t>
         </is>
       </c>
       <c r="E1173" s="7" t="inlineStr">
         <is>
-          <t>frontend</t>
+          <t>docs</t>
         </is>
       </c>
       <c r="F1173" s="7" t="inlineStr">
@@ -44120,25 +44507,1593 @@
       </c>
       <c r="B1174" s="15" t="inlineStr">
         <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C1174" s="15" t="inlineStr">
+        <is>
+          <t>5f96c5ea</t>
+        </is>
+      </c>
+      <c r="D1174" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-26 warehouse: 창고 지도 구조 편집과 권한 보존 수정</t>
+        </is>
+      </c>
+      <c r="E1174" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1174" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1175" s="7" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C1175" s="7" t="inlineStr">
+        <is>
+          <t>a5519e40</t>
+        </is>
+      </c>
+      <c r="D1175" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26 frontend: 입출고 내역 안정화와 피드백 문서 갱신</t>
+        </is>
+      </c>
+      <c r="E1175" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1175" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1176" s="15" t="inlineStr">
+        <is>
           <t>11:53</t>
         </is>
       </c>
-      <c r="C1174" s="15" t="inlineStr">
+      <c r="C1176" s="15" t="inlineStr">
         <is>
           <t>fe3fbdc2</t>
         </is>
       </c>
-      <c r="D1174" s="16" t="inlineStr">
+      <c r="D1176" s="16" t="inlineStr">
         <is>
           <t>2026-06-26 safety: 운영 검증 안정화</t>
         </is>
       </c>
-      <c r="E1174" s="15" t="inlineStr">
+      <c r="E1176" s="15" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F1174" s="15" t="inlineStr">
+      <c r="F1176" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1177" s="7" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1177" s="7" t="inlineStr">
+        <is>
+          <t>ae1c55f8</t>
+        </is>
+      </c>
+      <c r="D1177" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 shipping: 출하 관리 탭과 탭 표시 권한 추가</t>
+        </is>
+      </c>
+      <c r="E1177" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1177" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1178" s="15" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1178" s="15" t="inlineStr">
+        <is>
+          <t>ce3a43b6</t>
+        </is>
+      </c>
+      <c r="D1178" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 admin: 직원 표시 탭 권한 정리</t>
+        </is>
+      </c>
+      <c r="E1178" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1178" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1179" s="7" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C1179" s="7" t="inlineStr">
+        <is>
+          <t>7b165336</t>
+        </is>
+      </c>
+      <c r="D1179" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 docs: 6/20~26 주간보고 마감 및 개발현황 갱신</t>
+        </is>
+      </c>
+      <c r="E1179" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1179" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1180" s="15" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="C1180" s="15" t="inlineStr">
+        <is>
+          <t>4aae0d18</t>
+        </is>
+      </c>
+      <c r="D1180" s="16" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/main' into codex/screen-cleanup-a</t>
+        </is>
+      </c>
+      <c r="E1180" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1180" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1181" s="7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C1181" s="7" t="inlineStr">
+        <is>
+          <t>287eb743</t>
+        </is>
+      </c>
+      <c r="D1181" s="8" t="inlineStr">
+        <is>
+          <t>Merge pull request #32 from Hw-03/codex/screen-cleanup-a</t>
+        </is>
+      </c>
+      <c r="E1181" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1181" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1182" s="15" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C1182" s="15" t="inlineStr">
+        <is>
+          <t>831a25e0</t>
+        </is>
+      </c>
+      <c r="D1182" s="16" t="inlineStr">
+        <is>
+          <t>Merge pull request #33 from Hw-03/codex/shipping-management</t>
+        </is>
+      </c>
+      <c r="E1182" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1182" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1183" s="7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C1183" s="7" t="inlineStr">
+        <is>
+          <t>e36b187e</t>
+        </is>
+      </c>
+      <c r="D1183" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 docs: 브랜치 전환 금지 규칙 추가 (AGENTS.md + CLAUDE.md 동기)</t>
+        </is>
+      </c>
+      <c r="E1183" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1183" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1184" s="15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1184" s="15" t="inlineStr">
+        <is>
+          <t>cfc92120</t>
+        </is>
+      </c>
+      <c r="D1184" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 defect: 불량 바로 처리 개선</t>
+        </is>
+      </c>
+      <c r="E1184" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1184" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1185" s="7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C1185" s="7" t="inlineStr">
+        <is>
+          <t>d0ccb5e8</t>
+        </is>
+      </c>
+      <c r="D1185" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 ci: OpenAPI baseline 갱신</t>
+        </is>
+      </c>
+      <c r="E1185" s="7" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1185" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1186" s="15" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="C1186" s="15" t="inlineStr">
+        <is>
+          <t>475a4320</t>
+        </is>
+      </c>
+      <c r="D1186" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 shipping: 출하 요청 전환 오류와 PC 작업성 개선</t>
+        </is>
+      </c>
+      <c r="E1186" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1186" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1187" s="7" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="C1187" s="7" t="inlineStr">
+        <is>
+          <t>fb730c52</t>
+        </is>
+      </c>
+      <c r="D1187" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 docs: 비용 비례 검증 정책 명시 (AGENTS.md + CLAUDE.md 동기)</t>
+        </is>
+      </c>
+      <c r="E1187" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1187" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1188" s="15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="C1188" s="15" t="inlineStr">
+        <is>
+          <t>aff67d6f</t>
+        </is>
+      </c>
+      <c r="D1188" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 불량 카트 재작업 출처 고정 + 카테고리 셀렉트 통일</t>
+        </is>
+      </c>
+      <c r="E1188" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1188" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1189" s="7" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C1189" s="7" t="inlineStr">
+        <is>
+          <t>3da0182f</t>
+        </is>
+      </c>
+      <c r="D1189" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 상단 탭 아이콘 색상 동기화</t>
+        </is>
+      </c>
+      <c r="E1189" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1189" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1190" s="15" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="C1190" s="15" t="inlineStr">
+        <is>
+          <t>eb8ece46</t>
+        </is>
+      </c>
+      <c r="D1190" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 chore: verify_local 영역 자동 감지로 게이트 시간 단축</t>
+        </is>
+      </c>
+      <c r="E1190" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1190" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1191" s="7" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="C1191" s="7" t="inlineStr">
+        <is>
+          <t>85b34d4a</t>
+        </is>
+      </c>
+      <c r="D1191" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 불량 E2E spec 을 AppSelect 패턴으로 교체</t>
+        </is>
+      </c>
+      <c r="E1191" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1191" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1192" s="15" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="C1192" s="15" t="inlineStr">
+        <is>
+          <t>8eb0321f</t>
+        </is>
+      </c>
+      <c r="D1192" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 불량 E2E 두 번째 카테고리 선택 dialog 스코프 적용</t>
+        </is>
+      </c>
+      <c r="E1192" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1192" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1193" s="7" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C1193" s="7" t="inlineStr">
+        <is>
+          <t>e39687bc</t>
+        </is>
+      </c>
+      <c r="D1193" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 불량 E2E 처리 모달 카테고리 셀렉트 prefill 대응</t>
+        </is>
+      </c>
+      <c r="E1193" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1193" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1194" s="15" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1194" s="15" t="inlineStr">
+        <is>
+          <t>69e2ff17</t>
+        </is>
+      </c>
+      <c r="D1194" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29 frontend: 불량 E2E 두 번째 셀렉트 원래 native &lt;select&gt; 패턴 복원</t>
+        </is>
+      </c>
+      <c r="E1194" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1194" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1195" s="7" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="C1195" s="7" t="inlineStr">
+        <is>
+          <t>fb5ae877</t>
+        </is>
+      </c>
+      <c r="D1195" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-30 shipping: 출하 요청 전환 복구와 화면 정리</t>
+        </is>
+      </c>
+      <c r="E1195" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1195" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1196" s="15" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C1196" s="15" t="inlineStr">
+        <is>
+          <t>e7efd04f</t>
+        </is>
+      </c>
+      <c r="D1196" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30 frontend: 출하 PC 화면 흐름 개선</t>
+        </is>
+      </c>
+      <c r="E1196" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1196" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1197" s="7" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C1197" s="7" t="inlineStr">
+        <is>
+          <t>d8b878ef</t>
+        </is>
+      </c>
+      <c r="D1197" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-30 frontend: 출하 PC UI 3차 개선</t>
+        </is>
+      </c>
+      <c r="E1197" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1197" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1198" s="15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C1198" s="15" t="inlineStr">
+        <is>
+          <t>26be340e</t>
+        </is>
+      </c>
+      <c r="D1198" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30 frontend: 출하 작성 화면 4차 개선</t>
+        </is>
+      </c>
+      <c r="E1198" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1198" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1199" s="7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1199" s="7" t="inlineStr">
+        <is>
+          <t>f5db79e8</t>
+        </is>
+      </c>
+      <c r="D1199" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-30 defect: 바로 재작업 품목 선택 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1199" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1199" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1200" s="15" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C1200" s="15" t="inlineStr">
+        <is>
+          <t>c1825f1e</t>
+        </is>
+      </c>
+      <c r="D1200" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30 shipping: 출하 PC 화면 밀도 개선</t>
+        </is>
+      </c>
+      <c r="E1200" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1200" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1201" s="7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C1201" s="7" t="inlineStr">
+        <is>
+          <t>8dd946a7</t>
+        </is>
+      </c>
+      <c r="D1201" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-30 docs: 개선 투두와 e2e 조정 정리</t>
+        </is>
+      </c>
+      <c r="E1201" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1201" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1202" s="15" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C1202" s="15" t="inlineStr">
+        <is>
+          <t>642beae4</t>
+        </is>
+      </c>
+      <c r="D1202" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01 shipping: 출하 수량과 준비 화면 개선</t>
+        </is>
+      </c>
+      <c r="E1202" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1202" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1203" s="7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="C1203" s="7" t="inlineStr">
+        <is>
+          <t>9f5e8b33</t>
+        </is>
+      </c>
+      <c r="D1203" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01 docs: 클린코드 5원칙 CLAUDE.md·AGENTS.md 규칙화 + 적용 보고서 작성</t>
+        </is>
+      </c>
+      <c r="E1203" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1203" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1204" s="15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C1204" s="15" t="inlineStr">
+        <is>
+          <t>0c89593a</t>
+        </is>
+      </c>
+      <c r="D1204" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01 backend: 라우터 헬퍼 함수 반환 타입힌트 보강 (11곳)</t>
+        </is>
+      </c>
+      <c r="E1204" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1204" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1205" s="7" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C1205" s="7" t="inlineStr">
+        <is>
+          <t>cb7c457a</t>
+        </is>
+      </c>
+      <c r="D1205" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01 history: 입출고 내역 PC UX 개선 통합</t>
+        </is>
+      </c>
+      <c r="E1205" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1205" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1206" s="15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1206" s="15" t="inlineStr">
+        <is>
+          <t>a928390a</t>
+        </is>
+      </c>
+      <c r="D1206" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01 mes: 김건호 피드백 처리</t>
+        </is>
+      </c>
+      <c r="E1206" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1206" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1207" s="7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C1207" s="7" t="inlineStr">
+        <is>
+          <t>e1c0c56f</t>
+        </is>
+      </c>
+      <c r="D1207" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01 docs: 권동환 피드백 갱신</t>
+        </is>
+      </c>
+      <c r="E1207" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1207" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1208" s="15" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1208" s="15" t="inlineStr">
+        <is>
+          <t>97159092</t>
+        </is>
+      </c>
+      <c r="D1208" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01 history: 입출고 내역 PC UX 정리</t>
+        </is>
+      </c>
+      <c r="E1208" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1208" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1209" s="7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C1209" s="7" t="inlineStr">
+        <is>
+          <t>58f6b3a3</t>
+        </is>
+      </c>
+      <c r="D1209" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01 frontend: 로그인 팝업 스위치 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1209" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1209" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1210" s="15" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C1210" s="15" t="inlineStr">
+        <is>
+          <t>fb372970</t>
+        </is>
+      </c>
+      <c r="D1210" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01 docs: 권동환 피드백 추가</t>
+        </is>
+      </c>
+      <c r="E1210" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1210" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1211" s="7" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C1211" s="7" t="inlineStr">
+        <is>
+          <t>1766210b</t>
+        </is>
+      </c>
+      <c r="D1211" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-02 frontend: 출하 요청 작성 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1211" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1211" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1212" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1212" s="15" t="inlineStr">
+        <is>
+          <t>5103a9c6</t>
+        </is>
+      </c>
+      <c r="D1212" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02 history: 수량 조정 승인자 표시 수정</t>
+        </is>
+      </c>
+      <c r="E1212" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1212" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1213" s="7" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C1213" s="7" t="inlineStr">
+        <is>
+          <t>e048b202</t>
+        </is>
+      </c>
+      <c r="D1213" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-02 frontend: 권동환 피드백 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1213" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1213" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1214" s="15" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="C1214" s="15" t="inlineStr">
+        <is>
+          <t>e9bd2990</t>
+        </is>
+      </c>
+      <c r="D1214" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02 test: 생산 E2E 시드 부서 수정</t>
+        </is>
+      </c>
+      <c r="E1214" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1214" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1215" s="7" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C1215" s="7" t="inlineStr">
+        <is>
+          <t>f414eb12</t>
+        </is>
+      </c>
+      <c r="D1215" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-02 ux: 로그인 알림 팝업 기본값 개선</t>
+        </is>
+      </c>
+      <c r="E1215" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1215" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1216" s="15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1216" s="15" t="inlineStr">
+        <is>
+          <t>617f33bf</t>
+        </is>
+      </c>
+      <c r="D1216" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02 docs: PC 입출고 내역 후속 TODO 추가 + 2607 재고 매칭 산출물 gitignore</t>
+        </is>
+      </c>
+      <c r="E1216" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1216" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1217" s="7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C1217" s="7" t="inlineStr">
+        <is>
+          <t>f6f0f290</t>
+        </is>
+      </c>
+      <c r="D1217" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03 chore: 직원 서버 동기화 스크립트 + start-backend 좀비 방지</t>
+        </is>
+      </c>
+      <c r="E1217" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1217" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1218" s="15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C1218" s="15" t="inlineStr">
+        <is>
+          <t>2817d81a</t>
+        </is>
+      </c>
+      <c r="D1218" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03 frontend: 개발 서버 종료 덤프 기록 추가</t>
+        </is>
+      </c>
+      <c r="E1218" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1218" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1219" s="7" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C1219" s="7" t="inlineStr">
+        <is>
+          <t>95bce339</t>
+        </is>
+      </c>
+      <c r="D1219" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03 shipping: 구성품 변경 백엔드 원장 추가</t>
+        </is>
+      </c>
+      <c r="E1219" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1219" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1220" s="15" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C1220" s="15" t="inlineStr">
+        <is>
+          <t>3ebd6c91</t>
+        </is>
+      </c>
+      <c r="D1220" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03 shipping: 구성품 변경 독립 화면 추가</t>
+        </is>
+      </c>
+      <c r="E1220" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1220" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1221" s="7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C1221" s="7" t="inlineStr">
+        <is>
+          <t>40d67c14</t>
+        </is>
+      </c>
+      <c r="D1221" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03 history: 구성품 변경 내역 표현 정리</t>
+        </is>
+      </c>
+      <c r="E1221" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1221" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1222" s="15" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="C1222" s="15" t="inlineStr">
+        <is>
+          <t>aa625bd8</t>
+        </is>
+      </c>
+      <c r="D1222" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03 chore: 개발/직원 서버 프로파일 자동 감지 스크립트 도입</t>
+        </is>
+      </c>
+      <c r="E1222" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1222" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1223" s="7" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="C1223" s="7" t="inlineStr">
+        <is>
+          <t>e6d10d2b</t>
+        </is>
+      </c>
+      <c r="D1223" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03 docs: 권동환 피드백 신규 항목(출하탭 불필요 코드 정리) 등록</t>
+        </is>
+      </c>
+      <c r="E1223" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1223" s="7" t="inlineStr">
         <is>
           <t>근무</t>
         </is>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1222건 (회사 기간 670건)</t>
+          <t>1353건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>357건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>370건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>91 / 100개 (91%)</t>
+          <t>93 / 102개 (91%)</t>
         </is>
       </c>
     </row>
@@ -2470,78 +2470,351 @@
         </is>
       </c>
     </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-06  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (17)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-07  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-08  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-09  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (15)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-10  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (18)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-13  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-14  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-15  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (14)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-16  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (27)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="79">
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A68:E68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2553,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2969,6 +3242,60 @@
         <v>47</v>
       </c>
     </row>
+    <row r="18" ht="129.6" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-04 ~ 07-10</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>품목 전환 신설 + 입출고 내역 개편</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>품목 전환 기능 신설 (진행 중)
+출하 요청 작성 화면 개선 — 김건호 과장님 피드백
+부서 입출고 BOM·낱개 혼합 요청 지원 — 이형진 사원님 피드백
+입출고 내역 화면 전면 개편 착수 (진행 중)
+모바일 입출고·불량 화면 오류 수정 — 허동현 사원님 피드백
+모바일 알림·헤더·레이아웃 정리 — 이형진 사원님 피드백
+대시보드 스크롤 편의 개선 — 권동환 사원님 피드백
+화면 전환 속도·공통 패널 정리</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" ht="129.6" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11 ~ 07-16</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>출하·입출고 내역 마무리 + 사용출고 신설</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>출하 요청 작성 화면 정리
+출하 요청 오류 수정 — 김건호 과장님 피드백
+출하 최종 확인 화면 다듬기
+품목 전환 화면 마무리 다듬기 (진행 중)
+입출고 내역 화면 구조 개편
+입출고 내역 표시 오류 수정
+AS·연구용 자재 사용출고 처리 신설
+데이터 처리 안정성 강화 — 권동환 사원님 피드백</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2980,7 +3307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5209,52 +5536,52 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="n">
+      <c r="A93" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>품목 전환 기능</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>출하·입출고 중 품목을 다른 품목으로 전환 처리 (진행 중)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="n">
+      <c r="A94" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>AS·연구용 자재 사용출고</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>AS·연구 목적 자재 사용출고 전용 결재·승인 흐름</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5591,12 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>역할별 접근 권한 연동</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -5279,7 +5606,7 @@
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5616,12 @@
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -5304,7 +5631,7 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>재고 가용성 계산 고도화</t>
+          <t>부서 결재·집계·자동화</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5641,12 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -5329,7 +5656,7 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5666,12 @@
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
@@ -5352,7 +5679,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E98" s="13" t="inlineStr"/>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n">
@@ -5360,12 +5691,12 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>외부 접근 환경 구성</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
@@ -5373,7 +5704,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E99" s="13" t="inlineStr"/>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n">
@@ -5381,12 +5716,12 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>발주 관리</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -5394,11 +5729,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E100" s="13" t="inlineStr">
-        <is>
-          <t>사장님 요청 — 검토 중</t>
-        </is>
-      </c>
+      <c r="E100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n">
@@ -5406,20 +5737,66 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C101" s="12" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D101" s="14" t="inlineStr">
+      <c r="D103" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E101" s="13" t="inlineStr">
+      <c r="E103" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -5436,7 +5813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6936,6 +7313,222 @@
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="67.5" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 dev: 개발 직원 서버 실행 로그 깨짐 수정
+2026-07-06 frontend: 탭 전환 캐시와 목록 렌더링 개선
+2026-07-06 docs: 주간보고 개발 현황 갱신
+2026-07-06 docs: 작업 지침 보강
+2026-07-06 frontend: 입출고 품목 전환과 작성 화면 정리</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="67.5" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 docs: 품목 전환 구상과 입출고 UX 메모 정리
+2026-07-07 backend: 품목 전환 API와 원장 처리 추가
+2026-07-07 frontend: 품목 전환 화면과 입출고 작성 흐름 정리
+2026-07-07 docs: 사이드바와 모바일 입출고 TODO 정리
+2026-07-07 frontend: 입출고 작성 화면 UX 정리</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="67.5" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08 ux: 입출고 품목 전환 화면 정리
+2026-07-08 feedback: 미해결 피드백 5건 해결
+2026-07-08 e2e: 입출고 CI 흐름 수정
+2026-07-08 docs: 김현우·이형진 출하 피드백 신규 등록 + UX TODO 핸드오프 2건
+2026-07-08 chore: 직원 서버 입출고 실적 이식 스크립트 + verify 로그 gitignore</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="67.5" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 dev: 관제창 로그 표시 방식 정리
+2026-07-09 출하: 재고 부족 표시와 입출고 혼합 요청 개선
+2026-07-09 ux: PC UI 품목 전환과 출하 흐름 개편
+2026-07-09 docs: 자동화 시간대와 플랜 GOAL 규칙 추가
+2026-07-09 history: 입출고 내역 UX 정리</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="67.5" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 ux: 품목 전환·출하 후속 UX 정리
+2026-07-10 ux: 품목 전환 최종 실행 바 정리
+2026-07-10 ux: 품목 전환 화살표 표현 제거
+2026-07-10 docs: 품목 전환 마감 보완 TODO 추가
+2026-07-10 docs: 주간보고 7/4~7/10 갱신</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="67.5" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13 frontend: 품목 전환 최종 실행 화면 정리
+2026-07-13 frontend: 품목 전환 브라우저 단계 이력 복원
+2026-07-13 docs: 품목 전환 마감 TODO 갱신
+2026-07-13 frontend: 출하 요청 목록 프레임 정리
+2026-07-13 ux: 출하 요청 작성 작업 화면 밀도 정리</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="67.5" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14 history: 입출고 내역 후속 표시 개선 완료
+2026-07-14 test: 입출고 내역 재시도 CI 경쟁 상태 수정
+2026-07-14 ux: 출하 최종 확인 목록 높이 정리
+2026-07-14 ux: 출하 최종 확인 간격 조정
+2026-07-14 shipping: 출하 요청 품명 검증 UX 개선</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="67.5" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 attic: 불필요 보관 파일 정리와 인수인계 갱신
+2026-07-15 history: 입출고 이력 표시 개선
+2026-07-15 shipping: 신규 PA 출하품 표시와 수정 복귀
+2026-07-15 dev: 개발 서버 자동복구와 종료 진단 강화
+2026-07-15 history: 입출고 이력 그룹 조회와 목록 정보 구조 개선</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="67.5" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: 권동환 피드백과 출하 TODO 기록 갱신
+2026-07-16 runtime: 운영 산출물 루트 표준화
+2026-07-16 backup: SQLite 백업·복원 검증 강화
+2026-07-16 migration: Alembic 기준선과 스키마 상태 판별 도입
+2026-07-16 deploy: 직원 서버 배포 실패 안전성 강화</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -6952,7 +7545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1223"/>
+  <dimension ref="A1:F1354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46099,6 +46692,4198 @@
         </is>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1224" s="15" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C1224" s="15" t="inlineStr">
+        <is>
+          <t>13fed55d</t>
+        </is>
+      </c>
+      <c r="D1224" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 dev: 개발 직원 서버 실행 로그 깨짐 수정</t>
+        </is>
+      </c>
+      <c r="E1224" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1224" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1225" s="7" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="C1225" s="7" t="inlineStr">
+        <is>
+          <t>7b4db60f</t>
+        </is>
+      </c>
+      <c r="D1225" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 frontend: 탭 전환 캐시와 목록 렌더링 개선</t>
+        </is>
+      </c>
+      <c r="E1225" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1225" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1226" s="15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="C1226" s="15" t="inlineStr">
+        <is>
+          <t>735c22d8</t>
+        </is>
+      </c>
+      <c r="D1226" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 docs: 주간보고 개발 현황 갱신</t>
+        </is>
+      </c>
+      <c r="E1226" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1226" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1227" s="7" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="C1227" s="7" t="inlineStr">
+        <is>
+          <t>2429e69c</t>
+        </is>
+      </c>
+      <c r="D1227" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 docs: 작업 지침 보강</t>
+        </is>
+      </c>
+      <c r="E1227" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1227" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1228" s="15" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="C1228" s="15" t="inlineStr">
+        <is>
+          <t>a5f09b5a</t>
+        </is>
+      </c>
+      <c r="D1228" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 frontend: 입출고 품목 전환과 작성 화면 정리</t>
+        </is>
+      </c>
+      <c r="E1228" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1228" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1229" s="7" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="C1229" s="7" t="inlineStr">
+        <is>
+          <t>aabca7f7</t>
+        </is>
+      </c>
+      <c r="D1229" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 docs: 권동환 피드백 갱신</t>
+        </is>
+      </c>
+      <c r="E1229" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1229" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1230" s="15" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1230" s="15" t="inlineStr">
+        <is>
+          <t>9e66c450</t>
+        </is>
+      </c>
+      <c r="D1230" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 모바일 공통 화면 유틸 추가</t>
+        </is>
+      </c>
+      <c r="E1230" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1230" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1231" s="7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1231" s="7" t="inlineStr">
+        <is>
+          <t>d01b0c47</t>
+        </is>
+      </c>
+      <c r="D1231" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 모바일 프레임과 바텀시트 폭 고정</t>
+        </is>
+      </c>
+      <c r="E1231" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1231" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1232" s="15" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1232" s="15" t="inlineStr">
+        <is>
+          <t>ec71d0e2</t>
+        </is>
+      </c>
+      <c r="D1232" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 상단 헤더를 더보기로 정리</t>
+        </is>
+      </c>
+      <c r="E1232" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1232" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1233" s="7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1233" s="7" t="inlineStr">
+        <is>
+          <t>7fc982e0</t>
+        </is>
+      </c>
+      <c r="D1233" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 대시보드 재고 목록 정렬 개선</t>
+        </is>
+      </c>
+      <c r="E1233" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1233" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1234" s="15" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1234" s="15" t="inlineStr">
+        <is>
+          <t>341659d8</t>
+        </is>
+      </c>
+      <c r="D1234" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 내역과 출하 카드 폭 정리</t>
+        </is>
+      </c>
+      <c r="E1234" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1234" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1235" s="7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1235" s="7" t="inlineStr">
+        <is>
+          <t>28c36095</t>
+        </is>
+      </c>
+      <c r="D1235" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 warehouse: 모바일 품목 선택 폭 정리</t>
+        </is>
+      </c>
+      <c r="E1235" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1235" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1236" s="15" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1236" s="15" t="inlineStr">
+        <is>
+          <t>177792c1</t>
+        </is>
+      </c>
+      <c r="D1236" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 warehouse: 모바일 단계 전환 압축</t>
+        </is>
+      </c>
+      <c r="E1236" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1236" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1237" s="7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C1237" s="7" t="inlineStr">
+        <is>
+          <t>9671ac21</t>
+        </is>
+      </c>
+      <c r="D1237" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06 defect: 모바일 처리 단계 헤더 압축</t>
+        </is>
+      </c>
+      <c r="E1237" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1237" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1238" s="15" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C1238" s="15" t="inlineStr">
+        <is>
+          <t>746ba9e2</t>
+        </is>
+      </c>
+      <c r="D1238" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06 mobile: 모바일 알림 자동 팝업 제거</t>
+        </is>
+      </c>
+      <c r="E1238" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1238" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1239" s="7" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C1239" s="7" t="inlineStr">
+        <is>
+          <t>1edb287d</t>
+        </is>
+      </c>
+      <c r="D1239" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/mobile-frame-430' into HEAD</t>
+        </is>
+      </c>
+      <c r="E1239" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1239" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1240" s="19" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="C1240" s="19" t="inlineStr">
+        <is>
+          <t>1d8fd4eb</t>
+        </is>
+      </c>
+      <c r="D1240" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06 frontend: 데스크톱 탭 전환 잔상 제거</t>
+        </is>
+      </c>
+      <c r="E1240" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1240" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1241" s="7" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1241" s="7" t="inlineStr">
+        <is>
+          <t>84fd7cc5</t>
+        </is>
+      </c>
+      <c r="D1241" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 docs: 품목 전환 구상과 입출고 UX 메모 정리</t>
+        </is>
+      </c>
+      <c r="E1241" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1241" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1242" s="15" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="C1242" s="15" t="inlineStr">
+        <is>
+          <t>e35ff3ec</t>
+        </is>
+      </c>
+      <c r="D1242" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07 backend: 품목 전환 API와 원장 처리 추가</t>
+        </is>
+      </c>
+      <c r="E1242" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1242" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1243" s="7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="C1243" s="7" t="inlineStr">
+        <is>
+          <t>39e47b5d</t>
+        </is>
+      </c>
+      <c r="D1243" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 frontend: 품목 전환 화면과 입출고 작성 흐름 정리</t>
+        </is>
+      </c>
+      <c r="E1243" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1243" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1244" s="15" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C1244" s="15" t="inlineStr">
+        <is>
+          <t>40103685</t>
+        </is>
+      </c>
+      <c r="D1244" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07 docs: 사이드바와 모바일 입출고 TODO 정리</t>
+        </is>
+      </c>
+      <c r="E1244" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1244" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1245" s="7" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C1245" s="7" t="inlineStr">
+        <is>
+          <t>8ab698d3</t>
+        </is>
+      </c>
+      <c r="D1245" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 frontend: 입출고 작성 화면 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1245" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1245" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1246" s="15" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="C1246" s="15" t="inlineStr">
+        <is>
+          <t>31231a86</t>
+        </is>
+      </c>
+      <c r="D1246" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07 docs: 모바일 입출고 UX TODO 정리</t>
+        </is>
+      </c>
+      <c r="E1246" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1246" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1247" s="7" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C1247" s="7" t="inlineStr">
+        <is>
+          <t>ad727880</t>
+        </is>
+      </c>
+      <c r="D1247" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 backend: BOM 그래프 성능과 탐색 개선</t>
+        </is>
+      </c>
+      <c r="E1247" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1247" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1248" s="15" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C1248" s="15" t="inlineStr">
+        <is>
+          <t>53300f8d</t>
+        </is>
+      </c>
+      <c r="D1248" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07 mobile: 입출고 화면 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1248" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1248" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1249" s="7" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C1249" s="7" t="inlineStr">
+        <is>
+          <t>2ec40c4d</t>
+        </is>
+      </c>
+      <c r="D1249" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 frontend: 사이드바와 스크롤바 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1249" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1249" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1250" s="15" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C1250" s="15" t="inlineStr">
+        <is>
+          <t>4aca414c</t>
+        </is>
+      </c>
+      <c r="D1250" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07 frontend: 입출고 품목 전환 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1250" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1250" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1251" s="7" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1251" s="7" t="inlineStr">
+        <is>
+          <t>f3bf567f</t>
+        </is>
+      </c>
+      <c r="D1251" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07 docs: 피드백 문서 갱신</t>
+        </is>
+      </c>
+      <c r="E1251" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1251" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1252" s="15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C1252" s="15" t="inlineStr">
+        <is>
+          <t>5f195314</t>
+        </is>
+      </c>
+      <c r="D1252" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08 ux: 입출고 품목 전환 화면 정리</t>
+        </is>
+      </c>
+      <c r="E1252" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1252" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1253" s="7" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="C1253" s="7" t="inlineStr">
+        <is>
+          <t>6e8d7db3</t>
+        </is>
+      </c>
+      <c r="D1253" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08 feedback: 미해결 피드백 5건 해결</t>
+        </is>
+      </c>
+      <c r="E1253" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1253" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1254" s="15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C1254" s="15" t="inlineStr">
+        <is>
+          <t>7e0c3153</t>
+        </is>
+      </c>
+      <c r="D1254" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08 e2e: 입출고 CI 흐름 수정</t>
+        </is>
+      </c>
+      <c r="E1254" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1254" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1255" s="7" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1255" s="7" t="inlineStr">
+        <is>
+          <t>b6a4c515</t>
+        </is>
+      </c>
+      <c r="D1255" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08 docs: 김현우·이형진 출하 피드백 신규 등록 + UX TODO 핸드오프 2건</t>
+        </is>
+      </c>
+      <c r="E1255" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1255" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1256" s="15" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1256" s="15" t="inlineStr">
+        <is>
+          <t>e53174e7</t>
+        </is>
+      </c>
+      <c r="D1256" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08 chore: 직원 서버 입출고 실적 이식 스크립트 + verify 로그 gitignore</t>
+        </is>
+      </c>
+      <c r="E1256" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1256" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1257" s="7" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C1257" s="7" t="inlineStr">
+        <is>
+          <t>5a66b6c1</t>
+        </is>
+      </c>
+      <c r="D1257" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08 dev: 서버 실행 관제 배치 개선</t>
+        </is>
+      </c>
+      <c r="E1257" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1257" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1258" s="19" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C1258" s="19" t="inlineStr">
+        <is>
+          <t>57005d2e</t>
+        </is>
+      </c>
+      <c r="D1258" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08 common: 공통 모달과 패널 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1258" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1258" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1259" s="19" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C1259" s="19" t="inlineStr">
+        <is>
+          <t>c4a3240d</t>
+        </is>
+      </c>
+      <c r="D1259" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08 history: 입출고내역 펼침과 상세 연동 개선</t>
+        </is>
+      </c>
+      <c r="E1259" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1259" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1260" s="19" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C1260" s="19" t="inlineStr">
+        <is>
+          <t>b5d7a188</t>
+        </is>
+      </c>
+      <c r="D1260" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08 warehouse: 입출고와 품목 전환 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1260" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1260" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1261" s="19" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C1261" s="19" t="inlineStr">
+        <is>
+          <t>617aa877</t>
+        </is>
+      </c>
+      <c r="D1261" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08 shipping: 출하 요청 작성 화면 정보 위계 개선</t>
+        </is>
+      </c>
+      <c r="E1261" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1261" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1262" s="19" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C1262" s="19" t="inlineStr">
+        <is>
+          <t>7a98af2a</t>
+        </is>
+      </c>
+      <c r="D1262" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-08 dev: 관제창 분할 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1262" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1262" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1263" s="7" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="C1263" s="7" t="inlineStr">
+        <is>
+          <t>cb555ef6</t>
+        </is>
+      </c>
+      <c r="D1263" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 dev: 관제창 로그 표시 방식 정리</t>
+        </is>
+      </c>
+      <c r="E1263" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1263" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1264" s="15" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C1264" s="15" t="inlineStr">
+        <is>
+          <t>807bfcd2</t>
+        </is>
+      </c>
+      <c r="D1264" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 출하: 재고 부족 표시와 입출고 혼합 요청 개선</t>
+        </is>
+      </c>
+      <c r="E1264" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1264" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1265" s="7" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C1265" s="7" t="inlineStr">
+        <is>
+          <t>d9afe308</t>
+        </is>
+      </c>
+      <c r="D1265" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 ux: PC UI 품목 전환과 출하 흐름 개편</t>
+        </is>
+      </c>
+      <c r="E1265" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1265" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1266" s="15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="C1266" s="15" t="inlineStr">
+        <is>
+          <t>b4ffd528</t>
+        </is>
+      </c>
+      <c r="D1266" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 docs: 자동화 시간대와 플랜 GOAL 규칙 추가</t>
+        </is>
+      </c>
+      <c r="E1266" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1266" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1267" s="7" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C1267" s="7" t="inlineStr">
+        <is>
+          <t>ce01f879</t>
+        </is>
+      </c>
+      <c r="D1267" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 history: 입출고 내역 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1267" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1267" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1268" s="15" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C1268" s="15" t="inlineStr">
+        <is>
+          <t>a83dbb4f</t>
+        </is>
+      </c>
+      <c r="D1268" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 chore: E2E job 실패가 워크플로우 전체 실패로 승격되지 않도록 조정</t>
+        </is>
+      </c>
+      <c r="E1268" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1268" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1269" s="7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C1269" s="7" t="inlineStr">
+        <is>
+          <t>f075b15d</t>
+        </is>
+      </c>
+      <c r="D1269" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 docs: PC UI/UX 및 입출고 내역 개선 TODO 핸드오프 3건</t>
+        </is>
+      </c>
+      <c r="E1269" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1269" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1270" s="15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="C1270" s="15" t="inlineStr">
+        <is>
+          <t>213da504</t>
+        </is>
+      </c>
+      <c r="D1270" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 ux: PC 입출고 후속 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1270" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1270" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1271" s="7" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="C1271" s="7" t="inlineStr">
+        <is>
+          <t>a2fc4152</t>
+        </is>
+      </c>
+      <c r="D1271" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 docs: 입출고 내역 후속 TODO 정리</t>
+        </is>
+      </c>
+      <c r="E1271" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1271" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1272" s="15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="C1272" s="15" t="inlineStr">
+        <is>
+          <t>37c2fb46</t>
+        </is>
+      </c>
+      <c r="D1272" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 logs: 원본 로그 사용자 이벤트 보강</t>
+        </is>
+      </c>
+      <c r="E1272" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1272" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1273" s="7" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C1273" s="7" t="inlineStr">
+        <is>
+          <t>aed8de19</t>
+        </is>
+      </c>
+      <c r="D1273" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 docs: 김재헌 피드백 추가</t>
+        </is>
+      </c>
+      <c r="E1273" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1273" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1274" s="15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C1274" s="15" t="inlineStr">
+        <is>
+          <t>b5617fd1</t>
+        </is>
+      </c>
+      <c r="D1274" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 monitor: 프론트 오류 로그 강조</t>
+        </is>
+      </c>
+      <c r="E1274" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1274" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1275" s="7" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1275" s="7" t="inlineStr">
+        <is>
+          <t>c1cde5c9</t>
+        </is>
+      </c>
+      <c r="D1275" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 history: 상세 패널 표 밀림 수정</t>
+        </is>
+      </c>
+      <c r="E1275" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1275" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1276" s="15" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C1276" s="15" t="inlineStr">
+        <is>
+          <t>31a1b837</t>
+        </is>
+      </c>
+      <c r="D1276" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09 frontend: 모바일 불량 격리 선택창 개선</t>
+        </is>
+      </c>
+      <c r="E1276" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1276" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1277" s="7" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C1277" s="7" t="inlineStr">
+        <is>
+          <t>9fbe0ab8</t>
+        </is>
+      </c>
+      <c r="D1277" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09 frontend: CI 입출고 E2E 기준 보정</t>
+        </is>
+      </c>
+      <c r="E1277" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1277" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1278" s="15" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C1278" s="15" t="inlineStr">
+        <is>
+          <t>562d4e9f</t>
+        </is>
+      </c>
+      <c r="D1278" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 ux: 품목 전환·출하 후속 UX 정리</t>
+        </is>
+      </c>
+      <c r="E1278" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1278" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1279" s="7" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C1279" s="7" t="inlineStr">
+        <is>
+          <t>d19f12f6</t>
+        </is>
+      </c>
+      <c r="D1279" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 ux: 품목 전환 최종 실행 바 정리</t>
+        </is>
+      </c>
+      <c r="E1279" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1279" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1280" s="15" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C1280" s="15" t="inlineStr">
+        <is>
+          <t>d8785ddb</t>
+        </is>
+      </c>
+      <c r="D1280" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 ux: 품목 전환 화살표 표현 제거</t>
+        </is>
+      </c>
+      <c r="E1280" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1280" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1281" s="7" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C1281" s="7" t="inlineStr">
+        <is>
+          <t>09362172</t>
+        </is>
+      </c>
+      <c r="D1281" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: 품목 전환 마감 보완 TODO 추가</t>
+        </is>
+      </c>
+      <c r="E1281" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1281" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1282" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1282" s="15" t="inlineStr">
+        <is>
+          <t>eff9a85b</t>
+        </is>
+      </c>
+      <c r="D1282" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: 주간보고 7/4~7/10 갱신</t>
+        </is>
+      </c>
+      <c r="E1282" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1282" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1283" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1283" s="7" t="inlineStr">
+        <is>
+          <t>9e737362</t>
+        </is>
+      </c>
+      <c r="D1283" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: 외부반출 피드백 추가</t>
+        </is>
+      </c>
+      <c r="E1283" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1283" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1284" s="15" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="C1284" s="15" t="inlineStr">
+        <is>
+          <t>2575f8f3</t>
+        </is>
+      </c>
+      <c r="D1284" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: Codex 5.6 모델 선택 규칙 갱신</t>
+        </is>
+      </c>
+      <c r="E1284" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1284" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1285" s="7" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1285" s="7" t="inlineStr">
+        <is>
+          <t>7a3dbd96</t>
+        </is>
+      </c>
+      <c r="D1285" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: 플랜 스킬의 GPT-5.6 추천 기준 갱신</t>
+        </is>
+      </c>
+      <c r="E1285" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1285" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1286" s="15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C1286" s="15" t="inlineStr">
+        <is>
+          <t>5b64126f</t>
+        </is>
+      </c>
+      <c r="D1286" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 history: 품목 전환 요청자 기록</t>
+        </is>
+      </c>
+      <c r="E1286" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1286" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1287" s="7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1287" s="7" t="inlineStr">
+        <is>
+          <t>62130281</t>
+        </is>
+      </c>
+      <c r="D1287" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 defect: 직접 처리 사유와 감사 이력 보존</t>
+        </is>
+      </c>
+      <c r="E1287" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1287" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1288" s="15" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C1288" s="15" t="inlineStr">
+        <is>
+          <t>05f690b7</t>
+        </is>
+      </c>
+      <c r="D1288" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 history: 목록 표현과 묶음 행 정리</t>
+        </is>
+      </c>
+      <c r="E1288" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1288" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1289" s="7" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C1289" s="7" t="inlineStr">
+        <is>
+          <t>14b66e73</t>
+        </is>
+      </c>
+      <c r="D1289" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10 history: 상세 취소와 키포인트 패널 개선</t>
+        </is>
+      </c>
+      <c r="E1289" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1289" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1290" s="15" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C1290" s="15" t="inlineStr">
+        <is>
+          <t>81769672</t>
+        </is>
+      </c>
+      <c r="D1290" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10 history: 검증 기준과 TODO 갱신</t>
+        </is>
+      </c>
+      <c r="E1290" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1290" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1291" s="19" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1291" s="19" t="inlineStr">
+        <is>
+          <t>336036fb</t>
+        </is>
+      </c>
+      <c r="D1291" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10 history: 작업 묶음 조회 테스트 보강</t>
+        </is>
+      </c>
+      <c r="E1291" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1291" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1292" s="19" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1292" s="19" t="inlineStr">
+        <is>
+          <t>354fe4a8</t>
+        </is>
+      </c>
+      <c r="D1292" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10 frontend: PWA 매니페스트와 앱 아이콘 추가</t>
+        </is>
+      </c>
+      <c r="E1292" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1292" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1293" s="19" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1293" s="19" t="inlineStr">
+        <is>
+          <t>46899580</t>
+        </is>
+      </c>
+      <c r="D1293" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10 data: 품목 코드 공백 재번호 도구 추가</t>
+        </is>
+      </c>
+      <c r="E1293" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1293" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1294" s="19" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1294" s="19" t="inlineStr">
+        <is>
+          <t>d86fa542</t>
+        </is>
+      </c>
+      <c r="D1294" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10 data: 부서 안전재고 보충 도구 추가</t>
+        </is>
+      </c>
+      <c r="E1294" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1294" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1295" s="19" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1295" s="19" t="inlineStr">
+        <is>
+          <t>238ba116</t>
+        </is>
+      </c>
+      <c r="D1295" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10 docs: 코드 품질 개선 조사 기록</t>
+        </is>
+      </c>
+      <c r="E1295" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1295" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1296" s="15" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C1296" s="15" t="inlineStr">
+        <is>
+          <t>82afb6ea</t>
+        </is>
+      </c>
+      <c r="D1296" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13 frontend: 품목 전환 최종 실행 화면 정리</t>
+        </is>
+      </c>
+      <c r="E1296" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1296" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1297" s="7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C1297" s="7" t="inlineStr">
+        <is>
+          <t>020b5f6a</t>
+        </is>
+      </c>
+      <c r="D1297" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13 frontend: 품목 전환 브라우저 단계 이력 복원</t>
+        </is>
+      </c>
+      <c r="E1297" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1297" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1298" s="15" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C1298" s="15" t="inlineStr">
+        <is>
+          <t>3049fca9</t>
+        </is>
+      </c>
+      <c r="D1298" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13 docs: 품목 전환 마감 TODO 갱신</t>
+        </is>
+      </c>
+      <c r="E1298" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1298" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1299" s="7" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C1299" s="7" t="inlineStr">
+        <is>
+          <t>60591090</t>
+        </is>
+      </c>
+      <c r="D1299" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13 frontend: 출하 요청 목록 프레임 정리</t>
+        </is>
+      </c>
+      <c r="E1299" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1299" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1300" s="15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C1300" s="15" t="inlineStr">
+        <is>
+          <t>3c90da3e</t>
+        </is>
+      </c>
+      <c r="D1300" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13 ux: 출하 요청 작성 작업 화면 밀도 정리</t>
+        </is>
+      </c>
+      <c r="E1300" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1300" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1301" s="7" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="C1301" s="7" t="inlineStr">
+        <is>
+          <t>cee1d861</t>
+        </is>
+      </c>
+      <c r="D1301" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13 docs: 출하 후속 UI TODO 정리</t>
+        </is>
+      </c>
+      <c r="E1301" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1301" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1302" s="15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C1302" s="15" t="inlineStr">
+        <is>
+          <t>c515bed4</t>
+        </is>
+      </c>
+      <c r="D1302" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13 data: 입출고 검증 쇼케이스 생성 도구 추가</t>
+        </is>
+      </c>
+      <c r="E1302" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1302" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1303" s="7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1303" s="7" t="inlineStr">
+        <is>
+          <t>23bec886</t>
+        </is>
+      </c>
+      <c r="D1303" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13 history: 묶음 하위 상세와 목록 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1303" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1303" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1304" s="15" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C1304" s="15" t="inlineStr">
+        <is>
+          <t>f2fdc82c</t>
+        </is>
+      </c>
+      <c r="D1304" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13 docs: 입출고 내역 후속 TODO 정리</t>
+        </is>
+      </c>
+      <c r="E1304" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1304" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1305" s="19" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C1305" s="19" t="inlineStr">
+        <is>
+          <t>a10f3175</t>
+        </is>
+      </c>
+      <c r="D1305" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-14 history: 입출고 내역 후속 표시 개선 완료</t>
+        </is>
+      </c>
+      <c r="E1305" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1305" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1306" s="19" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="C1306" s="19" t="inlineStr">
+        <is>
+          <t>264d36c0</t>
+        </is>
+      </c>
+      <c r="D1306" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-14 test: 입출고 내역 재시도 CI 경쟁 상태 수정</t>
+        </is>
+      </c>
+      <c r="E1306" s="19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1306" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1307" s="7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C1307" s="7" t="inlineStr">
+        <is>
+          <t>d6721124</t>
+        </is>
+      </c>
+      <c r="D1307" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14 ux: 출하 최종 확인 목록 높이 정리</t>
+        </is>
+      </c>
+      <c r="E1307" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1307" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1308" s="15" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C1308" s="15" t="inlineStr">
+        <is>
+          <t>14e81821</t>
+        </is>
+      </c>
+      <c r="D1308" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14 ux: 출하 최종 확인 간격 조정</t>
+        </is>
+      </c>
+      <c r="E1308" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1308" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1309" s="7" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C1309" s="7" t="inlineStr">
+        <is>
+          <t>63d1632c</t>
+        </is>
+      </c>
+      <c r="D1309" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14 shipping: 출하 요청 품명 검증 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1309" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1309" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1310" s="15" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1310" s="15" t="inlineStr">
+        <is>
+          <t>86595404</t>
+        </is>
+      </c>
+      <c r="D1310" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14 history: 입출고 내역 후속 표시와 분류 개선</t>
+        </is>
+      </c>
+      <c r="E1310" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1310" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1311" s="7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C1311" s="7" t="inlineStr">
+        <is>
+          <t>8873a583</t>
+        </is>
+      </c>
+      <c r="D1311" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14 shipping: 준비 완료 요청 잠금 안내 정리</t>
+        </is>
+      </c>
+      <c r="E1311" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1311" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1312" s="15" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C1312" s="15" t="inlineStr">
+        <is>
+          <t>b641cd62</t>
+        </is>
+      </c>
+      <c r="D1312" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14 history: 수량보정 중복 생성과 표시 수정</t>
+        </is>
+      </c>
+      <c r="E1312" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1312" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1313" s="7" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C1313" s="7" t="inlineStr">
+        <is>
+          <t>685e0774</t>
+        </is>
+      </c>
+      <c r="D1313" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14 inventory: AS·연구 사용출고와 품목 전환 권한 구현</t>
+        </is>
+      </c>
+      <c r="E1313" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1313" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1314" s="15" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C1314" s="15" t="inlineStr">
+        <is>
+          <t>cc37d739</t>
+        </is>
+      </c>
+      <c r="D1314" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 attic: 불필요 보관 파일 정리와 인수인계 갱신</t>
+        </is>
+      </c>
+      <c r="E1314" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1314" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1315" s="7" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C1315" s="7" t="inlineStr">
+        <is>
+          <t>0b4c158e</t>
+        </is>
+      </c>
+      <c r="D1315" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 history: 입출고 이력 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1315" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1315" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1316" s="15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="C1316" s="15" t="inlineStr">
+        <is>
+          <t>5742346e</t>
+        </is>
+      </c>
+      <c r="D1316" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 shipping: 신규 PA 출하품 표시와 수정 복귀</t>
+        </is>
+      </c>
+      <c r="E1316" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1316" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1317" s="7" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C1317" s="7" t="inlineStr">
+        <is>
+          <t>3fdff5ac</t>
+        </is>
+      </c>
+      <c r="D1317" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 dev: 개발 서버 자동복구와 종료 진단 강화</t>
+        </is>
+      </c>
+      <c r="E1317" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1317" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1318" s="15" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C1318" s="15" t="inlineStr">
+        <is>
+          <t>25ff8201</t>
+        </is>
+      </c>
+      <c r="D1318" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 history: 입출고 이력 그룹 조회와 목록 정보 구조 개선</t>
+        </is>
+      </c>
+      <c r="E1318" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1318" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1319" s="7" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C1319" s="7" t="inlineStr">
+        <is>
+          <t>0466adcf</t>
+        </is>
+      </c>
+      <c r="D1319" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 shipping: 출하 화면 UI 정리</t>
+        </is>
+      </c>
+      <c r="E1319" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1319" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1320" s="15" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C1320" s="15" t="inlineStr">
+        <is>
+          <t>d4837d24</t>
+        </is>
+      </c>
+      <c r="D1320" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/shipping-ui-polish'</t>
+        </is>
+      </c>
+      <c r="E1320" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1320" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1321" s="7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C1321" s="7" t="inlineStr">
+        <is>
+          <t>0adf1f56</t>
+        </is>
+      </c>
+      <c r="D1321" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 frontend: 출하 구성품 코드 강조 개선</t>
+        </is>
+      </c>
+      <c r="E1321" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1321" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1322" s="15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="C1322" s="15" t="inlineStr">
+        <is>
+          <t>2f81ece2</t>
+        </is>
+      </c>
+      <c r="D1322" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 history: 입출고 내역 후속 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1322" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1322" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1323" s="7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="C1323" s="7" t="inlineStr">
+        <is>
+          <t>66785d05</t>
+        </is>
+      </c>
+      <c r="D1323" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 frontend: 출하 최종 확인 비율 복구</t>
+        </is>
+      </c>
+      <c r="E1323" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1323" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1324" s="15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C1324" s="15" t="inlineStr">
+        <is>
+          <t>d5d93b43</t>
+        </is>
+      </c>
+      <c r="D1324" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 docs: 피드백 및 UI 후속 문서 갱신</t>
+        </is>
+      </c>
+      <c r="E1324" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1324" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1325" s="7" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="C1325" s="7" t="inlineStr">
+        <is>
+          <t>0983d74d</t>
+        </is>
+      </c>
+      <c r="D1325" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 bom: BOM 표시 순서 표준화</t>
+        </is>
+      </c>
+      <c r="E1325" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1325" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1326" s="15" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C1326" s="15" t="inlineStr">
+        <is>
+          <t>a4d2ba0a</t>
+        </is>
+      </c>
+      <c r="D1326" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15 shipping: 출하 요청 BOM 표시와 최종 확인 레이아웃 개선</t>
+        </is>
+      </c>
+      <c r="E1326" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1326" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1327" s="7" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1327" s="7" t="inlineStr">
+        <is>
+          <t>fca27eb7</t>
+        </is>
+      </c>
+      <c r="D1327" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15 shipping: 출하 요청 예상 코드와 화면 요약 개선</t>
+        </is>
+      </c>
+      <c r="E1327" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1327" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1328" s="15" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1328" s="15" t="inlineStr">
+        <is>
+          <t>0f09067f</t>
+        </is>
+      </c>
+      <c r="D1328" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: 권동환 피드백과 출하 TODO 기록 갱신</t>
+        </is>
+      </c>
+      <c r="E1328" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1328" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1329" s="7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1329" s="7" t="inlineStr">
+        <is>
+          <t>e830a54f</t>
+        </is>
+      </c>
+      <c r="D1329" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 runtime: 운영 산출물 루트 표준화</t>
+        </is>
+      </c>
+      <c r="E1329" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1329" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1330" s="15" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C1330" s="15" t="inlineStr">
+        <is>
+          <t>60cf7ba7</t>
+        </is>
+      </c>
+      <c r="D1330" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 backup: SQLite 백업·복원 검증 강화</t>
+        </is>
+      </c>
+      <c r="E1330" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1330" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1331" s="7" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="C1331" s="7" t="inlineStr">
+        <is>
+          <t>8dc85913</t>
+        </is>
+      </c>
+      <c r="D1331" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 migration: Alembic 기준선과 스키마 상태 판별 도입</t>
+        </is>
+      </c>
+      <c r="E1331" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1331" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1332" s="15" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1332" s="15" t="inlineStr">
+        <is>
+          <t>19266643</t>
+        </is>
+      </c>
+      <c r="D1332" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 deploy: 직원 서버 배포 실패 안전성 강화</t>
+        </is>
+      </c>
+      <c r="E1332" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1332" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1333" s="7" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1333" s="7" t="inlineStr">
+        <is>
+          <t>aa118680</t>
+        </is>
+      </c>
+      <c r="D1333" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 backend: 최상위 트랜잭션 컨텍스트 추가</t>
+        </is>
+      </c>
+      <c r="E1333" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1333" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1334" s="15" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1334" s="15" t="inlineStr">
+        <is>
+          <t>717c7c56</t>
+        </is>
+      </c>
+      <c r="D1334" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 defect: 불량 처리 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1334" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1334" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1335" s="7" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1335" s="7" t="inlineStr">
+        <is>
+          <t>67e7529e</t>
+        </is>
+      </c>
+      <c r="D1335" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 dept: 부서 조정 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1335" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1335" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1336" s="15" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="C1336" s="15" t="inlineStr">
+        <is>
+          <t>ce2bccd7</t>
+        </is>
+      </c>
+      <c r="D1336" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 handover: 인수인계 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1336" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1336" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1337" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1337" s="7" t="inlineStr">
+        <is>
+          <t>e13b365f</t>
+        </is>
+      </c>
+      <c r="D1337" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 production: 생산 입고 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1337" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1337" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1338" s="15" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1338" s="15" t="inlineStr">
+        <is>
+          <t>625fdfb9</t>
+        </is>
+      </c>
+      <c r="D1338" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 inventory: 거래 보정과 취소 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1338" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1338" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1339" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1339" s="7" t="inlineStr">
+        <is>
+          <t>3828a2ab</t>
+        </is>
+      </c>
+      <c r="D1339" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 shipping: 출하 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1339" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1339" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1340" s="15" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1340" s="15" t="inlineStr">
+        <is>
+          <t>70314b8f</t>
+        </is>
+      </c>
+      <c r="D1340" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 io: 다라인 입출고 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1340" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1340" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1341" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1341" s="7" t="inlineStr">
+        <is>
+          <t>b6adc363</t>
+        </is>
+      </c>
+      <c r="D1341" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 stock: 재고 요청 생명주기 원자성을 서비스로 이전</t>
+        </is>
+      </c>
+      <c r="E1341" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1341" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1342" s="15" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1342" s="15" t="inlineStr">
+        <is>
+          <t>a8feee3c</t>
+        </is>
+      </c>
+      <c r="D1342" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 dev: 이력 쇼케이스에 최상위 트랜잭션 적용</t>
+        </is>
+      </c>
+      <c r="E1342" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1342" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1343" s="7" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1343" s="7" t="inlineStr">
+        <is>
+          <t>cfb936e9</t>
+        </is>
+      </c>
+      <c r="D1343" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 warehouse: R1 동시성 잠금과 성능 검증 추가</t>
+        </is>
+      </c>
+      <c r="E1343" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1343" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1344" s="15" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1344" s="15" t="inlineStr">
+        <is>
+          <t>b60bba6b</t>
+        </is>
+      </c>
+      <c r="D1344" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: AI 공통 컨텍스트 진입점 추가</t>
+        </is>
+      </c>
+      <c r="E1344" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1344" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1345" s="7" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1345" s="7" t="inlineStr">
+        <is>
+          <t>b52661c3</t>
+        </is>
+      </c>
+      <c r="D1345" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: 백업 배포 런타임 운영 문서 동기화</t>
+        </is>
+      </c>
+      <c r="E1345" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1345" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1346" s="15" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1346" s="15" t="inlineStr">
+        <is>
+          <t>e15c87ab</t>
+        </is>
+      </c>
+      <c r="D1346" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 ci: 플랫폼별 테스트 조건 정합화</t>
+        </is>
+      </c>
+      <c r="E1346" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1346" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1347" s="7" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C1347" s="7" t="inlineStr">
+        <is>
+          <t>06fa9af8</t>
+        </is>
+      </c>
+      <c r="D1347" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 frontend: 출하 최종 확인 BOM 계층과 높이 조정</t>
+        </is>
+      </c>
+      <c r="E1347" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1347" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1348" s="15" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C1348" s="15" t="inlineStr">
+        <is>
+          <t>f73fb941</t>
+        </is>
+      </c>
+      <c r="D1348" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 shipping: 5단계 최종 카드 크기 고정</t>
+        </is>
+      </c>
+      <c r="E1348" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1348" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1349" s="7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C1349" s="7" t="inlineStr">
+        <is>
+          <t>00c88a9e</t>
+        </is>
+      </c>
+      <c r="D1349" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 history: PC 입출고 내역 UX 후속 개선</t>
+        </is>
+      </c>
+      <c r="E1349" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1349" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1350" s="15" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="C1350" s="15" t="inlineStr">
+        <is>
+          <t>095b8aa4</t>
+        </is>
+      </c>
+      <c r="D1350" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: 검증 게이트 재실행 기준 보완</t>
+        </is>
+      </c>
+      <c r="E1350" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1350" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1351" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C1351" s="7" t="inlineStr">
+        <is>
+          <t>1935e729</t>
+        </is>
+      </c>
+      <c r="D1351" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 history: 입출고 내역 정보 표시 간소화</t>
+        </is>
+      </c>
+      <c r="E1351" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1351" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1352" s="15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C1352" s="15" t="inlineStr">
+        <is>
+          <t>b3728103</t>
+        </is>
+      </c>
+      <c r="D1352" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 ci: 번들 크기 게이트 여유와 표시 정밀도 보완</t>
+        </is>
+      </c>
+      <c r="E1352" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1352" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1353" s="7" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C1353" s="7" t="inlineStr">
+        <is>
+          <t>8954d855</t>
+        </is>
+      </c>
+      <c r="D1353" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 shipping: 출하 공정 색상과 최종 확인 정리</t>
+        </is>
+      </c>
+      <c r="E1353" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1353" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1354" s="15" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C1354" s="15" t="inlineStr">
+        <is>
+          <t>3617b188</t>
+        </is>
+      </c>
+      <c r="D1354" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 history: 입출고 내역 UX 후속 정리</t>
+        </is>
+      </c>
+      <c r="E1354" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1354" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1353건 (회사 기간 670건)</t>
+          <t>1479건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>370건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>379건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>93 / 102개 (91%)</t>
+          <t>98 / 107개 (92%)</t>
         </is>
       </c>
     </row>
@@ -2722,39 +2722,368 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■■■■■■■■■■■■■</t>
+            <t>■■■■■■■■■■■■■■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (27)</t>
+            <t xml:space="preserve">  (29)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-20  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (5)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-21  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-22  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (8)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-23  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (10)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-24  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-27  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (8)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-07-28  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (6)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-03  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (13)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-04  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (23)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-05  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (18)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-06  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="79">
+  <mergeCells count="90">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A91:E91"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A69:E69"/>
@@ -2775,14 +3104,17 @@
     <mergeCell ref="A67:E67"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A22:E22"/>
@@ -2798,15 +3130,18 @@
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A35:E35"/>
@@ -2815,6 +3150,7 @@
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2826,7 +3162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3293,7 +3629,56 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>59</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" ht="81" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17 ~ 07-24</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>모바일 체크리스트 + 관리자 정비</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>모바일 조립 체크리스트 신설 — 교차 확인 검증
+관리자 목록·탐색 구조 개편, 화면 시각적 통일
+입출고 내역 담당자·상세 패널 정비, 탭 전환 속도 개선
+대시보드 세션·상세, 생산 가능수량 팝업 정리
+출하·창고 사용성 개선, 출하 요청 개선 착수</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" ht="97.19999999999999" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-25 ~ 08-07</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>출하 개선 완료 + 설정 화면 통합</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>출하 요청 인보이스·이력 관리 개선 완료 (인보이스·수정이력·이력검색)
+개인 일일 작업 일지 신설
+관리자 내보내기 화면 정리 — F704-02·F705-02
+모바일 조립 체크리스트 박스 간 이동 추가
+설정 화면 통합(테마·사이드바), 다크 모드 색상 개선
+품목 표시 순서 통일, 화면 실시간 갱신 적용</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3307,7 +3692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5586,127 +5971,123 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="n">
+      <c r="A95" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>모바일 조립 체크리스트</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>교차 확인 검증 + 항목 관리·박스 간 이동</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="12" t="n">
+      <c r="A96" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>자재 입출고관리대장(F704-02)·연간 생산일지(F705-02) 다운로드</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>내보내기 화면에 BOM 다운로드 통합</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
+      <c r="A97" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>출하 인보이스·수정이력 관리</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>출하</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>준비완료 조건·모바일 안내·이력검색</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="12" t="n">
+      <c r="A98" s="9" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="inlineStr">
-        <is>
-          <t>재고 가용성 계산 고도화</t>
-        </is>
-      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>개인 일일 작업 일지</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="n">
+      <c r="A99" s="9" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>외부 접근 환경 구성</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr">
-        <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>설정 화면 통합</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>테마·사이드바 고정을 한 화면에서 관리</t>
         </is>
       </c>
     </row>
@@ -5716,12 +6097,12 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -5729,7 +6110,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E100" s="13" t="inlineStr"/>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>BOM·입출고 정리 후</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n">
@@ -5737,7 +6122,7 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -5750,7 +6135,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E101" s="13" t="inlineStr"/>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n">
@@ -5758,12 +6147,12 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -5773,7 +6162,7 @@
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
@@ -5783,20 +6172,137 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D103" s="14" t="inlineStr">
+      <c r="D108" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E103" s="13" t="inlineStr">
+      <c r="E108" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -5813,7 +6319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7517,7 +8023,7 @@
         </is>
       </c>
       <c r="B72" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
@@ -7529,6 +8035,270 @@
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="67.5" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20 history: 입출고 내역 표현과 부서 분류 정비
+2026-07-20 backend: 기존 SQLite DB Alembic 안전 온보딩
+2026-07-20 history: 입출고 내역 탭 전환 방식 정리 및 성능 개선
+2026-07-20 history: 완료 재고 이력 필터 정렬
+2026-07-20 desktop: 이력 담당자와 상세 패널 개선</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="67.5" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 frontend: 이력 상세와 공통 UI 가독성 개선
+2026-07-21 mobile: 생산 가능수량 상세 개선 투두 추가
+Merge branch 'codex/ui-followup-20260721'
+2026-07-21 history: 이력 라벨 검사 기준 정리
+2026-07-21 docs: 대시보드와 관리자 후속 투두 추가</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="67.5" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22 admin: 관리자 화면 정보 밀도와 탐색 구조 정리
+2026-07-22 frontend: 대시보드 상세 UI 정리
+2026-07-22 docs: 완료된 handoff 문서 archive/ 로 이동 + 새 작업 TODO 통합
+2026-07-22 warehouse: 초안 이어서 작업 단계 복원 수정
+2026-07-22 ux: 관리자·입출고 UX 개선</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="67.5" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 mobile: 사용자 메뉴와 체크리스트 개선
+2026-07-23 mobile: 체크리스트 완료 표시 정리
+2026-07-23 admin: 공통 레이아웃 여백과 액션 정리
+2026-07-23 admin: 직원과 부서 상세 높이 배분 정비
+2026-07-23 admin: 모델 목록과 상세 영역 비율 조정</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="67.5" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24 backend: F704-02 자재 입출고관리대장 내보내기 추가
+2026-07-24 frontend: F704-02 대장 다운로드 화면 추가
+2026-07-24 backend: F705-02 연간 생산일지 생성 추가
+2026-07-24 frontend: F705-02 생산일지 내보내기 추가
+Merge branch 'codex/f704-02-audit-ledger-impl'</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="67.5" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-27 shipping: 영업부 출하 운영 개선
+2026-07-27 deploy: 직원 동기화 스크립트와 운영 문서 갱신
+2026-07-27 deploy: 직원 동기화와 출하 이력 CI 수정
+2026-07-27 backend: 출하 구성품 마이그레이션 보존
+2026-07-27 frontend: 작업자 탭 세션과 로그인 알림 복구</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="67.5" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28 mes: 출하 연결 폐기와 관리자 BOM UX 정리
+2026-07-28 mes: 데스크톱·모바일 공통 흐름 개선
+2026-07-28 test: 반응형 전환 저장 보호 검증
+2026-07-28 mes: 개인 일일 작업 일지 추가
+2026-07-28 mobile: 조립 체크리스트 문구 수정과 박스 간 이동 추가</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="67.5" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 docs: gitignore 정리 + 출하 영업 확인 정책 수정 + 재고 검증 계획 문서
+2026-08-03 daily-report: 일일 작업 일보 화면 정비
+2026-08-03 chore: 디렉터리 정책과 런타임 산출물 정리
+2026-08-03 frontend: 출하 요청 인보이스 유지 오류 수정
+2026-08-03 admin: 내보내기 화면 정리 및 BOM 다운로드 통합</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="67.5" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 admin: BOM 표 헤더 가독성 조정
+2026-08-04 frontend: 입출고 요청 일시 표시 통일
+2026-08-04 frontend: 부분 BOM 경고를 상세 화면으로 이동
+2026-08-04 admin: F704 비고 원본 메모만 표시
+2026-08-04 frontend: 일일 작업 일보 저장 및 여백 개선</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="67.5" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 frontend: 부서 색상 팔레트 고압/튜닝 값 조정
+2026-08-05 ops: 직원 서버 동기화 dry-run 파일 클래스 리포팅 복원
+2026-08-05 docs: 품목코드 표시 정렬 통일 계획 문서
+2026-08-05 docs: 설정 모달 통합 계획 문서
+2026-08-05 archive: 통합 전 루트 WIP 복구본</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="67.5" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 items: 품목 공통 표시 순서 적용
+2026-08-06 ux: 설정 모달 목록형 구성 개선
+2026-08-06 daily-report: 빈 일보 화면 스크롤 조정
+2026-08-06 ui: 품목 등록 필수값 및 표 정렬 정비
+2026-08-06 ops: 자동 동기화에서 소스 git 상태 가드 제거</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -7545,7 +8315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1354"/>
+  <dimension ref="A1:F1480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50884,6 +51654,4038 @@
         </is>
       </c>
     </row>
+    <row r="1355">
+      <c r="A1355" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1355" s="7" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C1355" s="7" t="inlineStr">
+        <is>
+          <t>eccf6400</t>
+        </is>
+      </c>
+      <c r="D1355" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16 docs: 주간보고 7/11~7/16 갱신 및 개발현황 반영</t>
+        </is>
+      </c>
+      <c r="E1355" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1355" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1356" s="15" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C1356" s="15" t="inlineStr">
+        <is>
+          <t>40a5d969</t>
+        </is>
+      </c>
+      <c r="D1356" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16 history: 입출고 상세 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1356" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1356" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1357" s="7" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="C1357" s="7" t="inlineStr">
+        <is>
+          <t>2109f3fc</t>
+        </is>
+      </c>
+      <c r="D1357" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20 history: 입출고 내역 표현과 부서 분류 정비</t>
+        </is>
+      </c>
+      <c r="E1357" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1357" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1358" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1358" s="15" t="inlineStr">
+        <is>
+          <t>790200b9</t>
+        </is>
+      </c>
+      <c r="D1358" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20 backend: 기존 SQLite DB Alembic 안전 온보딩</t>
+        </is>
+      </c>
+      <c r="E1358" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1358" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1359" s="7" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C1359" s="7" t="inlineStr">
+        <is>
+          <t>25e7bf4f</t>
+        </is>
+      </c>
+      <c r="D1359" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20 history: 입출고 내역 탭 전환 방식 정리 및 성능 개선</t>
+        </is>
+      </c>
+      <c r="E1359" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1359" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1360" s="15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C1360" s="15" t="inlineStr">
+        <is>
+          <t>73dfacc0</t>
+        </is>
+      </c>
+      <c r="D1360" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20 history: 완료 재고 이력 필터 정렬</t>
+        </is>
+      </c>
+      <c r="E1360" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1360" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1361" s="7" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C1361" s="7" t="inlineStr">
+        <is>
+          <t>925e2ba5</t>
+        </is>
+      </c>
+      <c r="D1361" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20 desktop: 이력 담당자와 상세 패널 개선</t>
+        </is>
+      </c>
+      <c r="E1361" s="7" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F1361" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1362" s="15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C1362" s="15" t="inlineStr">
+        <is>
+          <t>8143f3fc</t>
+        </is>
+      </c>
+      <c r="D1362" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 frontend: 이력 상세와 공통 UI 가독성 개선</t>
+        </is>
+      </c>
+      <c r="E1362" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1362" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1363" s="7" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C1363" s="7" t="inlineStr">
+        <is>
+          <t>4724a0db</t>
+        </is>
+      </c>
+      <c r="D1363" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21 mobile: 생산 가능수량 상세 개선 투두 추가</t>
+        </is>
+      </c>
+      <c r="E1363" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1363" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1364" s="15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C1364" s="15" t="inlineStr">
+        <is>
+          <t>e3ea4e1f</t>
+        </is>
+      </c>
+      <c r="D1364" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/ui-followup-20260721'</t>
+        </is>
+      </c>
+      <c r="E1364" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1364" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1365" s="7" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="C1365" s="7" t="inlineStr">
+        <is>
+          <t>cbcc36e0</t>
+        </is>
+      </c>
+      <c r="D1365" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21 history: 이력 라벨 검사 기준 정리</t>
+        </is>
+      </c>
+      <c r="E1365" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1365" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1366" s="15" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C1366" s="15" t="inlineStr">
+        <is>
+          <t>166eb106</t>
+        </is>
+      </c>
+      <c r="D1366" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 docs: 대시보드와 관리자 후속 투두 추가</t>
+        </is>
+      </c>
+      <c r="E1366" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1366" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1367" s="7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C1367" s="7" t="inlineStr">
+        <is>
+          <t>446ce28c</t>
+        </is>
+      </c>
+      <c r="D1367" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21 admin: 관리자 UI 작업 영역 개선</t>
+        </is>
+      </c>
+      <c r="E1367" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1367" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1368" s="15" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="C1368" s="15" t="inlineStr">
+        <is>
+          <t>e3ae7f40</t>
+        </is>
+      </c>
+      <c r="D1368" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 admin: 관리자 후속 UX와 인증 다운로드 수정</t>
+        </is>
+      </c>
+      <c r="E1368" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1368" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1369" s="7" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C1369" s="7" t="inlineStr">
+        <is>
+          <t>cbe732b8</t>
+        </is>
+      </c>
+      <c r="D1369" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21 dashboard: 대시보드 세션 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1369" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1369" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1370" s="15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1370" s="15" t="inlineStr">
+        <is>
+          <t>33005eec</t>
+        </is>
+      </c>
+      <c r="D1370" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 dashboard: 대시보드 세션 UI 개선 병합</t>
+        </is>
+      </c>
+      <c r="E1370" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1370" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1371" s="7" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C1371" s="7" t="inlineStr">
+        <is>
+          <t>7634a3bf</t>
+        </is>
+      </c>
+      <c r="D1371" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21 ux: 생산 가능수량 팝업 모델 구조 정리 + 입출고 카드 반응형 재구성</t>
+        </is>
+      </c>
+      <c r="E1371" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1371" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1372" s="15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="C1372" s="15" t="inlineStr">
+        <is>
+          <t>a91f75b1</t>
+        </is>
+      </c>
+      <c r="D1372" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21 frontend: 번들 크기 게이트 여유 조정</t>
+        </is>
+      </c>
+      <c r="E1372" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1372" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1373" s="19" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C1373" s="19" t="inlineStr">
+        <is>
+          <t>f70cc0e2</t>
+        </is>
+      </c>
+      <c r="D1373" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-22 admin: 관리자 화면 정보 밀도와 탐색 구조 정리</t>
+        </is>
+      </c>
+      <c r="E1373" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1373" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1374" s="15" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C1374" s="15" t="inlineStr">
+        <is>
+          <t>530e419d</t>
+        </is>
+      </c>
+      <c r="D1374" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22 frontend: 대시보드 상세 UI 정리</t>
+        </is>
+      </c>
+      <c r="E1374" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1374" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1375" s="7" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C1375" s="7" t="inlineStr">
+        <is>
+          <t>f5fc9afd</t>
+        </is>
+      </c>
+      <c r="D1375" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22 docs: 완료된 handoff 문서 archive/ 로 이동 + 새 작업 TODO 통합본 시작</t>
+        </is>
+      </c>
+      <c r="E1375" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1375" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1376" s="15" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C1376" s="15" t="inlineStr">
+        <is>
+          <t>6aec5e71</t>
+        </is>
+      </c>
+      <c r="D1376" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22 warehouse: 초안 이어서 작업 단계 복원 수정</t>
+        </is>
+      </c>
+      <c r="E1376" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1376" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1377" s="7" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C1377" s="7" t="inlineStr">
+        <is>
+          <t>eb1dbba8</t>
+        </is>
+      </c>
+      <c r="D1377" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22 ux: 관리자·입출고 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1377" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1377" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1378" s="15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C1378" s="15" t="inlineStr">
+        <is>
+          <t>14189c13</t>
+        </is>
+      </c>
+      <c r="D1378" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22 admin: 관리자 UX 후속 개선</t>
+        </is>
+      </c>
+      <c r="E1378" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1378" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1379" s="7" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C1379" s="7" t="inlineStr">
+        <is>
+          <t>cca5eaaf</t>
+        </is>
+      </c>
+      <c r="D1379" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22 mobile: 조립 체크리스트 추가</t>
+        </is>
+      </c>
+      <c r="E1379" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1379" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1380" s="19" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C1380" s="19" t="inlineStr">
+        <is>
+          <t>bddfe2d7</t>
+        </is>
+      </c>
+      <c r="D1380" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-22 mobile: 더보기 메뉴 흐름 정리</t>
+        </is>
+      </c>
+      <c r="E1380" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1380" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1381" s="7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C1381" s="7" t="inlineStr">
+        <is>
+          <t>a9a0c40e</t>
+        </is>
+      </c>
+      <c r="D1381" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 mobile: 사용자 메뉴와 체크리스트 개선</t>
+        </is>
+      </c>
+      <c r="E1381" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1381" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1382" s="15" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C1382" s="15" t="inlineStr">
+        <is>
+          <t>ba199eb3</t>
+        </is>
+      </c>
+      <c r="D1382" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 mobile: 체크리스트 완료 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1382" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1382" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1383" s="7" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C1383" s="7" t="inlineStr">
+        <is>
+          <t>0ada229b</t>
+        </is>
+      </c>
+      <c r="D1383" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 admin: 공통 레이아웃 여백과 액션 정리</t>
+        </is>
+      </c>
+      <c r="E1383" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1383" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1384" s="15" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C1384" s="15" t="inlineStr">
+        <is>
+          <t>542a92cd</t>
+        </is>
+      </c>
+      <c r="D1384" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 admin: 직원과 부서 상세 높이 배분 정비</t>
+        </is>
+      </c>
+      <c r="E1384" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1384" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1385" s="7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C1385" s="7" t="inlineStr">
+        <is>
+          <t>c79988e6</t>
+        </is>
+      </c>
+      <c r="D1385" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 admin: 모델 목록과 상세 영역 비율 조정</t>
+        </is>
+      </c>
+      <c r="E1385" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1385" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1386" s="15" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C1386" s="15" t="inlineStr">
+        <is>
+          <t>0f89d282</t>
+        </is>
+      </c>
+      <c r="D1386" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 items: 기본 정보 필드 순서 재배치</t>
+        </is>
+      </c>
+      <c r="E1386" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1386" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1387" s="7" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C1387" s="7" t="inlineStr">
+        <is>
+          <t>f1314da5</t>
+        </is>
+      </c>
+      <c r="D1387" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 items: 목록과 상세 삭제 동작 통일</t>
+        </is>
+      </c>
+      <c r="E1387" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1387" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1388" s="15" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C1388" s="15" t="inlineStr">
+        <is>
+          <t>824dae49</t>
+        </is>
+      </c>
+      <c r="D1388" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 bom: 작업대 목록을 표 형식으로 통일</t>
+        </is>
+      </c>
+      <c r="E1388" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1388" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1389" s="7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C1389" s="7" t="inlineStr">
+        <is>
+          <t>25c213ea</t>
+        </is>
+      </c>
+      <c r="D1389" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 frontend: 관리자 UI 번들 예산 반영</t>
+        </is>
+      </c>
+      <c r="E1389" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1389" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1390" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1390" s="15" t="inlineStr">
+        <is>
+          <t>64108a92</t>
+        </is>
+      </c>
+      <c r="D1390" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23 admin: 관리자 목록과 BOM 행 시각 언어 통일</t>
+        </is>
+      </c>
+      <c r="E1390" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1390" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1391" s="7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1391" s="7" t="inlineStr">
+        <is>
+          <t>2d79e3b2</t>
+        </is>
+      </c>
+      <c r="D1391" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24 backend: F704-02 자재 입출고관리대장 내보내기 추가</t>
+        </is>
+      </c>
+      <c r="E1391" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1391" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1392" s="15" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C1392" s="15" t="inlineStr">
+        <is>
+          <t>4aec9c19</t>
+        </is>
+      </c>
+      <c r="D1392" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24 frontend: F704-02 대장 다운로드 화면 추가</t>
+        </is>
+      </c>
+      <c r="E1392" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1392" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1393" s="7" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C1393" s="7" t="inlineStr">
+        <is>
+          <t>06d96c28</t>
+        </is>
+      </c>
+      <c r="D1393" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24 backend: F705-02 연간 생산일지 생성 추가</t>
+        </is>
+      </c>
+      <c r="E1393" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1393" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1394" s="15" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="C1394" s="15" t="inlineStr">
+        <is>
+          <t>eac1e487</t>
+        </is>
+      </c>
+      <c r="D1394" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24 frontend: F705-02 생산일지 내보내기 추가</t>
+        </is>
+      </c>
+      <c r="E1394" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1394" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1395" s="7" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C1395" s="7" t="inlineStr">
+        <is>
+          <t>00e29261</t>
+        </is>
+      </c>
+      <c r="D1395" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/f704-02-audit-ledger-impl'</t>
+        </is>
+      </c>
+      <c r="E1395" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1395" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1396" s="15" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C1396" s="15" t="inlineStr">
+        <is>
+          <t>aa3bc840</t>
+        </is>
+      </c>
+      <c r="D1396" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24 docs: 관리자 UI 후속 작업 인계 기록</t>
+        </is>
+      </c>
+      <c r="E1396" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1396" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1397" s="7" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="C1397" s="7" t="inlineStr">
+        <is>
+          <t>8e802fd4</t>
+        </is>
+      </c>
+      <c r="D1397" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24 dev: 검증 범위와 번들 예산 정합화</t>
+        </is>
+      </c>
+      <c r="E1397" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1397" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1398" s="15" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C1398" s="15" t="inlineStr">
+        <is>
+          <t>ce285008</t>
+        </is>
+      </c>
+      <c r="D1398" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24 shipping: 출하 수량 스테퍼와 TODO 기록</t>
+        </is>
+      </c>
+      <c r="E1398" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1398" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1399" s="7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C1399" s="7" t="inlineStr">
+        <is>
+          <t>17f0df6c</t>
+        </is>
+      </c>
+      <c r="D1399" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24 mobile: 조립 체크리스트 관리와 항목 삭제 추가</t>
+        </is>
+      </c>
+      <c r="E1399" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1399" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1400" s="19" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="C1400" s="19" t="inlineStr">
+        <is>
+          <t>2d3d8eb5</t>
+        </is>
+      </c>
+      <c r="D1400" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-24 search: 공백 및 구분기호 무시 검색 적용</t>
+        </is>
+      </c>
+      <c r="E1400" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1400" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1401" s="19" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C1401" s="19" t="inlineStr">
+        <is>
+          <t>6f94c49b</t>
+        </is>
+      </c>
+      <c r="D1401" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-24 backend: 작성 중 재고 부족 재검증 수정</t>
+        </is>
+      </c>
+      <c r="E1401" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1401" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1402" s="19" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="C1402" s="19" t="inlineStr">
+        <is>
+          <t>66e81743</t>
+        </is>
+      </c>
+      <c r="D1402" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27 shipping: 영업부 출하 운영 개선</t>
+        </is>
+      </c>
+      <c r="E1402" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1402" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1403" s="7" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C1403" s="7" t="inlineStr">
+        <is>
+          <t>e44379e6</t>
+        </is>
+      </c>
+      <c r="D1403" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27 deploy: 직원 동기화 스크립트와 운영 문서 갱신</t>
+        </is>
+      </c>
+      <c r="E1403" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1403" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1404" s="15" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="C1404" s="15" t="inlineStr">
+        <is>
+          <t>15ae1064</t>
+        </is>
+      </c>
+      <c r="D1404" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-27 deploy: 직원 동기화와 출하 이력 CI 수정</t>
+        </is>
+      </c>
+      <c r="E1404" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1404" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1405" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C1405" s="7" t="inlineStr">
+        <is>
+          <t>2822bb75</t>
+        </is>
+      </c>
+      <c r="D1405" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27 backend: 출하 구성품 마이그레이션 보존</t>
+        </is>
+      </c>
+      <c r="E1405" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1405" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1406" s="15" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C1406" s="15" t="inlineStr">
+        <is>
+          <t>ccd836cd</t>
+        </is>
+      </c>
+      <c r="D1406" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-27 frontend: 작업자 탭 세션과 로그인 알림 복구</t>
+        </is>
+      </c>
+      <c r="E1406" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1406" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1407" s="7" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C1407" s="7" t="inlineStr">
+        <is>
+          <t>5b7f7fd6</t>
+        </is>
+      </c>
+      <c r="D1407" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27 shipping: 출하 준비 이력 연동 정합성 수정</t>
+        </is>
+      </c>
+      <c r="E1407" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1407" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1408" s="15" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C1408" s="15" t="inlineStr">
+        <is>
+          <t>b4897734</t>
+        </is>
+      </c>
+      <c r="D1408" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-27 shipping: 출하 준비를 재고 예약 기준으로 변경</t>
+        </is>
+      </c>
+      <c r="E1408" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1408" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1409" s="7" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C1409" s="7" t="inlineStr">
+        <is>
+          <t>2677f3be</t>
+        </is>
+      </c>
+      <c r="D1409" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27 shipping: 출하 SN 입력과 인보이스 중복 허용</t>
+        </is>
+      </c>
+      <c r="E1409" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1409" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1410" s="15" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C1410" s="15" t="inlineStr">
+        <is>
+          <t>025c8abd</t>
+        </is>
+      </c>
+      <c r="D1410" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-28 mes: 출하 연결 폐기와 관리자 BOM UX 정리</t>
+        </is>
+      </c>
+      <c r="E1410" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1410" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1411" s="7" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C1411" s="7" t="inlineStr">
+        <is>
+          <t>9f5a34da</t>
+        </is>
+      </c>
+      <c r="D1411" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28 mes: 데스크톱·모바일 공통 흐름 개선</t>
+        </is>
+      </c>
+      <c r="E1411" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1411" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1412" s="15" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C1412" s="15" t="inlineStr">
+        <is>
+          <t>49321981</t>
+        </is>
+      </c>
+      <c r="D1412" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-28 test: 반응형 전환 저장 보호 검증</t>
+        </is>
+      </c>
+      <c r="E1412" s="15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1412" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1413" s="7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C1413" s="7" t="inlineStr">
+        <is>
+          <t>d6781453</t>
+        </is>
+      </c>
+      <c r="D1413" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28 mes: 개인 일일 작업 일지 추가</t>
+        </is>
+      </c>
+      <c r="E1413" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1413" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1414" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C1414" s="15" t="inlineStr">
+        <is>
+          <t>6e66bfcd</t>
+        </is>
+      </c>
+      <c r="D1414" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-28 mobile: 조립 체크리스트 문구 수정과 박스 간 이동 추가</t>
+        </is>
+      </c>
+      <c r="E1414" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1414" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1415" s="7" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C1415" s="7" t="inlineStr">
+        <is>
+          <t>ab67bc6a</t>
+        </is>
+      </c>
+      <c r="D1415" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28 mes: 관리자·출하 UI와 스키마 보정</t>
+        </is>
+      </c>
+      <c r="E1415" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1415" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1416" s="15" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="C1416" s="15" t="inlineStr">
+        <is>
+          <t>d0eb3232</t>
+        </is>
+      </c>
+      <c r="D1416" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 docs: gitignore 정리 + 출하 영업 확인 정책 수정 + 재고 검증 계획 문서</t>
+        </is>
+      </c>
+      <c r="E1416" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1416" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1417" s="7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C1417" s="7" t="inlineStr">
+        <is>
+          <t>1677f2d3</t>
+        </is>
+      </c>
+      <c r="D1417" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03 daily-report: 일일 작업 일보 화면 정비</t>
+        </is>
+      </c>
+      <c r="E1417" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1417" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1418" s="15" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C1418" s="15" t="inlineStr">
+        <is>
+          <t>e5566f77</t>
+        </is>
+      </c>
+      <c r="D1418" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 chore: 디렉터리 정책과 런타임 산출물 정리</t>
+        </is>
+      </c>
+      <c r="E1418" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1418" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1419" s="7" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="C1419" s="7" t="inlineStr">
+        <is>
+          <t>f69ba096</t>
+        </is>
+      </c>
+      <c r="D1419" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03 frontend: 출하 요청 인보이스 유지 오류 수정</t>
+        </is>
+      </c>
+      <c r="E1419" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1419" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1420" s="15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C1420" s="15" t="inlineStr">
+        <is>
+          <t>ff5e1e26</t>
+        </is>
+      </c>
+      <c r="D1420" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 admin: 내보내기 화면 정리 및 BOM 다운로드 통합</t>
+        </is>
+      </c>
+      <c r="E1420" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1420" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1421" s="7" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="C1421" s="7" t="inlineStr">
+        <is>
+          <t>30645b9f</t>
+        </is>
+      </c>
+      <c r="D1421" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03 daily-report: 일일 작업 일보 거래 기록 개선</t>
+        </is>
+      </c>
+      <c r="E1421" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1421" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1422" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1422" s="15" t="inlineStr">
+        <is>
+          <t>92deb1bc</t>
+        </is>
+      </c>
+      <c r="D1422" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 frontend: 관리자 BOM 및 이력 UI 정리</t>
+        </is>
+      </c>
+      <c r="E1422" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1422" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1423" s="7" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C1423" s="7" t="inlineStr">
+        <is>
+          <t>1210235a</t>
+        </is>
+      </c>
+      <c r="D1423" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03 assembly: 체크리스트 섹션 이름수정·삭제·순서저장 추가</t>
+        </is>
+      </c>
+      <c r="E1423" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1423" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1424" s="15" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="C1424" s="15" t="inlineStr">
+        <is>
+          <t>7c2ce0a6</t>
+        </is>
+      </c>
+      <c r="D1424" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 ops: 직원 서버 자동배포 스키마 안전장치 추가</t>
+        </is>
+      </c>
+      <c r="E1424" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1424" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1425" s="7" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="C1425" s="7" t="inlineStr">
+        <is>
+          <t>258c3703</t>
+        </is>
+      </c>
+      <c r="D1425" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03 chore: 번들 크기 게이트 여유 조정 (2.20MB → 2.25MB)</t>
+        </is>
+      </c>
+      <c r="E1425" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1425" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1426" s="15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C1426" s="15" t="inlineStr">
+        <is>
+          <t>763ef683</t>
+        </is>
+      </c>
+      <c r="D1426" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-03 docs: 관리자 내보내기 카드 분리 계획 문서 3건</t>
+        </is>
+      </c>
+      <c r="E1426" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1426" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1427" s="19" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="C1427" s="19" t="inlineStr">
+        <is>
+          <t>f442cdb6</t>
+        </is>
+      </c>
+      <c r="D1427" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-03 daily-report: 일일 작업 일보 정렬과 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1427" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1427" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1428" s="19" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C1428" s="19" t="inlineStr">
+        <is>
+          <t>69a257a6</t>
+        </is>
+      </c>
+      <c r="D1428" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-03 mobile: 조립 체크리스트 관리 UX 재구성</t>
+        </is>
+      </c>
+      <c r="E1428" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1428" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1429" s="19" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="C1429" s="19" t="inlineStr">
+        <is>
+          <t>9e4db5d0</t>
+        </is>
+      </c>
+      <c r="D1429" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-04 admin: BOM 표 헤더 가독성 조정</t>
+        </is>
+      </c>
+      <c r="E1429" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1429" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1430" s="15" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C1430" s="15" t="inlineStr">
+        <is>
+          <t>52415365</t>
+        </is>
+      </c>
+      <c r="D1430" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 입출고 요청 일시 표시 통일</t>
+        </is>
+      </c>
+      <c r="E1430" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1430" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1431" s="7" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C1431" s="7" t="inlineStr">
+        <is>
+          <t>8433575d</t>
+        </is>
+      </c>
+      <c r="D1431" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 부분 BOM 경고를 상세 화면으로 이동</t>
+        </is>
+      </c>
+      <c r="E1431" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1431" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1432" s="15" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="C1432" s="15" t="inlineStr">
+        <is>
+          <t>7540e0ce</t>
+        </is>
+      </c>
+      <c r="D1432" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 admin: F704 비고 원본 메모만 표시</t>
+        </is>
+      </c>
+      <c r="E1432" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1432" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1433" s="7" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C1433" s="7" t="inlineStr">
+        <is>
+          <t>d4fe022c</t>
+        </is>
+      </c>
+      <c r="D1433" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 일일 작업 일보 저장 및 여백 개선</t>
+        </is>
+      </c>
+      <c r="E1433" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1433" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1434" s="15" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C1434" s="15" t="inlineStr">
+        <is>
+          <t>856dbeeb</t>
+        </is>
+      </c>
+      <c r="D1434" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 backend: F704-02 자재 입출고대장 양식 정리</t>
+        </is>
+      </c>
+      <c r="E1434" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1434" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1435" s="7" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="C1435" s="7" t="inlineStr">
+        <is>
+          <t>32c15c2a</t>
+        </is>
+      </c>
+      <c r="D1435" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 다크 모드 색상 체계 개선</t>
+        </is>
+      </c>
+      <c r="E1435" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1435" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1436" s="15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C1436" s="15" t="inlineStr">
+        <is>
+          <t>2b069bdd</t>
+        </is>
+      </c>
+      <c r="D1436" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/dark-mode-palette'</t>
+        </is>
+      </c>
+      <c r="E1436" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1436" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1437" s="7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C1437" s="7" t="inlineStr">
+        <is>
+          <t>aba4d2b0</t>
+        </is>
+      </c>
+      <c r="D1437" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 backend: F704 다운로드 서식 및 Excel 열림 수정</t>
+        </is>
+      </c>
+      <c r="E1437" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1437" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1438" s="15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C1438" s="15" t="inlineStr">
+        <is>
+          <t>65dacaa9</t>
+        </is>
+      </c>
+      <c r="D1438" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 daily-report: 작업 내역 높이와 가독성 조정</t>
+        </is>
+      </c>
+      <c r="E1438" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1438" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1439" s="7" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C1439" s="7" t="inlineStr">
+        <is>
+          <t>15ff3e4e</t>
+        </is>
+      </c>
+      <c r="D1439" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 부서 색상 테마 정비</t>
+        </is>
+      </c>
+      <c r="E1439" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1439" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1440" s="15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C1440" s="15" t="inlineStr">
+        <is>
+          <t>5d60ba7b</t>
+        </is>
+      </c>
+      <c r="D1440" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 shipping: 픽업 완료 취소 및 부족재고 창고에서 담기 추가</t>
+        </is>
+      </c>
+      <c r="E1440" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1440" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1441" s="7" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="C1441" s="7" t="inlineStr">
+        <is>
+          <t>5bfbe658</t>
+        </is>
+      </c>
+      <c r="D1441" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 chore: 브레인스토밍 스킬 런타임 상태 파일 무시</t>
+        </is>
+      </c>
+      <c r="E1441" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1441" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1442" s="15" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C1442" s="15" t="inlineStr">
+        <is>
+          <t>ca3c2f2b</t>
+        </is>
+      </c>
+      <c r="D1442" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 부서 색상 대비 조정</t>
+        </is>
+      </c>
+      <c r="E1442" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1442" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1443" s="7" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="C1443" s="7" t="inlineStr">
+        <is>
+          <t>6af70ffd</t>
+        </is>
+      </c>
+      <c r="D1443" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 ux: 직원별 사이드바 고정 모드 추가</t>
+        </is>
+      </c>
+      <c r="E1443" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1443" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1444" s="15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C1444" s="15" t="inlineStr">
+        <is>
+          <t>2744d938</t>
+        </is>
+      </c>
+      <c r="D1444" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 shipping: 픽업 완료 취소 및 부족재고 창고에서 담기 추가</t>
+        </is>
+      </c>
+      <c r="E1444" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1444" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1445" s="7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C1445" s="7" t="inlineStr">
+        <is>
+          <t>beae7edf</t>
+        </is>
+      </c>
+      <c r="D1445" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 관리자 내보내기 단일 카드 통합</t>
+        </is>
+      </c>
+      <c r="E1445" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1445" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1446" s="15" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="C1446" s="15" t="inlineStr">
+        <is>
+          <t>fd20472e</t>
+        </is>
+      </c>
+      <c r="D1446" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04 weekly: 주간 재고 증가·감소 분리 표시</t>
+        </is>
+      </c>
+      <c r="E1446" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1446" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1447" s="7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1447" s="7" t="inlineStr">
+        <is>
+          <t>46d0f13d</t>
+        </is>
+      </c>
+      <c r="D1447" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 설정 모달로 테마와 사이드바 통합</t>
+        </is>
+      </c>
+      <c r="E1447" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1447" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1448" s="15" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1448" s="15" t="inlineStr">
+        <is>
+          <t>998a4b9c</t>
+        </is>
+      </c>
+      <c r="D1448" s="16" t="inlineStr">
+        <is>
+          <t>Merge remote-tracking branch 'origin/main' into codex/settings-modal</t>
+        </is>
+      </c>
+      <c r="E1448" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1448" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1449" s="7" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C1449" s="7" t="inlineStr">
+        <is>
+          <t>a82e908d</t>
+        </is>
+      </c>
+      <c r="D1449" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 품목코드 모델기호 정렬 통일</t>
+        </is>
+      </c>
+      <c r="E1449" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1449" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1450" s="19" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C1450" s="19" t="inlineStr">
+        <is>
+          <t>f3bf63e8</t>
+        </is>
+      </c>
+      <c r="D1450" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-04 realtime: 수량·품목 변경 즉시 갱신</t>
+        </is>
+      </c>
+      <c r="E1450" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1450" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1451" s="7" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C1451" s="7" t="inlineStr">
+        <is>
+          <t>f8796ba4</t>
+        </is>
+      </c>
+      <c r="D1451" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 frontend: 부서 색상 팔레트 고압/튜닝 값 조정</t>
+        </is>
+      </c>
+      <c r="E1451" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1451" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1452" s="15" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C1452" s="15" t="inlineStr">
+        <is>
+          <t>0d19361b</t>
+        </is>
+      </c>
+      <c r="D1452" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 ops: 직원 서버 동기화 dry-run 파일 클래스 리포팅 복원</t>
+        </is>
+      </c>
+      <c r="E1452" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1452" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1453" s="7" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C1453" s="7" t="inlineStr">
+        <is>
+          <t>4ef43f60</t>
+        </is>
+      </c>
+      <c r="D1453" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 docs: 품목코드 표시 정렬 통일 계획 문서</t>
+        </is>
+      </c>
+      <c r="E1453" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1453" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1454" s="15" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C1454" s="15" t="inlineStr">
+        <is>
+          <t>62e38928</t>
+        </is>
+      </c>
+      <c r="D1454" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 docs: 설정 모달 통합 계획 문서</t>
+        </is>
+      </c>
+      <c r="E1454" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1454" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1455" s="7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1455" s="7" t="inlineStr">
+        <is>
+          <t>335fc1b3</t>
+        </is>
+      </c>
+      <c r="D1455" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 frontend: 설정 모달로 테마와 사이드바 통합</t>
+        </is>
+      </c>
+      <c r="E1455" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1455" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1456" s="15" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1456" s="15" t="inlineStr">
+        <is>
+          <t>406a7270</t>
+        </is>
+      </c>
+      <c r="D1456" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 archive: 통합 전 루트 WIP 복구본</t>
+        </is>
+      </c>
+      <c r="E1456" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1456" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1457" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1457" s="7" t="inlineStr">
+        <is>
+          <t>d29aa35a</t>
+        </is>
+      </c>
+      <c r="D1457" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 archive: 통합 전 감사 WIP 복구본</t>
+        </is>
+      </c>
+      <c r="E1457" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1457" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1458" s="15" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1458" s="15" t="inlineStr">
+        <is>
+          <t>99f3c608</t>
+        </is>
+      </c>
+      <c r="D1458" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 archive: 분리 HEAD staged WIP 복구본</t>
+        </is>
+      </c>
+      <c r="E1458" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1458" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1459" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1459" s="7" t="inlineStr">
+        <is>
+          <t>364b3956</t>
+        </is>
+      </c>
+      <c r="D1459" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 archive: 분리 HEAD unstaged WIP 복구본</t>
+        </is>
+      </c>
+      <c r="E1459" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1459" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1460" s="15" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1460" s="15" t="inlineStr">
+        <is>
+          <t>ca5b362f</t>
+        </is>
+      </c>
+      <c r="D1460" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/settings-modal' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1460" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1460" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1461" s="7" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="C1461" s="7" t="inlineStr">
+        <is>
+          <t>18b40b62</t>
+        </is>
+      </c>
+      <c r="D1461" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/shipping-shortage-pickup-cancel' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1461" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1461" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1462" s="15" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C1462" s="15" t="inlineStr">
+        <is>
+          <t>c187322d</t>
+        </is>
+      </c>
+      <c r="D1462" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'recovery/consolidation-20260805-root' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1462" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1462" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1463" s="7" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C1463" s="7" t="inlineStr">
+        <is>
+          <t>1bbe154d</t>
+        </is>
+      </c>
+      <c r="D1463" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'recovery/consolidation-20260805-audit' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1463" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1463" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1464" s="15" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C1464" s="15" t="inlineStr">
+        <is>
+          <t>c86f8301</t>
+        </is>
+      </c>
+      <c r="D1464" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'recovery/consolidation-20260805-detached' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1464" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1464" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1465" s="7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C1465" s="7" t="inlineStr">
+        <is>
+          <t>0071830b</t>
+        </is>
+      </c>
+      <c r="D1465" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/ui-parity-improvements' into consolidation/20260805-main</t>
+        </is>
+      </c>
+      <c r="E1465" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1465" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1466" s="15" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C1466" s="15" t="inlineStr">
+        <is>
+          <t>741c435f</t>
+        </is>
+      </c>
+      <c r="D1466" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 frontend: 통합 후 모바일 타입 계약 정합화</t>
+        </is>
+      </c>
+      <c r="E1466" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1466" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1467" s="7" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="C1467" s="7" t="inlineStr">
+        <is>
+          <t>3c84a700</t>
+        </is>
+      </c>
+      <c r="D1467" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 frontend: 통합 WIP 흐름 복원</t>
+        </is>
+      </c>
+      <c r="E1467" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1467" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1468" s="15" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C1468" s="15" t="inlineStr">
+        <is>
+          <t>5cb8135e</t>
+        </is>
+      </c>
+      <c r="D1468" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05 e2e: 정상 복귀 확인 흐름 반영</t>
+        </is>
+      </c>
+      <c r="E1468" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1468" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1469" s="7" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C1469" s="7" t="inlineStr">
+        <is>
+          <t>cbc7974a</t>
+        </is>
+      </c>
+      <c r="D1469" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05 ux: 설정·BOM·수량 입력 흐름 개선</t>
+        </is>
+      </c>
+      <c r="E1469" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1469" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1470" s="15" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="C1470" s="15" t="inlineStr">
+        <is>
+          <t>5efc2f7c</t>
+        </is>
+      </c>
+      <c r="D1470" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 items: 품목 공통 표시 순서 적용</t>
+        </is>
+      </c>
+      <c r="E1470" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1470" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1471" s="7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C1471" s="7" t="inlineStr">
+        <is>
+          <t>cb8d85dd</t>
+        </is>
+      </c>
+      <c r="D1471" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 ux: 설정 모달 목록형 구성 개선</t>
+        </is>
+      </c>
+      <c r="E1471" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1471" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1472" s="15" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="C1472" s="15" t="inlineStr">
+        <is>
+          <t>7d3fa788</t>
+        </is>
+      </c>
+      <c r="D1472" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 daily-report: 빈 일보 화면 스크롤 조정</t>
+        </is>
+      </c>
+      <c r="E1472" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1472" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1473" s="7" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1473" s="7" t="inlineStr">
+        <is>
+          <t>d424a89f</t>
+        </is>
+      </c>
+      <c r="D1473" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 ui: 품목 등록 필수값 및 표 정렬 정비</t>
+        </is>
+      </c>
+      <c r="E1473" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1473" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1474" s="15" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C1474" s="15" t="inlineStr">
+        <is>
+          <t>b6246a46</t>
+        </is>
+      </c>
+      <c r="D1474" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 ops: 자동 동기화에서 소스 git 상태 가드 제거</t>
+        </is>
+      </c>
+      <c r="E1474" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1474" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1475" s="7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C1475" s="7" t="inlineStr">
+        <is>
+          <t>fd755999</t>
+        </is>
+      </c>
+      <c r="D1475" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 docs: 설정·관리자·입출고·대시보드 후속 TODO 수집</t>
+        </is>
+      </c>
+      <c r="E1475" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1475" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1476" s="15" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C1476" s="15" t="inlineStr">
+        <is>
+          <t>e4f02bb8</t>
+        </is>
+      </c>
+      <c r="D1476" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 ci: OpenAPI 기준과 번들 예산 갱신</t>
+        </is>
+      </c>
+      <c r="E1476" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1476" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1477" s="7" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C1477" s="7" t="inlineStr">
+        <is>
+          <t>b83dff18</t>
+        </is>
+      </c>
+      <c r="D1477" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 ux: 설정 모달 상호작용 개선</t>
+        </is>
+      </c>
+      <c r="E1477" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1477" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1478" s="15" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1478" s="15" t="inlineStr">
+        <is>
+          <t>fe808358</t>
+        </is>
+      </c>
+      <c r="D1478" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 items: 선택 항목 검증 및 폼 배치 조정</t>
+        </is>
+      </c>
+      <c r="E1478" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1478" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1479" s="7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C1479" s="7" t="inlineStr">
+        <is>
+          <t>5a3319dd</t>
+        </is>
+      </c>
+      <c r="D1479" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-06 items: 검색 중 품목 순서 재배치 차단</t>
+        </is>
+      </c>
+      <c r="E1479" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1479" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1480" s="15" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C1480" s="15" t="inlineStr">
+        <is>
+          <t>f365f682</t>
+        </is>
+      </c>
+      <c r="D1480" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-06 ops: 생산부 6개 부서 재고 동기화 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="E1480" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1480" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1479건 (회사 기간 670건)</t>
+          <t>1489건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -3059,8 +3059,35 @@
         </is>
       </c>
     </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-07  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (10)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="91">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A11:E11"/>
@@ -3081,6 +3108,7 @@
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
@@ -3669,16 +3697,16 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>출하 요청 인보이스·이력 관리 개선 완료 (인보이스·수정이력·이력검색)
-개인 일일 작업 일지 신설
+          <t>출하 요청 인보이스·이력 관리 개선 완료 (인보이스·수정이력·이력검색·BOM 재사용)
+일일 작업 일보 MES 도입 (기존 엑셀 작성 방식 대체)
 관리자 내보내기 화면 정리 — F704-02·F705-02
 모바일 조립 체크리스트 박스 간 이동 추가
-설정 화면 통합(테마·사이드바), 다크 모드 색상 개선
+설정 화면 통합(테마·사이드바) + 일반 탭 전환, 다크 모드 색상 개선
 품목 표시 순서 통일, 화면 실시간 갱신 적용</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -6051,7 +6079,7 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>개인 일일 작업 일지</t>
+          <t>일일 작업 일보 MES 도입</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -6064,7 +6092,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E98" s="10" t="inlineStr"/>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>기존 엑셀 작성 방식 대체</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="n">
@@ -6319,7 +6351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8299,6 +8331,30 @@
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="67.5" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 dashboard: 0 재고 칩 숨김 처리
+2026-08-07 shipping: BOM 후보 재사용 선택 추가
+2026-08-07 docs: 주간보고 7/25~8/7 갱신
+2026-08-07 inventory: 재고 동기화와 품목 정렬 도구 추가
+2026-08-07 backend: 출하 BOM 후보 스키마 컬럼 타입 복구 마이그레이션 추가</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -8315,7 +8371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1480"/>
+  <dimension ref="A1:F1490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -55686,6 +55742,326 @@
         </is>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1481" s="7" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C1481" s="7" t="inlineStr">
+        <is>
+          <t>5ce17642</t>
+        </is>
+      </c>
+      <c r="D1481" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 dashboard: 0 재고 칩 숨김 처리</t>
+        </is>
+      </c>
+      <c r="E1481" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1481" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1482" s="15" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="C1482" s="15" t="inlineStr">
+        <is>
+          <t>84371faf</t>
+        </is>
+      </c>
+      <c r="D1482" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 shipping: BOM 후보 재사용 선택 추가</t>
+        </is>
+      </c>
+      <c r="E1482" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1482" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1483" s="7" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C1483" s="7" t="inlineStr">
+        <is>
+          <t>ba472af2</t>
+        </is>
+      </c>
+      <c r="D1483" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 docs: 주간보고 7/25~8/7 갱신</t>
+        </is>
+      </c>
+      <c r="E1483" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1483" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1484" s="15" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C1484" s="15" t="inlineStr">
+        <is>
+          <t>6ac0832f</t>
+        </is>
+      </c>
+      <c r="D1484" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 inventory: 재고 동기화와 품목 정렬 도구 추가</t>
+        </is>
+      </c>
+      <c r="E1484" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1484" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1485" s="7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C1485" s="7" t="inlineStr">
+        <is>
+          <t>e50bc417</t>
+        </is>
+      </c>
+      <c r="D1485" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 backend: 출하 BOM 후보 스키마 컬럼 타입 복구 마이그레이션 추가</t>
+        </is>
+      </c>
+      <c r="E1485" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1485" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1486" s="15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C1486" s="15" t="inlineStr">
+        <is>
+          <t>0eb3a237</t>
+        </is>
+      </c>
+      <c r="D1486" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 frontend: ShippingFinalizationMode 타입 재노출 누락 보완</t>
+        </is>
+      </c>
+      <c r="E1486" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1486" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1487" s="7" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C1487" s="7" t="inlineStr">
+        <is>
+          <t>1f4b440c</t>
+        </is>
+      </c>
+      <c r="D1487" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 ops: 자동 동기화 하위 프로세스 출력 표시 복구</t>
+        </is>
+      </c>
+      <c r="E1487" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1487" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1488" s="15" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C1488" s="15" t="inlineStr">
+        <is>
+          <t>2e909b94</t>
+        </is>
+      </c>
+      <c r="D1488" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 ci: OpenAPI 기준 명세 갱신</t>
+        </is>
+      </c>
+      <c r="E1488" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1488" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1489" s="7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="C1489" s="7" t="inlineStr">
+        <is>
+          <t>dcce843d</t>
+        </is>
+      </c>
+      <c r="D1489" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 ci: 프런트 번들 예산 소폭 조정</t>
+        </is>
+      </c>
+      <c r="E1489" s="7" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1489" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1490" s="15" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C1490" s="15" t="inlineStr">
+        <is>
+          <t>8c216246</t>
+        </is>
+      </c>
+      <c r="D1490" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 desktop: 설정을 일반 탭으로 전환</t>
+        </is>
+      </c>
+      <c r="E1490" s="15" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F1490" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1489건 (회사 기간 670건)</t>
+          <t>1580건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>379건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>392건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>98 / 107개 (92%)</t>
+          <t>102 / 111개 (92%)</t>
         </is>
       </c>
     </row>
@@ -3074,6 +3074,216 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (12)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-10  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (14)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-12  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (6)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-13  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-14  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (9)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-18  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-19  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (18)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-20  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
             <t>■■■■■</t>
           </r>
           <r>
@@ -3086,13 +3296,41 @@
         </is>
       </c>
     </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-08-21  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (12)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="99">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A79:E79"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
@@ -3105,6 +3343,7 @@
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
@@ -3121,11 +3360,14 @@
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
@@ -3155,6 +3397,7 @@
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A61:E61"/>
@@ -3164,9 +3407,11 @@
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
@@ -3190,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3706,6 +3951,33 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" ht="129.6" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-08 ~ 08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>MES 단독 운영 전환 + 화면 정비</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>엑셀 병행 중단 — MES 단독 운영 전환
+생산 가능수량·BOM 화면 개편, 기준 출하품 자동 선정
+AS·연구용 사용출고 기능 확장 (BOM 차감 방식 포함)
+대시보드 필터 개선, 재작업 취소 안전성 보강
+입출고 내역 시각·표시 오류 수정, 재고 예약·부족 처리 개선
+BOM 완료 잠금, 관리자·전 메뉴 UI 정비
+품목 선택 전체 화면, 분해 재고 차감 오류 수정
+출하 요청 카드 수량 표시 추가</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
         <v>89</v>
       </c>
     </row>
@@ -3720,7 +3992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6124,102 +6396,102 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="n">
+      <c r="A100" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D100" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E100" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>MES 단독 운영 전환</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>엑셀 병행 기록 중단, MES를 재고 업무 단일 공식 기록으로 전환</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="12" t="n">
+      <c r="A101" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>PF별 생산 가능수량 화면</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>완제품별 생산 가능수량 확인 + BOM 화면 개편</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="12" t="n">
+      <c r="A102" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E102" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>기준 출하품 자동 선정</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>담당자 수동 선택 → 시스템 자동 선정</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="n">
+      <c r="A103" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E103" s="13" t="inlineStr">
-        <is>
-          <t>재고 가용성 계산 고도화</t>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>품목 선택 전체 화면</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>창고</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>창고 화면 품목 선택을 전체 화면으로 확대</t>
         </is>
       </c>
     </row>
@@ -6229,12 +6501,12 @@
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -6244,7 +6516,7 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6526,12 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
@@ -6267,7 +6539,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E105" s="13" t="inlineStr"/>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n">
@@ -6275,12 +6551,12 @@
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
@@ -6288,7 +6564,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E106" s="13" t="inlineStr"/>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
@@ -6296,12 +6576,12 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -6311,7 +6591,7 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
@@ -6321,20 +6601,112 @@
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C112" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D108" s="14" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E108" s="13" t="inlineStr">
+      <c r="E112" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -6351,7 +6723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8343,7 +8715,7 @@
         </is>
       </c>
       <c r="B84" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
@@ -8355,6 +8727,198 @@
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="67.5" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 admin: 관리자 탭 선택 윤곽선 복구
+2026-08-10 desktop: 일일 작업 일보 달력 팝업 복구
+2026-08-10 frontend: 로그인 화면 DEXRAY 마스코트 배치
+2026-08-10 backend: 창고 승인 재고 부족 오류 수정
+2026-08-10 docs: 주간보고 마감 정리 + 대시보드 후속 TODO 수집</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="67.5" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-12 frontend: 입출고 품목 선택 토글 개선
+2026-08-12 frontend: 재고 예약과 출고 가능 수량 표시 개선
+2026-08-12 frontend: 업무 허브 카드 호버 및 설명문 통일
+2026-08-12 backend: 직원 체크리스트 동기화 마이그레이션 추가
+2026-08-12 frontend: 출하 상세 가독성 개선</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="67.5" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13 inventory: 부서 승인 대기 재고 예약 적용
+2026-08-13 deploy: 모델 PF 핀 제거 정책 보강
+2026-08-13 runtime: 시작 시 DB 마이그레이션 준비 자동화
+2026-08-13 frontend: 출하 대시보드 일보 후속 UX 반영
+2026-08-13 docs: 전수 코드 품질·재고 신뢰도 감사 계획 추가</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="67.5" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 frontend: 실시간 갱신 화면 깜빡임 제거
+2026-08-14 warehouse: 사용출고 BOM·낱개 선택 지원
+2026-08-14 mes: 후속 UI와 재고 취소 안전성 개선
+2026-08-14 frontend: 직원 서버 운영 실행 안정화
+2026-08-14 frontend: 이력 시각을 KST로 고정</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="67.5" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 대시보드 필터 AND/OR 규칙 정상화
+2026-08-18 io: 낱개 부서 입출고 메모 필수화
+2026-08-18 frontend: 데스크톱 목록과 출하 이력 UI 개선
+2026-08-18 items: BOM 자동 재고 미반영 품목 지원
+2026-08-18 frontend: 로그인 직원 목록 로드 실패 원인을 콘솔에 남김</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="67.5" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 mes: 명칭·운영 계약·문서 정합화
+2026-08-19 history: 입출고 작성 간격과 이력 표면 복원
+2026-08-19 test: 위험 기반 검증 속도 개선
+Merge branch 'codex/verification-speed'
+2026-08-19 ci: Windows PowerShell UTF-8 검증 수정</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="67.5" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 frontend: 재고·입출고 목록 스크롤 영역 하단 모서리 마스킹 보정
+2026-08-20 frontend: 생산 가능수량 상세에서 BOM 미완성·PF 경로 없는 품목 흐림 표시
+2026-08-20 frontend: BOM 모달 트리 깊이 배경 혼합을 oklab 색공간으로 변경
+2026-08-20 handoff: 대시보드·입출고 내역 후속 TODO 2건 신설
+2026-08-20 weekly: 주간보고 8/8~8/21 갱신</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="67.5" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 warehouse: 연구 사용출고 BOM 차감 방식 추가
+2026-08-21 warehouse: 연구 사용출고 BOM 하위 수량 고정
+2026-08-21 warehouse: 품목 선택 전체 화면 추가
+Merge branch 'main' into HEAD
+2026-08-21 shipping: 출하 요청 이력 카드 정보 블록 정리</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -8371,7 +8935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1490"/>
+  <dimension ref="A1:F1581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56062,6 +56626,2918 @@
         </is>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1491" s="7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C1491" s="7" t="inlineStr">
+        <is>
+          <t>43a9a311</t>
+        </is>
+      </c>
+      <c r="D1491" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07 desktop: 데스크톱 UI 후속 개선</t>
+        </is>
+      </c>
+      <c r="E1491" s="7" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F1491" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1492" s="15" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C1492" s="15" t="inlineStr">
+        <is>
+          <t>ef01f06f</t>
+        </is>
+      </c>
+      <c r="D1492" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07 ux: 데스크톱 표면과 테두리 정리</t>
+        </is>
+      </c>
+      <c r="E1492" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1492" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1493" s="7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C1493" s="7" t="inlineStr">
+        <is>
+          <t>975fe00c</t>
+        </is>
+      </c>
+      <c r="D1493" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 admin: 관리자 탭 선택 윤곽선 복구</t>
+        </is>
+      </c>
+      <c r="E1493" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1493" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1494" s="15" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1494" s="15" t="inlineStr">
+        <is>
+          <t>44ed7ded</t>
+        </is>
+      </c>
+      <c r="D1494" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 desktop: 일일 작업 일보 달력 팝업 복구</t>
+        </is>
+      </c>
+      <c r="E1494" s="15" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="F1494" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1495" s="7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="C1495" s="7" t="inlineStr">
+        <is>
+          <t>0b508e9e</t>
+        </is>
+      </c>
+      <c r="D1495" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 frontend: 로그인 화면 DEXRAY 마스코트 배치</t>
+        </is>
+      </c>
+      <c r="E1495" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1495" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1496" s="15" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C1496" s="15" t="inlineStr">
+        <is>
+          <t>1ecf1192</t>
+        </is>
+      </c>
+      <c r="D1496" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 backend: 창고 승인 재고 부족 오류 수정</t>
+        </is>
+      </c>
+      <c r="E1496" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1496" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1497" s="7" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C1497" s="7" t="inlineStr">
+        <is>
+          <t>77c30d3d</t>
+        </is>
+      </c>
+      <c r="D1497" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 docs: 주간보고 마감 정리 + 대시보드 후속 TODO 수집</t>
+        </is>
+      </c>
+      <c r="E1497" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1497" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1498" s="15" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C1498" s="15" t="inlineStr">
+        <is>
+          <t>62e40f42</t>
+        </is>
+      </c>
+      <c r="D1498" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 frontend: 직원 환경 로그인 마스코트 표시</t>
+        </is>
+      </c>
+      <c r="E1498" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1498" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1499" s="7" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C1499" s="7" t="inlineStr">
+        <is>
+          <t>bf909d6f</t>
+        </is>
+      </c>
+      <c r="D1499" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 warehouse: 창고 수량보정 입출고 추가</t>
+        </is>
+      </c>
+      <c r="E1499" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1499" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1500" s="15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C1500" s="15" t="inlineStr">
+        <is>
+          <t>29d7c1f6</t>
+        </is>
+      </c>
+      <c r="D1500" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 frontend: 사이드바 탭 전환 애니메이션 통일</t>
+        </is>
+      </c>
+      <c r="E1500" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1500" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1501" s="7" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C1501" s="7" t="inlineStr">
+        <is>
+          <t>464b8e98</t>
+        </is>
+      </c>
+      <c r="D1501" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 frontend: 일일 작업 일보 저장 상태 동기화 수정</t>
+        </is>
+      </c>
+      <c r="E1501" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1501" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1502" s="15" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C1502" s="15" t="inlineStr">
+        <is>
+          <t>62a63047</t>
+        </is>
+      </c>
+      <c r="D1502" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 dashboard: AND OR 필터 조건 추가</t>
+        </is>
+      </c>
+      <c r="E1502" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1502" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1503" s="7" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="C1503" s="7" t="inlineStr">
+        <is>
+          <t>030d7127</t>
+        </is>
+      </c>
+      <c r="D1503" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 ops: 주간 재고 정합성 검증 도구 추가</t>
+        </is>
+      </c>
+      <c r="E1503" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1503" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1504" s="19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C1504" s="19" t="inlineStr">
+        <is>
+          <t>d218a87c</t>
+        </is>
+      </c>
+      <c r="D1504" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-10 admin: 관리자 탭 개별 테두리 복원</t>
+        </is>
+      </c>
+      <c r="E1504" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1504" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1505" s="19" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C1505" s="19" t="inlineStr">
+        <is>
+          <t>0a0323e7</t>
+        </is>
+      </c>
+      <c r="D1505" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-10 backend: OS 라이센스 라벨 생산 수량 제외</t>
+        </is>
+      </c>
+      <c r="E1505" s="19" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1505" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1506" s="19" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C1506" s="19" t="inlineStr">
+        <is>
+          <t>a868d534</t>
+        </is>
+      </c>
+      <c r="D1506" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-10 dev: 개발 서버 프로필 및 복구 안정화</t>
+        </is>
+      </c>
+      <c r="E1506" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1506" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1507" s="7" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1507" s="7" t="inlineStr">
+        <is>
+          <t>17852efd</t>
+        </is>
+      </c>
+      <c r="D1507" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12 frontend: 입출고 품목 선택 토글 개선</t>
+        </is>
+      </c>
+      <c r="E1507" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1507" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1508" s="15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C1508" s="15" t="inlineStr">
+        <is>
+          <t>41aff42f</t>
+        </is>
+      </c>
+      <c r="D1508" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-12 frontend: 재고 예약과 출고 가능 수량 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1508" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1508" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1509" s="7" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C1509" s="7" t="inlineStr">
+        <is>
+          <t>02f75d00</t>
+        </is>
+      </c>
+      <c r="D1509" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12 frontend: 업무 허브 카드 호버 및 설명문 통일</t>
+        </is>
+      </c>
+      <c r="E1509" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1509" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1510" s="15" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="C1510" s="15" t="inlineStr">
+        <is>
+          <t>9f23db70</t>
+        </is>
+      </c>
+      <c r="D1510" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-12 backend: 직원 체크리스트 동기화 마이그레이션 추가</t>
+        </is>
+      </c>
+      <c r="E1510" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1510" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1511" s="7" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C1511" s="7" t="inlineStr">
+        <is>
+          <t>7ca95a38</t>
+        </is>
+      </c>
+      <c r="D1511" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12 frontend: 출하 상세 가독성 개선</t>
+        </is>
+      </c>
+      <c r="E1511" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1511" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1512" s="19" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="C1512" s="19" t="inlineStr">
+        <is>
+          <t>ff116bd2</t>
+        </is>
+      </c>
+      <c r="D1512" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-12 capacity: 자동 기준 출하품 선정 전환</t>
+        </is>
+      </c>
+      <c r="E1512" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1512" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1513" s="19" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="C1513" s="19" t="inlineStr">
+        <is>
+          <t>71d6a34f</t>
+        </is>
+      </c>
+      <c r="D1513" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-13 inventory: 부서 승인 대기 재고 예약 적용</t>
+        </is>
+      </c>
+      <c r="E1513" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1513" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1514" s="15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1514" s="15" t="inlineStr">
+        <is>
+          <t>3400cb8c</t>
+        </is>
+      </c>
+      <c r="D1514" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-13 deploy: 모델 PF 핀 제거 정책 보강</t>
+        </is>
+      </c>
+      <c r="E1514" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1514" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1515" s="7" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C1515" s="7" t="inlineStr">
+        <is>
+          <t>42945db0</t>
+        </is>
+      </c>
+      <c r="D1515" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13 runtime: 시작 시 DB 마이그레이션 준비 자동화</t>
+        </is>
+      </c>
+      <c r="E1515" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1515" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1516" s="15" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C1516" s="15" t="inlineStr">
+        <is>
+          <t>90516ecb</t>
+        </is>
+      </c>
+      <c r="D1516" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-13 frontend: 출하 대시보드 일보 후속 UX 반영</t>
+        </is>
+      </c>
+      <c r="E1516" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1516" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1517" s="7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C1517" s="7" t="inlineStr">
+        <is>
+          <t>8be64743</t>
+        </is>
+      </c>
+      <c r="D1517" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13 docs: 전수 코드 품질·재고 신뢰도 감사 계획 추가</t>
+        </is>
+      </c>
+      <c r="E1517" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1517" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1518" s="15" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="C1518" s="15" t="inlineStr">
+        <is>
+          <t>f6a15640</t>
+        </is>
+      </c>
+      <c r="D1518" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-13 audit: 작업 감사 이력 및 내보내기 추가</t>
+        </is>
+      </c>
+      <c r="E1518" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1518" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1519" s="7" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="C1519" s="7" t="inlineStr">
+        <is>
+          <t>ab8b2a1e</t>
+        </is>
+      </c>
+      <c r="D1519" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13 quality: 1차 코드 품질 개선 체크포인트 반영</t>
+        </is>
+      </c>
+      <c r="E1519" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1519" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1520" s="15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C1520" s="15" t="inlineStr">
+        <is>
+          <t>715eb1b8</t>
+        </is>
+      </c>
+      <c r="D1520" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-13 items: 초기 재고 0 등록 허용</t>
+        </is>
+      </c>
+      <c r="E1520" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1520" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1521" s="7" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C1521" s="7" t="inlineStr">
+        <is>
+          <t>9afd57b6</t>
+        </is>
+      </c>
+      <c r="D1521" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13 docs: MES 전환 검토 보고서 및 검증 근거 추가</t>
+        </is>
+      </c>
+      <c r="E1521" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1521" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1522" s="15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="C1522" s="15" t="inlineStr">
+        <is>
+          <t>674b9106</t>
+        </is>
+      </c>
+      <c r="D1522" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 frontend: 실시간 갱신 화면 깜빡임 제거</t>
+        </is>
+      </c>
+      <c r="E1522" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1522" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1523" s="7" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C1523" s="7" t="inlineStr">
+        <is>
+          <t>acc24fcd</t>
+        </is>
+      </c>
+      <c r="D1523" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14 warehouse: 사용출고 BOM·낱개 선택 지원</t>
+        </is>
+      </c>
+      <c r="E1523" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1523" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1524" s="15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C1524" s="15" t="inlineStr">
+        <is>
+          <t>0fe9b11a</t>
+        </is>
+      </c>
+      <c r="D1524" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 mes: 후속 UI와 재고 취소 안전성 개선</t>
+        </is>
+      </c>
+      <c r="E1524" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1524" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1525" s="7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C1525" s="7" t="inlineStr">
+        <is>
+          <t>5777de35</t>
+        </is>
+      </c>
+      <c r="D1525" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14 frontend: 직원 서버 운영 실행 안정화</t>
+        </is>
+      </c>
+      <c r="E1525" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1525" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1526" s="15" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C1526" s="15" t="inlineStr">
+        <is>
+          <t>1c87d101</t>
+        </is>
+      </c>
+      <c r="D1526" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 frontend: 이력 시각을 KST로 고정</t>
+        </is>
+      </c>
+      <c r="E1526" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1526" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1527" s="7" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="C1527" s="7" t="inlineStr">
+        <is>
+          <t>1fe7467c</t>
+        </is>
+      </c>
+      <c r="D1527" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14 history: 입출고 요약 증감 표시 수정</t>
+        </is>
+      </c>
+      <c r="E1527" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1527" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1528" s="15" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C1528" s="15" t="inlineStr">
+        <is>
+          <t>b874201d</t>
+        </is>
+      </c>
+      <c r="D1528" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 fix: 실시간 갱신과 SQLite 조회 안정화</t>
+        </is>
+      </c>
+      <c r="E1528" s="15" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1528" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1529" s="7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C1529" s="7" t="inlineStr">
+        <is>
+          <t>9e166210</t>
+        </is>
+      </c>
+      <c r="D1529" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14 bom: 완료 BOM 수정 잠금 적용</t>
+        </is>
+      </c>
+      <c r="E1529" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1529" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1530" s="15" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="C1530" s="15" t="inlineStr">
+        <is>
+          <t>917145c3</t>
+        </is>
+      </c>
+      <c r="D1530" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-14 defect: 재작업 취소 호환성 및 연결 오류 안내 개선</t>
+        </is>
+      </c>
+      <c r="E1530" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1530" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1531" s="19" t="inlineStr">
+        <is>
+          <t>00:22</t>
+        </is>
+      </c>
+      <c r="C1531" s="19" t="inlineStr">
+        <is>
+          <t>66a08c5a</t>
+        </is>
+      </c>
+      <c r="D1531" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 대시보드 필터 AND/OR 규칙 정상화</t>
+        </is>
+      </c>
+      <c r="E1531" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1531" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1532" s="19" t="inlineStr">
+        <is>
+          <t>00:37</t>
+        </is>
+      </c>
+      <c r="C1532" s="19" t="inlineStr">
+        <is>
+          <t>c71cc729</t>
+        </is>
+      </c>
+      <c r="D1532" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-18 io: 낱개 부서 입출고 메모 필수화</t>
+        </is>
+      </c>
+      <c r="E1532" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1532" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1533" s="7" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="C1533" s="7" t="inlineStr">
+        <is>
+          <t>05afa1cf</t>
+        </is>
+      </c>
+      <c r="D1533" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 데스크톱 목록과 출하 이력 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1533" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1533" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1534" s="15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C1534" s="15" t="inlineStr">
+        <is>
+          <t>83349b02</t>
+        </is>
+      </c>
+      <c r="D1534" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-18 items: BOM 자동 재고 미반영 품목 지원</t>
+        </is>
+      </c>
+      <c r="E1534" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1534" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1535" s="7" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1535" s="7" t="inlineStr">
+        <is>
+          <t>3de3bba8</t>
+        </is>
+      </c>
+      <c r="D1535" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 로그인 직원 목록 로드 실패 원인을 콘솔에 남김</t>
+        </is>
+      </c>
+      <c r="E1535" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1535" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1536" s="15" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C1536" s="15" t="inlineStr">
+        <is>
+          <t>91fecf43</t>
+        </is>
+      </c>
+      <c r="D1536" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-18 chore: schema-readiness 테스트의 파일 지문 해시를 스트림 방식으로 변경</t>
+        </is>
+      </c>
+      <c r="E1536" s="15" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+      <c r="F1536" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1537" s="7" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C1537" s="7" t="inlineStr">
+        <is>
+          <t>ee2528a5</t>
+        </is>
+      </c>
+      <c r="D1537" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 handoff: 전 메뉴 후속 TODO 정리(2026-08-14 수집)</t>
+        </is>
+      </c>
+      <c r="E1537" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1537" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1538" s="15" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C1538" s="15" t="inlineStr">
+        <is>
+          <t>79c6d0b5</t>
+        </is>
+      </c>
+      <c r="D1538" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 상단 상태 표기에서 System 제거</t>
+        </is>
+      </c>
+      <c r="E1538" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1538" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1539" s="7" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C1539" s="7" t="inlineStr">
+        <is>
+          <t>8056633c</t>
+        </is>
+      </c>
+      <c r="D1539" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 warehouse: AS·연구 사용출고 위치별 차감 구현</t>
+        </is>
+      </c>
+      <c r="E1539" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1539" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1540" s="15" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C1540" s="15" t="inlineStr">
+        <is>
+          <t>ee9c59da</t>
+        </is>
+      </c>
+      <c r="D1540" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 입출고 수량 및 최종 확인 정렬 통일</t>
+        </is>
+      </c>
+      <c r="E1540" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1540" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1541" s="7" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="C1541" s="7" t="inlineStr">
+        <is>
+          <t>70084869</t>
+        </is>
+      </c>
+      <c r="D1541" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18 frontend: 전 메뉴 후속 UI 개선</t>
+        </is>
+      </c>
+      <c r="E1541" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1541" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1542" s="19" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="C1542" s="19" t="inlineStr">
+        <is>
+          <t>a2157fe9</t>
+        </is>
+      </c>
+      <c r="D1542" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 mes: 명칭·운영 계약·문서 정합화</t>
+        </is>
+      </c>
+      <c r="E1542" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1542" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1543" s="19" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="C1543" s="19" t="inlineStr">
+        <is>
+          <t>7edf4a11</t>
+        </is>
+      </c>
+      <c r="D1543" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 history: 입출고 작성 간격과 이력 표면 복원</t>
+        </is>
+      </c>
+      <c r="E1543" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1543" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1544" s="19" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C1544" s="19" t="inlineStr">
+        <is>
+          <t>f9f1dd28</t>
+        </is>
+      </c>
+      <c r="D1544" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 test: 위험 기반 검증 속도 개선</t>
+        </is>
+      </c>
+      <c r="E1544" s="19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F1544" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1545" s="7" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1545" s="7" t="inlineStr">
+        <is>
+          <t>d2661fd3</t>
+        </is>
+      </c>
+      <c r="D1545" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/verification-speed'</t>
+        </is>
+      </c>
+      <c r="E1545" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1545" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1546" s="15" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C1546" s="15" t="inlineStr">
+        <is>
+          <t>b84ac039</t>
+        </is>
+      </c>
+      <c r="D1546" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 ci: Windows PowerShell UTF-8 검증 수정</t>
+        </is>
+      </c>
+      <c r="E1546" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1546" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1547" s="7" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C1547" s="7" t="inlineStr">
+        <is>
+          <t>90ce42d9</t>
+        </is>
+      </c>
+      <c r="D1547" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19 handoff: 전 메뉴 후속 TODO 보강(UI 검증 원칙·추가 관찰)</t>
+        </is>
+      </c>
+      <c r="E1547" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1547" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1548" s="15" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C1548" s="15" t="inlineStr">
+        <is>
+          <t>a370f4ba</t>
+        </is>
+      </c>
+      <c r="D1548" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 frontend: 대시보드 불용 필터와 엄격한 AND 적용</t>
+        </is>
+      </c>
+      <c r="E1548" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1548" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1549" s="7" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C1549" s="7" t="inlineStr">
+        <is>
+          <t>dcf5835e</t>
+        </is>
+      </c>
+      <c r="D1549" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19 ux: BOM 구성 보기 트리 가독성 개선</t>
+        </is>
+      </c>
+      <c r="E1549" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1549" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1550" s="15" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C1550" s="15" t="inlineStr">
+        <is>
+          <t>350d2aae</t>
+        </is>
+      </c>
+      <c r="D1550" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 mes: KST 월 필터와 표면 품질 개선</t>
+        </is>
+      </c>
+      <c r="E1550" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1550" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1551" s="7" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C1551" s="7" t="inlineStr">
+        <is>
+          <t>1510cb56</t>
+        </is>
+      </c>
+      <c r="D1551" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19 ux: BOM 수량 조정 정렬과 UI 검토 기록</t>
+        </is>
+      </c>
+      <c r="E1551" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1551" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1552" s="15" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C1552" s="15" t="inlineStr">
+        <is>
+          <t>8bdb8921</t>
+        </is>
+      </c>
+      <c r="D1552" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 dashboard: PF별 생산 가능수량과 BOM 화면 개편</t>
+        </is>
+      </c>
+      <c r="E1552" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1552" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1553" s="7" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C1553" s="7" t="inlineStr">
+        <is>
+          <t>c01034a3</t>
+        </is>
+      </c>
+      <c r="D1553" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19 bom: BOM 현재 재고와 모달 UX 개선</t>
+        </is>
+      </c>
+      <c r="E1553" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1553" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1554" s="15" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C1554" s="15" t="inlineStr">
+        <is>
+          <t>f86dad54</t>
+        </is>
+      </c>
+      <c r="D1554" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 capacity: 생산 가능수량 상세 화면 정리</t>
+        </is>
+      </c>
+      <c r="E1554" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1554" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1555" s="7" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C1555" s="7" t="inlineStr">
+        <is>
+          <t>a587cbfe</t>
+        </is>
+      </c>
+      <c r="D1555" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19 frontend: OR 필터 구분 간 AND 적용</t>
+        </is>
+      </c>
+      <c r="E1555" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1555" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1556" s="15" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C1556" s="15" t="inlineStr">
+        <is>
+          <t>0369395b</t>
+        </is>
+      </c>
+      <c r="D1556" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-19 history: 입출고 내역 스크롤바 모서리 정리</t>
+        </is>
+      </c>
+      <c r="E1556" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1556" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1557" s="19" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C1557" s="19" t="inlineStr">
+        <is>
+          <t>16b532a9</t>
+        </is>
+      </c>
+      <c r="D1557" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 history: 입출고 내역 표 모서리와 담당자 열 정리</t>
+        </is>
+      </c>
+      <c r="E1557" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1557" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1558" s="19" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C1558" s="19" t="inlineStr">
+        <is>
+          <t>ab7f88c6</t>
+        </is>
+      </c>
+      <c r="D1558" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 history: 스크롤 중 표 모서리 배경 수정</t>
+        </is>
+      </c>
+      <c r="E1558" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1558" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1559" s="19" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="C1559" s="19" t="inlineStr">
+        <is>
+          <t>fdf0d561</t>
+        </is>
+      </c>
+      <c r="D1559" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-19 ci: 프런트 번들 예산 소폭 조정</t>
+        </is>
+      </c>
+      <c r="E1559" s="19" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1559" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1560" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1560" s="15" t="inlineStr">
+        <is>
+          <t>3eda140b</t>
+        </is>
+      </c>
+      <c r="D1560" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-20 frontend: 재고·입출고 목록 스크롤 영역 하단 모서리 마스킹 보정</t>
+        </is>
+      </c>
+      <c r="E1560" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1560" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1561" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1561" s="7" t="inlineStr">
+        <is>
+          <t>0fef6739</t>
+        </is>
+      </c>
+      <c r="D1561" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 frontend: 생산 가능수량 상세에서 BOM 미완성·PF 경로 없는 품목 흐림 표시</t>
+        </is>
+      </c>
+      <c r="E1561" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1561" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1562" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1562" s="15" t="inlineStr">
+        <is>
+          <t>3dadee4e</t>
+        </is>
+      </c>
+      <c r="D1562" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-20 frontend: BOM 모달 트리 깊이 배경 혼합을 oklab 색공간으로 변경</t>
+        </is>
+      </c>
+      <c r="E1562" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1562" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1563" s="7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C1563" s="7" t="inlineStr">
+        <is>
+          <t>f7d369c0</t>
+        </is>
+      </c>
+      <c r="D1563" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 handoff: 대시보드·입출고 내역 후속 TODO 2건 신설</t>
+        </is>
+      </c>
+      <c r="E1563" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1563" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1564" s="15" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C1564" s="15" t="inlineStr">
+        <is>
+          <t>dc3cbf0b</t>
+        </is>
+      </c>
+      <c r="D1564" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-20 weekly: 주간보고 8/8~8/21 갱신</t>
+        </is>
+      </c>
+      <c r="E1564" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1564" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1565" s="7" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C1565" s="7" t="inlineStr">
+        <is>
+          <t>d6a07eac</t>
+        </is>
+      </c>
+      <c r="D1565" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 docs: 스크롤바를 객체 밖 레일로 분리하는 작업 요령 신설</t>
+        </is>
+      </c>
+      <c r="E1565" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1565" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1566" s="15" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="C1566" s="15" t="inlineStr">
+        <is>
+          <t>82d9b02a</t>
+        </is>
+      </c>
+      <c r="D1566" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-20 handoff: 데스크톱 레이아웃·스크롤바·주간보고 TODO 신설</t>
+        </is>
+      </c>
+      <c r="E1566" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1566" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1567" s="7" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="C1567" s="7" t="inlineStr">
+        <is>
+          <t>1674fd48</t>
+        </is>
+      </c>
+      <c r="D1567" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 dev: 프런트 종료 후보 추적 추가</t>
+        </is>
+      </c>
+      <c r="E1567" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1567" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1568" s="15" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C1568" s="15" t="inlineStr">
+        <is>
+          <t>6e9af3f4</t>
+        </is>
+      </c>
+      <c r="D1568" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-20 ux: 데스크톱 UI와 다운로드 동작 통일</t>
+        </is>
+      </c>
+      <c r="E1568" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1568" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1569" s="7" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="C1569" s="7" t="inlineStr">
+        <is>
+          <t>7131e082</t>
+        </is>
+      </c>
+      <c r="D1569" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20 backend: 분해 차감 부서 기준 수정</t>
+        </is>
+      </c>
+      <c r="E1569" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F1569" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1570" s="15" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="C1570" s="15" t="inlineStr">
+        <is>
+          <t>9a39235c</t>
+        </is>
+      </c>
+      <c r="D1570" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 warehouse: 연구 사용출고 BOM 차감 방식 추가</t>
+        </is>
+      </c>
+      <c r="E1570" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1570" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1571" s="7" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C1571" s="7" t="inlineStr">
+        <is>
+          <t>ea6da670</t>
+        </is>
+      </c>
+      <c r="D1571" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21 warehouse: 연구 사용출고 BOM 하위 수량 고정</t>
+        </is>
+      </c>
+      <c r="E1571" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1571" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1572" s="15" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C1572" s="15" t="inlineStr">
+        <is>
+          <t>bf8d5412</t>
+        </is>
+      </c>
+      <c r="D1572" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 warehouse: 품목 선택 전체 화면 추가</t>
+        </is>
+      </c>
+      <c r="E1572" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1572" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1573" s="7" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C1573" s="7" t="inlineStr">
+        <is>
+          <t>957ec658</t>
+        </is>
+      </c>
+      <c r="D1573" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'main' into HEAD</t>
+        </is>
+      </c>
+      <c r="E1573" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1573" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1574" s="15" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C1574" s="15" t="inlineStr">
+        <is>
+          <t>92687887</t>
+        </is>
+      </c>
+      <c r="D1574" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 shipping: 출하 요청 이력 카드 정보 블록 정리</t>
+        </is>
+      </c>
+      <c r="E1574" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1574" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1575" s="7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C1575" s="7" t="inlineStr">
+        <is>
+          <t>70387b95</t>
+        </is>
+      </c>
+      <c r="D1575" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21 dashboard: 재고 화면 간격 정돈</t>
+        </is>
+      </c>
+      <c r="E1575" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1575" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1576" s="15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C1576" s="15" t="inlineStr">
+        <is>
+          <t>603a5993</t>
+        </is>
+      </c>
+      <c r="D1576" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 frontend: 대시보드 고정 헤더 곡률 정리</t>
+        </is>
+      </c>
+      <c r="E1576" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1576" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1577" s="7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C1577" s="7" t="inlineStr">
+        <is>
+          <t>42319b45</t>
+        </is>
+      </c>
+      <c r="D1577" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21 shipping: 출하 요청 카드 배치와 CI 오류 정리</t>
+        </is>
+      </c>
+      <c r="E1577" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1577" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1578" s="15" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C1578" s="15" t="inlineStr">
+        <is>
+          <t>d32a2b44</t>
+        </is>
+      </c>
+      <c r="D1578" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 ci: 누적 UI 변경에 맞춰 번들 예산 조정</t>
+        </is>
+      </c>
+      <c r="E1578" s="15" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="F1578" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1579" s="7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C1579" s="7" t="inlineStr">
+        <is>
+          <t>d498837c</t>
+        </is>
+      </c>
+      <c r="D1579" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21 dev: 프런트 종료 원인 진단 추가</t>
+        </is>
+      </c>
+      <c r="E1579" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1579" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1580" s="15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C1580" s="15" t="inlineStr">
+        <is>
+          <t>35e0b5ab</t>
+        </is>
+      </c>
+      <c r="D1580" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21 shipping: 출하 요청 카드·상세 헤더에 출하 수량 표시 추가</t>
+        </is>
+      </c>
+      <c r="E1580" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1580" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1581" s="7" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C1581" s="7" t="inlineStr">
+        <is>
+          <t>54d2f97e</t>
+        </is>
+      </c>
+      <c r="D1581" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21 docs: 원자재 보류 제거 계획·설계 문서 추가</t>
+        </is>
+      </c>
+      <c r="E1581" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1581" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
